--- a/test/package-of-documents/Відомості.xlsx
+++ b/test/package-of-documents/Відомості.xlsx
@@ -17,19 +17,19 @@
     <definedName name="Ф80">#REF!</definedName>
     <definedName name="A1048577" localSheetId="0">#REF!</definedName>
     <definedName name="Ф80" localSheetId="0">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Зведена D5'!$C$3:$T$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Зведена D5'!$C$3:$U$36</definedName>
     <definedName name="A1048577" localSheetId="1">#REF!</definedName>
     <definedName name="Ф80" localSheetId="1">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Зведена D7'!$C$3:$T$48</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Зведена D7'!$C$3:$U$48</definedName>
     <definedName name="A1048577" localSheetId="2">#REF!</definedName>
     <definedName name="Ф80" localSheetId="2">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Зведена G1'!$C$3:$T$25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Зведена G1'!$C$3:$U$25</definedName>
     <definedName name="A1048577" localSheetId="3">#REF!</definedName>
     <definedName name="Ф80" localSheetId="3">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Рейтингова D5'!$C$3:$U$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Рейтингова D5'!$C$3:$V$16</definedName>
     <definedName name="A1048577" localSheetId="4">#REF!</definedName>
     <definedName name="Ф80" localSheetId="4">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Рейтингова D7'!$C$3:$U$25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Рейтингова D7'!$C$3:$V$25</definedName>
   </definedNames>
   <calcPr calcId="191029" calcMode="autoNoTable" fullCalcOnLoad="1"/>
 </workbook>
@@ -1121,7 +1121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V38"/>
+  <dimension ref="A1:W38"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1"/>
   <cols>
     <col width="2.7109375" customWidth="1" style="1" min="1" max="2"/>
@@ -1129,10 +1129,9 @@
     <col width="6.5703125" customWidth="1" style="1" min="4" max="4"/>
     <col width="40.42578125" customWidth="1" style="1" min="5" max="5"/>
     <col width="6.7109375" customWidth="1" style="1" min="6" max="25"/>
-    <col width="11.3" customWidth="1" min="20" max="20"/>
-    <col width="2.7" customWidth="1" min="21" max="21"/>
+    <col width="11.3" customWidth="1" min="21" max="21"/>
     <col width="2.7" customWidth="1" min="22" max="22"/>
-    <col hidden="1" width="13" customWidth="1" min="23" max="23"/>
+    <col width="2.7" customWidth="1" min="23" max="23"/>
     <col hidden="1" width="13" customWidth="1" min="24" max="24"/>
     <col hidden="1" width="13" customWidth="1" min="25" max="25"/>
     <col hidden="1" width="11.28515625" customWidth="1" style="1" min="26" max="26"/>
@@ -1172,6 +1171,7 @@
       <c r="T1" s="38" t="n"/>
       <c r="U1" s="38" t="n"/>
       <c r="V1" s="38" t="n"/>
+      <c r="W1" s="38" t="n"/>
     </row>
     <row r="2" ht="12" customHeight="1">
       <c r="A2" s="40" t="n"/>
@@ -1194,8 +1194,9 @@
       <c r="R2" s="18" t="n"/>
       <c r="S2" s="18" t="n"/>
       <c r="T2" s="18" t="n"/>
-      <c r="U2" s="19" t="n"/>
-      <c r="V2" s="39" t="n"/>
+      <c r="U2" s="18" t="n"/>
+      <c r="V2" s="19" t="n"/>
+      <c r="W2" s="39" t="n"/>
     </row>
     <row r="3" ht="54.95" customFormat="1" customHeight="1" s="2">
       <c r="A3" s="40" t="n"/>
@@ -1224,8 +1225,9 @@
       <c r="R3" s="86" t="n"/>
       <c r="S3" s="86" t="n"/>
       <c r="T3" s="86" t="n"/>
-      <c r="U3" s="20" t="n"/>
-      <c r="V3" s="39" t="n"/>
+      <c r="U3" s="86" t="n"/>
+      <c r="V3" s="20" t="n"/>
+      <c r="W3" s="39" t="n"/>
     </row>
     <row r="4" ht="15" customFormat="1" customHeight="1" s="3">
       <c r="A4" s="40" t="n"/>
@@ -1252,8 +1254,9 @@
       <c r="R4" s="86" t="n"/>
       <c r="S4" s="86" t="n"/>
       <c r="T4" s="86" t="n"/>
-      <c r="U4" s="20" t="n"/>
-      <c r="V4" s="39" t="n"/>
+      <c r="U4" s="86" t="n"/>
+      <c r="V4" s="20" t="n"/>
+      <c r="W4" s="39" t="n"/>
     </row>
     <row r="5" ht="15" customFormat="1" customHeight="1" s="2">
       <c r="A5" s="40" t="n"/>
@@ -1280,15 +1283,16 @@
       <c r="R5" s="87" t="n"/>
       <c r="S5" s="87" t="n"/>
       <c r="T5" s="87" t="n"/>
-      <c r="U5" s="20" t="n"/>
-      <c r="V5" s="39" t="n"/>
+      <c r="U5" s="87" t="n"/>
+      <c r="V5" s="20" t="n"/>
+      <c r="W5" s="39" t="n"/>
     </row>
     <row r="6" ht="15" customFormat="1" customHeight="1" s="2">
       <c r="A6" s="40" t="n"/>
       <c r="B6" s="12" t="n"/>
       <c r="C6" s="73" t="inlineStr">
         <is>
-          <t>За І семестр 2025-2026 н.р.</t>
+          <t>За ІІ семестр 2025-2026 н.р.</t>
         </is>
       </c>
       <c r="D6" s="87" t="n"/>
@@ -1308,8 +1312,9 @@
       <c r="R6" s="87" t="n"/>
       <c r="S6" s="87" t="n"/>
       <c r="T6" s="87" t="n"/>
-      <c r="U6" s="20" t="n"/>
-      <c r="V6" s="39" t="n"/>
+      <c r="U6" s="87" t="n"/>
+      <c r="V6" s="20" t="n"/>
+      <c r="W6" s="39" t="n"/>
     </row>
     <row r="7" ht="15" customFormat="1" customHeight="1" s="2">
       <c r="A7" s="40" t="n"/>
@@ -1336,8 +1341,9 @@
       <c r="R7" s="88" t="n"/>
       <c r="S7" s="88" t="n"/>
       <c r="T7" s="88" t="n"/>
-      <c r="U7" s="20" t="n"/>
-      <c r="V7" s="39" t="n"/>
+      <c r="U7" s="88" t="n"/>
+      <c r="V7" s="20" t="n"/>
+      <c r="W7" s="39" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="40" t="n"/>
@@ -1375,14 +1381,15 @@
       <c r="P8" s="89" t="n"/>
       <c r="Q8" s="89" t="n"/>
       <c r="R8" s="89" t="n"/>
-      <c r="S8" s="90" t="n"/>
-      <c r="T8" s="91" t="inlineStr">
+      <c r="S8" s="89" t="n"/>
+      <c r="T8" s="90" t="n"/>
+      <c r="U8" s="91" t="inlineStr">
         <is>
           <t>Середній бал</t>
         </is>
       </c>
-      <c r="U8" s="20" t="n"/>
-      <c r="V8" s="39" t="n"/>
+      <c r="V8" s="20" t="n"/>
+      <c r="W8" s="39" t="n"/>
     </row>
     <row r="9" ht="125.1" customHeight="1">
       <c r="A9" s="40" t="n"/>
@@ -1392,91 +1399,97 @@
       <c r="E9" s="92" t="n"/>
       <c r="F9" s="13" t="inlineStr">
         <is>
+          <t>Астрономія
+Наговська Т.С.</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
           <t>Біологія
 Богданенко О.В.</t>
         </is>
       </c>
-      <c r="G9" s="13" t="inlineStr">
+      <c r="H9" s="13" t="inlineStr">
         <is>
           <t>Всесвітня історія
 Мельничук С.А.</t>
         </is>
       </c>
-      <c r="H9" s="13" t="inlineStr">
+      <c r="I9" s="13" t="inlineStr">
         <is>
           <t>Географія
 Наговська Т.С.</t>
         </is>
       </c>
-      <c r="I9" s="13" t="inlineStr">
+      <c r="J9" s="13" t="inlineStr">
         <is>
           <t>Зарубіжна література
 Сербулова Ю.А.</t>
         </is>
       </c>
-      <c r="J9" s="13" t="inlineStr">
+      <c r="K9" s="13" t="inlineStr">
         <is>
           <t>Захист України
 Лазар В.І.</t>
         </is>
       </c>
-      <c r="K9" s="13" t="inlineStr">
+      <c r="L9" s="13" t="inlineStr">
         <is>
           <t>Іноземна мова
 Сербулова Ю.А.</t>
         </is>
       </c>
-      <c r="L9" s="13" t="inlineStr">
+      <c r="M9" s="13" t="inlineStr">
         <is>
           <t>Інформатика
 Бєльдюгіна С.С.</t>
         </is>
       </c>
-      <c r="M9" s="13" t="inlineStr">
+      <c r="N9" s="13" t="inlineStr">
         <is>
           <t>Історія України
 Левчук Т.Г.</t>
         </is>
       </c>
-      <c r="N9" s="13" t="inlineStr">
+      <c r="O9" s="13" t="inlineStr">
         <is>
           <t>Математика
 Бондаренко О.С.</t>
         </is>
       </c>
-      <c r="O9" s="13" t="inlineStr">
+      <c r="P9" s="13" t="inlineStr">
         <is>
           <t>Українська література
 Антропова Л.І.</t>
         </is>
       </c>
-      <c r="P9" s="13" t="inlineStr">
+      <c r="Q9" s="13" t="inlineStr">
         <is>
           <t>Українська мова
 Антропова Л.І.</t>
         </is>
       </c>
-      <c r="Q9" s="13" t="inlineStr">
+      <c r="R9" s="13" t="inlineStr">
         <is>
           <t>Фізика
 Калюта Н.М.</t>
         </is>
       </c>
-      <c r="R9" s="13" t="inlineStr">
+      <c r="S9" s="13" t="inlineStr">
         <is>
           <t>Фізична культура
 Возіян О.Г.</t>
         </is>
       </c>
-      <c r="S9" s="13" t="inlineStr">
+      <c r="T9" s="13" t="inlineStr">
         <is>
           <t>Хімія
 Сахно Н.О.</t>
         </is>
       </c>
-      <c r="T9" s="92" t="n"/>
-      <c r="U9" s="20" t="n"/>
-      <c r="V9" s="39" t="n"/>
+      <c r="U9" s="92" t="n"/>
+      <c r="V9" s="20" t="n"/>
+      <c r="W9" s="39" t="n"/>
     </row>
     <row r="10" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A10" s="40" t="n"/>
@@ -1495,55 +1508,58 @@
         </is>
       </c>
       <c r="F10" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="G10" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="G10" s="49" t="n">
+      <c r="H10" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="H10" s="49" t="n">
+      <c r="I10" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="I10" s="49" t="n">
+      <c r="J10" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="J10" s="49" t="n">
+      <c r="K10" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="K10" s="49" t="n">
+      <c r="L10" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="L10" s="49" t="n">
-        <v>8</v>
-      </c>
-      <c r="M10" s="49" t="inlineStr">
+      <c r="M10" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="N10" s="49" t="inlineStr">
         <is>
           <t>н/а</t>
         </is>
       </c>
-      <c r="N10" s="49" t="n">
+      <c r="O10" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="O10" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="P10" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q10" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="Q10" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="R10" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="S10" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="S10" s="49" t="n">
+      <c r="T10" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="T10" s="42">
-        <f>IF(COUNTIF($F10:S10,"=*")&gt;0,IF($C10="К","-"," - "),IF(COUNTIF($F10:S10,"&lt;4")&gt;0,IF(C10="К","-"," - "),(IFERROR(AVERAGE($F10:S10),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U10" s="22" t="n"/>
-      <c r="V10" s="39" t="n"/>
+      <c r="U10" s="42">
+        <f>IF(COUNTIF($F10:T10,"=*")&gt;0,IF($C10="К","-"," - "),IF(COUNTIF($F10:T10,"&lt;4")&gt;0,IF(C10="К","-"," - "),(IFERROR(AVERAGE($F10:T10),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V10" s="22" t="n"/>
+      <c r="W10" s="39" t="n"/>
     </row>
     <row r="11" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A11" s="40" t="n"/>
@@ -1562,55 +1578,58 @@
         </is>
       </c>
       <c r="F11" s="49" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G11" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="H11" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="H11" s="49" t="n">
+      <c r="I11" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="I11" s="49" t="n">
+      <c r="J11" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="J11" s="49" t="n">
-        <v>6</v>
-      </c>
       <c r="K11" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="L11" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="L11" s="49" t="n">
+      <c r="M11" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="M11" s="49" t="inlineStr">
+      <c r="N11" s="49" t="inlineStr">
         <is>
           <t>н/а</t>
         </is>
       </c>
-      <c r="N11" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="O11" s="49" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P11" s="49" t="n">
         <v>7</v>
       </c>
       <c r="Q11" s="49" t="n">
+        <v>7</v>
+      </c>
+      <c r="R11" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="R11" s="49" t="n">
+      <c r="S11" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="S11" s="49" t="n">
+      <c r="T11" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="T11" s="42">
-        <f>IF(COUNTIF($F11:S11,"=*")&gt;0,IF($C11="К","-"," - "),IF(COUNTIF($F11:S11,"&lt;4")&gt;0,IF(C11="К","-"," - "),(IFERROR(AVERAGE($F11:S11),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U11" s="22" t="n"/>
-      <c r="V11" s="39" t="n"/>
+      <c r="U11" s="42">
+        <f>IF(COUNTIF($F11:T11,"=*")&gt;0,IF($C11="К","-"," - "),IF(COUNTIF($F11:T11,"&lt;4")&gt;0,IF(C11="К","-"," - "),(IFERROR(AVERAGE($F11:T11),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V11" s="22" t="n"/>
+      <c r="W11" s="39" t="n"/>
     </row>
     <row r="12" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A12" s="40" t="n"/>
@@ -1629,57 +1648,60 @@
         </is>
       </c>
       <c r="F12" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="G12" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="G12" s="49" t="n">
+      <c r="H12" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="H12" s="49" t="n">
+      <c r="I12" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="I12" s="49" t="inlineStr">
+      <c r="J12" s="49" t="inlineStr">
         <is>
           <t>н/а</t>
         </is>
       </c>
-      <c r="J12" s="49" t="n">
+      <c r="K12" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="K12" s="49" t="n">
+      <c r="L12" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="L12" s="49" t="n">
+      <c r="M12" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="M12" s="49" t="n">
-        <v>6</v>
-      </c>
       <c r="N12" s="49" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O12" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="P12" s="49" t="n">
         <v>9</v>
-      </c>
-      <c r="P12" s="49" t="n">
-        <v>10</v>
       </c>
       <c r="Q12" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="R12" s="49" t="inlineStr">
+      <c r="R12" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="S12" s="49" t="inlineStr">
         <is>
           <t>н/а</t>
         </is>
       </c>
-      <c r="S12" s="49" t="n">
+      <c r="T12" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="T12" s="42">
-        <f>IF(COUNTIF($F12:S12,"=*")&gt;0,IF($C12="К","-"," - "),IF(COUNTIF($F12:S12,"&lt;4")&gt;0,IF(C12="К","-"," - "),(IFERROR(AVERAGE($F12:S12),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U12" s="22" t="n"/>
-      <c r="V12" s="39" t="n"/>
+      <c r="U12" s="42">
+        <f>IF(COUNTIF($F12:T12,"=*")&gt;0,IF($C12="К","-"," - "),IF(COUNTIF($F12:T12,"&lt;4")&gt;0,IF(C12="К","-"," - "),(IFERROR(AVERAGE($F12:T12),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V12" s="22" t="n"/>
+      <c r="W12" s="39" t="n"/>
     </row>
     <row r="13" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A13" s="40" t="n"/>
@@ -1698,53 +1720,56 @@
         </is>
       </c>
       <c r="F13" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="G13" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="G13" s="49" t="n">
-        <v>6</v>
-      </c>
       <c r="H13" s="49" t="n">
         <v>6</v>
       </c>
       <c r="I13" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="J13" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="J13" s="49" t="n">
+      <c r="K13" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="K13" s="49" t="n">
+      <c r="L13" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="L13" s="49" t="n">
+      <c r="M13" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="M13" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="N13" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="O13" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="O13" s="49" t="n">
+      <c r="P13" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="P13" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="Q13" s="49" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R13" s="49" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="S13" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="T13" s="42">
-        <f>IF(COUNTIF($F13:S13,"=*")&gt;0,IF($C13="К","-"," - "),IF(COUNTIF($F13:S13,"&lt;4")&gt;0,IF(C13="К","-"," - "),(IFERROR(AVERAGE($F13:S13),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U13" s="22" t="n"/>
-      <c r="V13" s="39" t="n"/>
+      <c r="T13" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="U13" s="42">
+        <f>IF(COUNTIF($F13:T13,"=*")&gt;0,IF($C13="К","-"," - "),IF(COUNTIF($F13:T13,"&lt;4")&gt;0,IF(C13="К","-"," - "),(IFERROR(AVERAGE($F13:T13),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V13" s="22" t="n"/>
+      <c r="W13" s="39" t="n"/>
     </row>
     <row r="14" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A14" s="40" t="n"/>
@@ -1763,57 +1788,60 @@
         </is>
       </c>
       <c r="F14" s="49" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G14" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="H14" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="H14" s="49" t="n">
+      <c r="I14" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="I14" s="49" t="n">
-        <v>6</v>
-      </c>
       <c r="J14" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="K14" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="K14" s="49" t="inlineStr">
+      <c r="L14" s="49" t="inlineStr">
         <is>
           <t>н/а</t>
         </is>
       </c>
-      <c r="L14" s="49" t="n">
-        <v>6</v>
-      </c>
       <c r="M14" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="N14" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="N14" s="49" t="n">
+      <c r="O14" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="O14" s="49" t="inlineStr">
+      <c r="P14" s="49" t="inlineStr">
         <is>
           <t>н/а</t>
         </is>
       </c>
-      <c r="P14" s="49" t="n">
+      <c r="Q14" s="49" t="n">
         <v>5</v>
-      </c>
-      <c r="Q14" s="49" t="n">
-        <v>10</v>
       </c>
       <c r="R14" s="49" t="n">
         <v>10</v>
       </c>
       <c r="S14" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="T14" s="42">
-        <f>IF(COUNTIF($F14:S14,"=*")&gt;0,IF($C14="К","-"," - "),IF(COUNTIF($F14:S14,"&lt;4")&gt;0,IF(C14="К","-"," - "),(IFERROR(AVERAGE($F14:S14),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U14" s="22" t="n"/>
-      <c r="V14" s="39" t="n"/>
+      <c r="U14" s="42">
+        <f>IF(COUNTIF($F14:T14,"=*")&gt;0,IF($C14="К","-"," - "),IF(COUNTIF($F14:T14,"&lt;4")&gt;0,IF(C14="К","-"," - "),(IFERROR(AVERAGE($F14:T14),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V14" s="22" t="n"/>
+      <c r="W14" s="39" t="n"/>
     </row>
     <row r="15" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A15" s="40" t="n"/>
@@ -1832,59 +1860,62 @@
         </is>
       </c>
       <c r="F15" s="49" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G15" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="H15" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="H15" s="49" t="n">
+      <c r="I15" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="I15" s="49" t="n">
+      <c r="J15" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="J15" s="49" t="n">
-        <v>6</v>
-      </c>
       <c r="K15" s="49" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L15" s="49" t="n">
         <v>8</v>
       </c>
       <c r="M15" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="N15" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="N15" s="49" t="n">
+      <c r="O15" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="O15" s="49" t="inlineStr">
+      <c r="P15" s="49" t="inlineStr">
         <is>
           <t>н/а</t>
         </is>
       </c>
-      <c r="P15" s="49" t="n">
+      <c r="Q15" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="Q15" s="49" t="inlineStr">
+      <c r="R15" s="49" t="inlineStr">
         <is>
           <t>н/а</t>
         </is>
       </c>
-      <c r="R15" s="49" t="n">
+      <c r="S15" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="S15" s="49" t="inlineStr">
+      <c r="T15" s="49" t="inlineStr">
         <is>
           <t>н/а</t>
         </is>
       </c>
-      <c r="T15" s="42">
-        <f>IF(COUNTIF($F15:S15,"=*")&gt;0,IF($C15="К","-"," - "),IF(COUNTIF($F15:S15,"&lt;4")&gt;0,IF(C15="К","-"," - "),(IFERROR(AVERAGE($F15:S15),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U15" s="22" t="n"/>
-      <c r="V15" s="39" t="n"/>
+      <c r="U15" s="42">
+        <f>IF(COUNTIF($F15:T15,"=*")&gt;0,IF($C15="К","-"," - "),IF(COUNTIF($F15:T15,"&lt;4")&gt;0,IF(C15="К","-"," - "),(IFERROR(AVERAGE($F15:T15),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V15" s="22" t="n"/>
+      <c r="W15" s="39" t="n"/>
     </row>
     <row r="16" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A16" s="40" t="n"/>
@@ -1908,54 +1939,57 @@
       <c r="G16" s="49" t="n">
         <v>8</v>
       </c>
-      <c r="H16" s="49" t="inlineStr">
+      <c r="H16" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="I16" s="49" t="inlineStr">
         <is>
           <t>н/а</t>
         </is>
       </c>
-      <c r="I16" s="49" t="n">
+      <c r="J16" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="J16" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="K16" s="49" t="n">
         <v>8</v>
       </c>
       <c r="L16" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="M16" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="M16" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="N16" s="49" t="n">
         <v>8</v>
       </c>
-      <c r="O16" s="49" t="inlineStr">
+      <c r="O16" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="P16" s="49" t="inlineStr">
         <is>
           <t>н/а</t>
         </is>
       </c>
-      <c r="P16" s="49" t="inlineStr">
+      <c r="Q16" s="49" t="inlineStr">
         <is>
           <t>н/а</t>
         </is>
       </c>
-      <c r="Q16" s="49" t="n">
+      <c r="R16" s="49" t="n">
         <v>5</v>
-      </c>
-      <c r="R16" s="49" t="n">
-        <v>10</v>
       </c>
       <c r="S16" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="T16" s="42">
-        <f>IF(COUNTIF($F16:S16,"=*")&gt;0,IF($C16="К","-"," - "),IF(COUNTIF($F16:S16,"&lt;4")&gt;0,IF(C16="К","-"," - "),(IFERROR(AVERAGE($F16:S16),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U16" s="22" t="n"/>
-      <c r="V16" s="39" t="n"/>
+      <c r="T16" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="U16" s="42">
+        <f>IF(COUNTIF($F16:T16,"=*")&gt;0,IF($C16="К","-"," - "),IF(COUNTIF($F16:T16,"&lt;4")&gt;0,IF(C16="К","-"," - "),(IFERROR(AVERAGE($F16:T16),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V16" s="22" t="n"/>
+      <c r="W16" s="39" t="n"/>
     </row>
     <row r="17" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A17" s="40" t="n"/>
@@ -1974,53 +2008,56 @@
         </is>
       </c>
       <c r="F17" s="49" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G17" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="H17" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="H17" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="I17" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="J17" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="J17" s="49" t="n">
+      <c r="K17" s="49" t="n">
         <v>9</v>
-      </c>
-      <c r="K17" s="49" t="n">
-        <v>10</v>
       </c>
       <c r="L17" s="49" t="n">
         <v>10</v>
       </c>
       <c r="M17" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="N17" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="N17" s="49" t="n">
-        <v>6</v>
-      </c>
       <c r="O17" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="P17" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="P17" s="49" t="n">
+      <c r="Q17" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="Q17" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="R17" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="S17" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="S17" s="49" t="n">
+      <c r="T17" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="T17" s="42">
-        <f>IF(COUNTIF($F17:S17,"=*")&gt;0,IF($C17="К","-"," - "),IF(COUNTIF($F17:S17,"&lt;4")&gt;0,IF(C17="К","-"," - "),(IFERROR(AVERAGE($F17:S17),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U17" s="22" t="n"/>
-      <c r="V17" s="39" t="n"/>
+      <c r="U17" s="42">
+        <f>IF(COUNTIF($F17:T17,"=*")&gt;0,IF($C17="К","-"," - "),IF(COUNTIF($F17:T17,"&lt;4")&gt;0,IF(C17="К","-"," - "),(IFERROR(AVERAGE($F17:T17),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V17" s="22" t="n"/>
+      <c r="W17" s="39" t="n"/>
     </row>
     <row r="18" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A18" s="40" t="n"/>
@@ -2039,57 +2076,60 @@
         </is>
       </c>
       <c r="F18" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="G18" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="G18" s="49" t="n">
+      <c r="H18" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="H18" s="49" t="inlineStr">
+      <c r="I18" s="49" t="inlineStr">
         <is>
           <t>н/а</t>
         </is>
       </c>
-      <c r="I18" s="49" t="n">
+      <c r="J18" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="J18" s="49" t="n">
-        <v>6</v>
-      </c>
-      <c r="K18" s="49" t="inlineStr">
+      <c r="K18" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="L18" s="49" t="inlineStr">
         <is>
           <t>н/а</t>
         </is>
-      </c>
-      <c r="L18" s="49" t="n">
-        <v>11</v>
       </c>
       <c r="M18" s="49" t="n">
         <v>11</v>
       </c>
       <c r="N18" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="O18" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="O18" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="P18" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q18" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="Q18" s="49" t="n">
+      <c r="R18" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="R18" s="49" t="n">
+      <c r="S18" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="S18" s="49" t="n">
+      <c r="T18" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="T18" s="42">
-        <f>IF(COUNTIF($F18:S18,"=*")&gt;0,IF($C18="К","-"," - "),IF(COUNTIF($F18:S18,"&lt;4")&gt;0,IF(C18="К","-"," - "),(IFERROR(AVERAGE($F18:S18),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U18" s="22" t="n"/>
-      <c r="V18" s="39" t="n"/>
+      <c r="U18" s="42">
+        <f>IF(COUNTIF($F18:T18,"=*")&gt;0,IF($C18="К","-"," - "),IF(COUNTIF($F18:T18,"&lt;4")&gt;0,IF(C18="К","-"," - "),(IFERROR(AVERAGE($F18:T18),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V18" s="22" t="n"/>
+      <c r="W18" s="39" t="n"/>
     </row>
     <row r="19" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A19" s="40" t="n"/>
@@ -2111,50 +2151,53 @@
         <v>4</v>
       </c>
       <c r="G19" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="H19" s="49" t="n">
         <v>7</v>
-      </c>
-      <c r="H19" s="49" t="n">
-        <v>9</v>
       </c>
       <c r="I19" s="49" t="n">
         <v>9</v>
       </c>
       <c r="J19" s="49" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K19" s="49" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L19" s="49" t="n">
         <v>8</v>
       </c>
       <c r="M19" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="N19" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="N19" s="49" t="n">
+      <c r="O19" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="O19" s="49" t="n">
+      <c r="P19" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="P19" s="49" t="n">
+      <c r="Q19" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="Q19" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="R19" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="S19" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="S19" s="49" t="n">
-        <v>8</v>
-      </c>
-      <c r="T19" s="42">
-        <f>IF(COUNTIF($F19:S19,"=*")&gt;0,IF($C19="К","-"," - "),IF(COUNTIF($F19:S19,"&lt;4")&gt;0,IF(C19="К","-"," - "),(IFERROR(AVERAGE($F19:S19),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U19" s="22" t="n"/>
-      <c r="V19" s="39" t="n"/>
+      <c r="T19" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="U19" s="42">
+        <f>IF(COUNTIF($F19:T19,"=*")&gt;0,IF($C19="К","-"," - "),IF(COUNTIF($F19:T19,"&lt;4")&gt;0,IF(C19="К","-"," - "),(IFERROR(AVERAGE($F19:T19),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V19" s="22" t="n"/>
+      <c r="W19" s="39" t="n"/>
     </row>
     <row r="20" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A20" s="40" t="n"/>
@@ -2173,53 +2216,56 @@
         </is>
       </c>
       <c r="F20" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="G20" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="G20" s="49" t="n">
+      <c r="H20" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="H20" s="49" t="n">
+      <c r="I20" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="I20" s="49" t="n">
+      <c r="J20" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="J20" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="K20" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="L20" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="L20" s="49" t="n">
+      <c r="M20" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="M20" s="49" t="n">
+      <c r="N20" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="N20" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="O20" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="P20" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="P20" s="49" t="n">
+      <c r="Q20" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="Q20" s="49" t="n">
+      <c r="R20" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="R20" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="S20" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="T20" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="T20" s="42">
-        <f>IF(COUNTIF($F20:S20,"=*")&gt;0,IF($C20="К","-"," - "),IF(COUNTIF($F20:S20,"&lt;4")&gt;0,IF(C20="К","-"," - "),(IFERROR(AVERAGE($F20:S20),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U20" s="22" t="n"/>
-      <c r="V20" s="39" t="n"/>
+      <c r="U20" s="42">
+        <f>IF(COUNTIF($F20:T20,"=*")&gt;0,IF($C20="К","-"," - "),IF(COUNTIF($F20:T20,"&lt;4")&gt;0,IF(C20="К","-"," - "),(IFERROR(AVERAGE($F20:T20),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V20" s="22" t="n"/>
+      <c r="W20" s="39" t="n"/>
     </row>
     <row r="21" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A21" s="40" t="n"/>
@@ -2238,38 +2284,38 @@
         </is>
       </c>
       <c r="F21" s="49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G21" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="H21" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="H21" s="49" t="n">
+      <c r="I21" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="I21" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="J21" s="49" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K21" s="49" t="n">
         <v>5</v>
       </c>
       <c r="L21" s="49" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M21" s="49" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N21" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="O21" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="O21" s="49" t="n">
+      <c r="P21" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="P21" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="Q21" s="49" t="n">
         <v>8</v>
       </c>
@@ -2279,12 +2325,15 @@
       <c r="S21" s="49" t="n">
         <v>8</v>
       </c>
-      <c r="T21" s="42">
-        <f>IF(COUNTIF($F21:S21,"=*")&gt;0,IF($C21="К","-"," - "),IF(COUNTIF($F21:S21,"&lt;4")&gt;0,IF(C21="К","-"," - "),(IFERROR(AVERAGE($F21:S21),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U21" s="22" t="n"/>
-      <c r="V21" s="39" t="n"/>
+      <c r="T21" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="U21" s="42">
+        <f>IF(COUNTIF($F21:T21,"=*")&gt;0,IF($C21="К","-"," - "),IF(COUNTIF($F21:T21,"&lt;4")&gt;0,IF(C21="К","-"," - "),(IFERROR(AVERAGE($F21:T21),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V21" s="22" t="n"/>
+      <c r="W21" s="39" t="n"/>
     </row>
     <row r="22" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A22" s="40" t="n"/>
@@ -2303,57 +2352,60 @@
         </is>
       </c>
       <c r="F22" s="49" t="n">
-        <v>6</v>
-      </c>
-      <c r="G22" s="49" t="inlineStr">
+        <v>11</v>
+      </c>
+      <c r="G22" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="H22" s="49" t="inlineStr">
         <is>
           <t>н/а</t>
         </is>
-      </c>
-      <c r="H22" s="49" t="n">
-        <v>9</v>
       </c>
       <c r="I22" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="J22" s="49" t="inlineStr">
+      <c r="J22" s="49" t="n">
+        <v>9</v>
+      </c>
+      <c r="K22" s="49" t="inlineStr">
         <is>
           <t>н/а</t>
         </is>
       </c>
-      <c r="K22" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="L22" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="M22" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="M22" s="49" t="n">
+      <c r="N22" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="N22" s="49" t="n">
-        <v>6</v>
-      </c>
       <c r="O22" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="P22" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="P22" s="49" t="n">
+      <c r="Q22" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="Q22" s="49" t="n">
+      <c r="R22" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="R22" s="49" t="n">
-        <v>6</v>
-      </c>
       <c r="S22" s="49" t="n">
-        <v>8</v>
-      </c>
-      <c r="T22" s="42">
-        <f>IF(COUNTIF($F22:S22,"=*")&gt;0,IF($C22="К","-"," - "),IF(COUNTIF($F22:S22,"&lt;4")&gt;0,IF(C22="К","-"," - "),(IFERROR(AVERAGE($F22:S22),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U22" s="22" t="n"/>
-      <c r="V22" s="39" t="n"/>
+        <v>6</v>
+      </c>
+      <c r="T22" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="U22" s="42">
+        <f>IF(COUNTIF($F22:T22,"=*")&gt;0,IF($C22="К","-"," - "),IF(COUNTIF($F22:T22,"&lt;4")&gt;0,IF(C22="К","-"," - "),(IFERROR(AVERAGE($F22:T22),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V22" s="22" t="n"/>
+      <c r="W22" s="39" t="n"/>
     </row>
     <row r="23" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A23" s="40" t="n"/>
@@ -2372,53 +2424,56 @@
         </is>
       </c>
       <c r="F23" s="49" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G23" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="H23" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="H23" s="49" t="n">
+      <c r="I23" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="I23" s="49" t="n">
+      <c r="J23" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="J23" s="49" t="n">
+      <c r="K23" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="K23" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="L23" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="M23" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="M23" s="49" t="n">
+      <c r="N23" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="N23" s="49" t="n">
+      <c r="O23" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="O23" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="P23" s="49" t="n">
         <v>8</v>
       </c>
       <c r="Q23" s="49" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R23" s="49" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="S23" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="T23" s="42">
-        <f>IF(COUNTIF($F23:S23,"=*")&gt;0,IF($C23="К","-"," - "),IF(COUNTIF($F23:S23,"&lt;4")&gt;0,IF(C23="К","-"," - "),(IFERROR(AVERAGE($F23:S23),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U23" s="22" t="n"/>
-      <c r="V23" s="39" t="n"/>
+      <c r="T23" s="49" t="n">
+        <v>9</v>
+      </c>
+      <c r="U23" s="42">
+        <f>IF(COUNTIF($F23:T23,"=*")&gt;0,IF($C23="К","-"," - "),IF(COUNTIF($F23:T23,"&lt;4")&gt;0,IF(C23="К","-"," - "),(IFERROR(AVERAGE($F23:T23),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V23" s="22" t="n"/>
+      <c r="W23" s="39" t="n"/>
     </row>
     <row r="24" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A24" s="40" t="n"/>
@@ -2437,27 +2492,27 @@
         </is>
       </c>
       <c r="F24" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="G24" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="G24" s="49" t="n">
-        <v>6</v>
-      </c>
       <c r="H24" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="I24" s="49" t="inlineStr">
+      <c r="I24" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="J24" s="49" t="inlineStr">
         <is>
           <t>н/а</t>
         </is>
       </c>
-      <c r="J24" s="49" t="n">
+      <c r="K24" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="K24" s="49" t="n">
+      <c r="L24" s="49" t="n">
         <v>9</v>
-      </c>
-      <c r="L24" s="49" t="n">
-        <v>11</v>
       </c>
       <c r="M24" s="49" t="n">
         <v>11</v>
@@ -2466,26 +2521,29 @@
         <v>11</v>
       </c>
       <c r="O24" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="P24" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="P24" s="49" t="n">
+      <c r="Q24" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="Q24" s="49" t="n">
+      <c r="R24" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="R24" s="49" t="n">
+      <c r="S24" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="S24" s="49" t="n">
-        <v>8</v>
-      </c>
-      <c r="T24" s="42">
-        <f>IF(COUNTIF($F24:S24,"=*")&gt;0,IF($C24="К","-"," - "),IF(COUNTIF($F24:S24,"&lt;4")&gt;0,IF(C24="К","-"," - "),(IFERROR(AVERAGE($F24:S24),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U24" s="22" t="n"/>
-      <c r="V24" s="39" t="n"/>
+      <c r="T24" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="U24" s="42">
+        <f>IF(COUNTIF($F24:T24,"=*")&gt;0,IF($C24="К","-"," - "),IF(COUNTIF($F24:T24,"&lt;4")&gt;0,IF(C24="К","-"," - "),(IFERROR(AVERAGE($F24:T24),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V24" s="22" t="n"/>
+      <c r="W24" s="39" t="n"/>
     </row>
     <row r="25" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A25" s="40" t="n"/>
@@ -2504,16 +2562,16 @@
         </is>
       </c>
       <c r="F25" s="49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G25" s="49" t="n">
         <v>10</v>
       </c>
       <c r="H25" s="49" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I25" s="49" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J25" s="49" t="n">
         <v>9</v>
@@ -2522,35 +2580,38 @@
         <v>9</v>
       </c>
       <c r="L25" s="49" t="n">
+        <v>9</v>
+      </c>
+      <c r="M25" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="M25" s="49" t="n">
+      <c r="N25" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="N25" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="O25" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="P25" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="P25" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="Q25" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="R25" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="R25" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="S25" s="49" t="n">
         <v>8</v>
       </c>
-      <c r="T25" s="42">
-        <f>IF(COUNTIF($F25:S25,"=*")&gt;0,IF($C25="К","-"," - "),IF(COUNTIF($F25:S25,"&lt;4")&gt;0,IF(C25="К","-"," - "),(IFERROR(AVERAGE($F25:S25),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U25" s="22" t="n"/>
-      <c r="V25" s="39" t="n"/>
+      <c r="T25" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="U25" s="42">
+        <f>IF(COUNTIF($F25:T25,"=*")&gt;0,IF($C25="К","-"," - "),IF(COUNTIF($F25:T25,"&lt;4")&gt;0,IF(C25="К","-"," - "),(IFERROR(AVERAGE($F25:T25),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V25" s="22" t="n"/>
+      <c r="W25" s="39" t="n"/>
     </row>
     <row r="26" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A26" s="40" t="n"/>
@@ -2569,55 +2630,58 @@
         </is>
       </c>
       <c r="F26" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="G26" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="G26" s="49" t="inlineStr">
+      <c r="H26" s="49" t="inlineStr">
         <is>
           <t>н/а</t>
         </is>
       </c>
-      <c r="H26" s="49" t="n">
+      <c r="I26" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="I26" s="49" t="n">
+      <c r="J26" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="J26" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="K26" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="L26" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="L26" s="49" t="n">
+      <c r="M26" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="M26" s="49" t="n">
+      <c r="N26" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="N26" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="O26" s="49" t="n">
         <v>8</v>
       </c>
       <c r="P26" s="49" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q26" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="R26" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="R26" s="49" t="n">
+      <c r="S26" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="S26" s="49" t="n">
+      <c r="T26" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="T26" s="42">
-        <f>IF(COUNTIF($F26:S26,"=*")&gt;0,IF($C26="К","-"," - "),IF(COUNTIF($F26:S26,"&lt;4")&gt;0,IF(C26="К","-"," - "),(IFERROR(AVERAGE($F26:S26),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U26" s="22" t="n"/>
-      <c r="V26" s="39" t="n"/>
+      <c r="U26" s="42">
+        <f>IF(COUNTIF($F26:T26,"=*")&gt;0,IF($C26="К","-"," - "),IF(COUNTIF($F26:T26,"&lt;4")&gt;0,IF(C26="К","-"," - "),(IFERROR(AVERAGE($F26:T26),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V26" s="22" t="n"/>
+      <c r="W26" s="39" t="n"/>
     </row>
     <row r="27" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A27" s="40" t="n"/>
@@ -2639,52 +2703,55 @@
         <v>9</v>
       </c>
       <c r="G27" s="49" t="n">
+        <v>9</v>
+      </c>
+      <c r="H27" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="H27" s="49" t="n">
+      <c r="I27" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="I27" s="49" t="inlineStr">
+      <c r="J27" s="49" t="inlineStr">
         <is>
           <t>н/а</t>
         </is>
       </c>
-      <c r="J27" s="49" t="n">
+      <c r="K27" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="K27" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="L27" s="49" t="n">
         <v>8</v>
       </c>
       <c r="M27" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="N27" s="49" t="n">
         <v>5</v>
-      </c>
-      <c r="N27" s="49" t="n">
-        <v>7</v>
       </c>
       <c r="O27" s="49" t="n">
         <v>7</v>
       </c>
       <c r="P27" s="49" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q27" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="Q27" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="R27" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="S27" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="S27" s="49" t="n">
-        <v>8</v>
-      </c>
-      <c r="T27" s="42">
-        <f>IF(COUNTIF($F27:S27,"=*")&gt;0,IF($C27="К","-"," - "),IF(COUNTIF($F27:S27,"&lt;4")&gt;0,IF(C27="К","-"," - "),(IFERROR(AVERAGE($F27:S27),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U27" s="22" t="n"/>
-      <c r="V27" s="39" t="n"/>
+      <c r="T27" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="U27" s="42">
+        <f>IF(COUNTIF($F27:T27,"=*")&gt;0,IF($C27="К","-"," - "),IF(COUNTIF($F27:T27,"&lt;4")&gt;0,IF(C27="К","-"," - "),(IFERROR(AVERAGE($F27:T27),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V27" s="22" t="n"/>
+      <c r="W27" s="39" t="n"/>
     </row>
     <row r="28" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A28" s="40" t="n"/>
@@ -2752,12 +2819,16 @@
         <f>IF(SUM(S$10:S27)=0,IF(COUNTA(S$10:S27)=0,"Очікую",0),SUM(S$10:S27)/$D27)</f>
         <v/>
       </c>
-      <c r="T28" s="9">
-        <f>IFERROR(AVERAGE($F28:S28),"Очікую")</f>
-        <v/>
-      </c>
-      <c r="U28" s="20" t="n"/>
-      <c r="V28" s="39" t="n"/>
+      <c r="T28" s="8">
+        <f>IF(SUM(T$10:T27)=0,IF(COUNTA(T$10:T27)=0,"Очікую",0),SUM(T$10:T27)/$D27)</f>
+        <v/>
+      </c>
+      <c r="U28" s="9">
+        <f>IFERROR(AVERAGE($F28:T28),"Очікую")</f>
+        <v/>
+      </c>
+      <c r="V28" s="20" t="n"/>
+      <c r="W28" s="39" t="n"/>
     </row>
     <row r="29" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A29" s="40" t="n"/>
@@ -2825,9 +2896,13 @@
         <f>IF(SUM(S$10:S27)=0,IF(COUNTA(S$10:S27)=0,"Очікую",0),IF(COUNTIF(S$10:S27,"&gt;=4")=0,0,COUNTIF(S$10:S27,"&gt;=4")/$D27*100))</f>
         <v/>
       </c>
-      <c r="T29" s="6" t="n"/>
-      <c r="U29" s="20" t="n"/>
-      <c r="V29" s="39" t="n"/>
+      <c r="T29" s="43">
+        <f>IF(SUM(T$10:T27)=0,IF(COUNTA(T$10:T27)=0,"Очікую",0),IF(COUNTIF(T$10:T27,"&gt;=4")=0,0,COUNTIF(T$10:T27,"&gt;=4")/$D27*100))</f>
+        <v/>
+      </c>
+      <c r="U29" s="6" t="n"/>
+      <c r="V29" s="20" t="n"/>
+      <c r="W29" s="39" t="n"/>
     </row>
     <row r="30" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A30" s="40" t="n"/>
@@ -2895,9 +2970,13 @@
         <f>IF(SUM(S$10:S27)=0,IF(COUNTA(S$10:S27)=0,"Очікую",0),IF(COUNTIF(S$10:S27,"&gt;=7")=0,0,COUNTIF(S$10:S27,"&gt;=7")/$D27*100))</f>
         <v/>
       </c>
-      <c r="T30" s="6" t="n"/>
-      <c r="U30" s="20" t="n"/>
-      <c r="V30" s="39" t="n"/>
+      <c r="T30" s="43">
+        <f>IF(SUM(T$10:T27)=0,IF(COUNTA(T$10:T27)=0,"Очікую",0),IF(COUNTIF(T$10:T27,"&gt;=7")=0,0,COUNTIF(T$10:T27,"&gt;=7")/$D27*100))</f>
+        <v/>
+      </c>
+      <c r="U30" s="6" t="n"/>
+      <c r="V30" s="20" t="n"/>
+      <c r="W30" s="39" t="n"/>
     </row>
     <row r="31" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A31" s="40" t="n"/>
@@ -2910,7 +2989,7 @@
         </is>
       </c>
       <c r="F31" s="8">
-        <f>IFERROR(AVERAGE(F29:S29),"Очікую")</f>
+        <f>IFERROR(AVERAGE(F29:T29),"Очікую")</f>
         <v/>
       </c>
       <c r="G31" s="6" t="n"/>
@@ -2927,8 +3006,9 @@
       <c r="R31" s="6" t="n"/>
       <c r="S31" s="6" t="n"/>
       <c r="T31" s="6" t="n"/>
-      <c r="U31" s="20" t="n"/>
-      <c r="V31" s="39" t="n"/>
+      <c r="U31" s="6" t="n"/>
+      <c r="V31" s="20" t="n"/>
+      <c r="W31" s="39" t="n"/>
     </row>
     <row r="32" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A32" s="40" t="n"/>
@@ -2941,7 +3021,7 @@
         </is>
       </c>
       <c r="F32" s="8">
-        <f>IFERROR(AVERAGE($F30:S30),"Очікую")</f>
+        <f>IFERROR(AVERAGE($F30:T30),"Очікую")</f>
         <v/>
       </c>
       <c r="G32" s="6" t="n"/>
@@ -2958,8 +3038,9 @@
       <c r="R32" s="6" t="n"/>
       <c r="S32" s="6" t="n"/>
       <c r="T32" s="6" t="n"/>
-      <c r="U32" s="20" t="n"/>
-      <c r="V32" s="39" t="n"/>
+      <c r="U32" s="6" t="n"/>
+      <c r="V32" s="20" t="n"/>
+      <c r="W32" s="39" t="n"/>
     </row>
     <row r="33" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A33" s="40" t="n"/>
@@ -2985,12 +3066,13 @@
       <c r="N33" s="6" t="n"/>
       <c r="O33" s="6" t="n"/>
       <c r="P33" s="6" t="n"/>
-      <c r="Q33" s="52" t="n"/>
+      <c r="Q33" s="6" t="n"/>
       <c r="R33" s="52" t="n"/>
       <c r="S33" s="52" t="n"/>
       <c r="T33" s="52" t="n"/>
-      <c r="U33" s="20" t="n"/>
-      <c r="V33" s="39" t="n"/>
+      <c r="U33" s="52" t="n"/>
+      <c r="V33" s="20" t="n"/>
+      <c r="W33" s="39" t="n"/>
     </row>
     <row r="34" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A34" s="40" t="n"/>
@@ -3015,11 +3097,11 @@
       <c r="I34" s="55" t="n"/>
       <c r="J34" s="55" t="n"/>
       <c r="K34" s="55" t="n"/>
-      <c r="L34" s="6" t="n"/>
+      <c r="L34" s="55" t="n"/>
       <c r="M34" s="6" t="n"/>
       <c r="N34" s="6" t="n"/>
-      <c r="O34" s="56" t="n"/>
-      <c r="P34" s="54" t="inlineStr">
+      <c r="O34" s="6" t="n"/>
+      <c r="P34" s="56" t="inlineStr">
         <is>
           <t>Ірина ДОПІРА</t>
         </is>
@@ -3028,8 +3110,9 @@
       <c r="R34" s="54" t="n"/>
       <c r="S34" s="54" t="n"/>
       <c r="T34" s="54" t="n"/>
-      <c r="U34" s="20" t="n"/>
-      <c r="V34" s="39" t="n"/>
+      <c r="U34" s="54" t="n"/>
+      <c r="V34" s="20" t="n"/>
+      <c r="W34" s="39" t="n"/>
     </row>
     <row r="35" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A35" s="40" t="n"/>
@@ -3049,17 +3132,18 @@
       <c r="I35" s="55" t="n"/>
       <c r="J35" s="55" t="n"/>
       <c r="K35" s="55" t="n"/>
-      <c r="L35" s="6" t="n"/>
+      <c r="L35" s="55" t="n"/>
       <c r="M35" s="6" t="n"/>
       <c r="N35" s="6" t="n"/>
-      <c r="O35" s="56" t="n"/>
-      <c r="P35" s="52" t="n"/>
+      <c r="O35" s="6" t="n"/>
+      <c r="P35" s="56" t="n"/>
       <c r="Q35" s="52" t="n"/>
       <c r="R35" s="52" t="n"/>
       <c r="S35" s="52" t="n"/>
       <c r="T35" s="52" t="n"/>
-      <c r="U35" s="20" t="n"/>
-      <c r="V35" s="39" t="n"/>
+      <c r="U35" s="52" t="n"/>
+      <c r="V35" s="20" t="n"/>
+      <c r="W35" s="39" t="n"/>
     </row>
     <row r="36" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A36" s="40" t="n"/>
@@ -3072,7 +3156,7 @@
         </is>
       </c>
       <c r="F36" s="63">
-        <f>IF(F33="Очікую","Очікую",IF(F33-COUNTIF($T$10:$T27," - ")&lt;ROUNDDOWN(F33*0.4,0),F33-COUNTIF($T$10:$T27," - "),ROUNDDOWN(F33*0.4,0)))</f>
+        <f>IF(F33="Очікую","Очікую",IF(F33-COUNTIF($U$10:$U27," - ")&lt;ROUNDDOWN(F33*0.4,0),F33-COUNTIF($U$10:$U27," - "),ROUNDDOWN(F33*0.4,0)))</f>
         <v/>
       </c>
       <c r="G36" s="6" t="n"/>
@@ -3084,11 +3168,11 @@
       <c r="I36" s="56" t="n"/>
       <c r="J36" s="56" t="n"/>
       <c r="K36" s="56" t="n"/>
-      <c r="L36" s="6" t="n"/>
+      <c r="L36" s="56" t="n"/>
       <c r="M36" s="6" t="n"/>
       <c r="N36" s="6" t="n"/>
-      <c r="O36" s="56" t="n"/>
-      <c r="P36" s="54" t="inlineStr">
+      <c r="O36" s="6" t="n"/>
+      <c r="P36" s="56" t="inlineStr">
         <is>
           <t>Маргарита БРІТІКОВА</t>
         </is>
@@ -3097,8 +3181,9 @@
       <c r="R36" s="54" t="n"/>
       <c r="S36" s="54" t="n"/>
       <c r="T36" s="54" t="n"/>
-      <c r="U36" s="20" t="n"/>
-      <c r="V36" s="39" t="n"/>
+      <c r="U36" s="54" t="n"/>
+      <c r="V36" s="20" t="n"/>
+      <c r="W36" s="39" t="n"/>
     </row>
     <row r="37" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A37" s="40" t="n"/>
@@ -3121,8 +3206,9 @@
       <c r="R37" s="14" t="n"/>
       <c r="S37" s="14" t="n"/>
       <c r="T37" s="14" t="n"/>
-      <c r="U37" s="15" t="n"/>
-      <c r="V37" s="39" t="n"/>
+      <c r="U37" s="14" t="n"/>
+      <c r="V37" s="15" t="n"/>
+      <c r="W37" s="39" t="n"/>
     </row>
     <row r="38" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A38" s="38" t="n"/>
@@ -3146,7 +3232,8 @@
       <c r="S38" s="38" t="n"/>
       <c r="T38" s="38" t="n"/>
       <c r="U38" s="38" t="n"/>
-      <c r="V38" s="39" t="n"/>
+      <c r="V38" s="38" t="n"/>
+      <c r="W38" s="39" t="n"/>
     </row>
     <row r="39" hidden="1" ht="15" customFormat="1" customHeight="1" s="11"/>
     <row r="40" hidden="1" ht="15" customFormat="1" customHeight="1" s="11"/>
@@ -3232,16 +3319,16 @@
     <row r="120" hidden="1" ht="12" customHeight="1"/>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="C3:T3"/>
-    <mergeCell ref="F8:S8"/>
-    <mergeCell ref="C6:T6"/>
-    <mergeCell ref="C7:T7"/>
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="E8:E9"/>
+    <mergeCell ref="C5:U5"/>
+    <mergeCell ref="U8:U9"/>
     <mergeCell ref="D8:D9"/>
-    <mergeCell ref="C5:T5"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="C4:T4"/>
+    <mergeCell ref="C3:U3"/>
+    <mergeCell ref="C7:U7"/>
+    <mergeCell ref="C4:U4"/>
+    <mergeCell ref="F8:T8"/>
+    <mergeCell ref="C6:U6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.1968503937007874" right="0.1968503937007874" top="0.1968503937007874" bottom="0.1968503937007874" header="0" footer="0"/>
@@ -3256,7 +3343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V50"/>
+  <dimension ref="A1:W50"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1"/>
   <cols>
     <col width="2.7109375" customWidth="1" style="1" min="1" max="2"/>
@@ -3264,10 +3351,9 @@
     <col width="6.5703125" customWidth="1" style="1" min="4" max="4"/>
     <col width="40.42578125" customWidth="1" style="1" min="5" max="5"/>
     <col width="6.7109375" customWidth="1" style="1" min="6" max="25"/>
-    <col width="11.3" customWidth="1" min="20" max="20"/>
-    <col width="2.7" customWidth="1" min="21" max="21"/>
+    <col width="11.3" customWidth="1" min="21" max="21"/>
     <col width="2.7" customWidth="1" min="22" max="22"/>
-    <col hidden="1" width="13" customWidth="1" min="23" max="23"/>
+    <col width="2.7" customWidth="1" min="23" max="23"/>
     <col hidden="1" width="13" customWidth="1" min="24" max="24"/>
     <col hidden="1" width="13" customWidth="1" min="25" max="25"/>
     <col hidden="1" width="11.28515625" customWidth="1" style="1" min="26" max="26"/>
@@ -3307,6 +3393,7 @@
       <c r="T1" s="38" t="n"/>
       <c r="U1" s="38" t="n"/>
       <c r="V1" s="38" t="n"/>
+      <c r="W1" s="38" t="n"/>
     </row>
     <row r="2" ht="12" customHeight="1">
       <c r="A2" s="40" t="n"/>
@@ -3329,8 +3416,9 @@
       <c r="R2" s="18" t="n"/>
       <c r="S2" s="18" t="n"/>
       <c r="T2" s="18" t="n"/>
-      <c r="U2" s="19" t="n"/>
-      <c r="V2" s="39" t="n"/>
+      <c r="U2" s="18" t="n"/>
+      <c r="V2" s="19" t="n"/>
+      <c r="W2" s="39" t="n"/>
     </row>
     <row r="3" ht="54.95" customFormat="1" customHeight="1" s="2">
       <c r="A3" s="40" t="n"/>
@@ -3359,8 +3447,9 @@
       <c r="R3" s="86" t="n"/>
       <c r="S3" s="86" t="n"/>
       <c r="T3" s="86" t="n"/>
-      <c r="U3" s="20" t="n"/>
-      <c r="V3" s="39" t="n"/>
+      <c r="U3" s="86" t="n"/>
+      <c r="V3" s="20" t="n"/>
+      <c r="W3" s="39" t="n"/>
     </row>
     <row r="4" ht="15" customFormat="1" customHeight="1" s="3">
       <c r="A4" s="40" t="n"/>
@@ -3387,8 +3476,9 @@
       <c r="R4" s="86" t="n"/>
       <c r="S4" s="86" t="n"/>
       <c r="T4" s="86" t="n"/>
-      <c r="U4" s="20" t="n"/>
-      <c r="V4" s="39" t="n"/>
+      <c r="U4" s="86" t="n"/>
+      <c r="V4" s="20" t="n"/>
+      <c r="W4" s="39" t="n"/>
     </row>
     <row r="5" ht="15" customFormat="1" customHeight="1" s="2">
       <c r="A5" s="40" t="n"/>
@@ -3415,15 +3505,16 @@
       <c r="R5" s="87" t="n"/>
       <c r="S5" s="87" t="n"/>
       <c r="T5" s="87" t="n"/>
-      <c r="U5" s="20" t="n"/>
-      <c r="V5" s="39" t="n"/>
+      <c r="U5" s="87" t="n"/>
+      <c r="V5" s="20" t="n"/>
+      <c r="W5" s="39" t="n"/>
     </row>
     <row r="6" ht="15" customFormat="1" customHeight="1" s="2">
       <c r="A6" s="40" t="n"/>
       <c r="B6" s="12" t="n"/>
       <c r="C6" s="73" t="inlineStr">
         <is>
-          <t>За І семестр 2025-2026 н.р.</t>
+          <t>За ІІ семестр 2025-2026 н.р.</t>
         </is>
       </c>
       <c r="D6" s="87" t="n"/>
@@ -3443,8 +3534,9 @@
       <c r="R6" s="87" t="n"/>
       <c r="S6" s="87" t="n"/>
       <c r="T6" s="87" t="n"/>
-      <c r="U6" s="20" t="n"/>
-      <c r="V6" s="39" t="n"/>
+      <c r="U6" s="87" t="n"/>
+      <c r="V6" s="20" t="n"/>
+      <c r="W6" s="39" t="n"/>
     </row>
     <row r="7" ht="15" customFormat="1" customHeight="1" s="2">
       <c r="A7" s="40" t="n"/>
@@ -3471,8 +3563,9 @@
       <c r="R7" s="88" t="n"/>
       <c r="S7" s="88" t="n"/>
       <c r="T7" s="88" t="n"/>
-      <c r="U7" s="20" t="n"/>
-      <c r="V7" s="39" t="n"/>
+      <c r="U7" s="88" t="n"/>
+      <c r="V7" s="20" t="n"/>
+      <c r="W7" s="39" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="40" t="n"/>
@@ -3510,14 +3603,15 @@
       <c r="P8" s="89" t="n"/>
       <c r="Q8" s="89" t="n"/>
       <c r="R8" s="89" t="n"/>
-      <c r="S8" s="90" t="n"/>
-      <c r="T8" s="91" t="inlineStr">
+      <c r="S8" s="89" t="n"/>
+      <c r="T8" s="90" t="n"/>
+      <c r="U8" s="91" t="inlineStr">
         <is>
           <t>Середній бал</t>
         </is>
       </c>
-      <c r="U8" s="20" t="n"/>
-      <c r="V8" s="39" t="n"/>
+      <c r="V8" s="20" t="n"/>
+      <c r="W8" s="39" t="n"/>
     </row>
     <row r="9" ht="125.1" customHeight="1">
       <c r="A9" s="40" t="n"/>
@@ -3527,91 +3621,97 @@
       <c r="E9" s="92" t="n"/>
       <c r="F9" s="13" t="inlineStr">
         <is>
+          <t>Астрономія
+Наговська Т.С.</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
           <t>Біологія
 Богданенко О.В.</t>
         </is>
       </c>
-      <c r="G9" s="13" t="inlineStr">
+      <c r="H9" s="13" t="inlineStr">
         <is>
           <t>Всесвітня історія
 Мельничук С.А.</t>
         </is>
       </c>
-      <c r="H9" s="13" t="inlineStr">
+      <c r="I9" s="13" t="inlineStr">
         <is>
           <t>Географія
 Наговська Т.С.</t>
         </is>
       </c>
-      <c r="I9" s="13" t="inlineStr">
+      <c r="J9" s="13" t="inlineStr">
         <is>
           <t>Зарубіжна література
 Сербулова Ю.А.</t>
         </is>
       </c>
-      <c r="J9" s="13" t="inlineStr">
+      <c r="K9" s="13" t="inlineStr">
         <is>
           <t>Захист України
 Лазар В.І.</t>
         </is>
       </c>
-      <c r="K9" s="13" t="inlineStr">
+      <c r="L9" s="13" t="inlineStr">
         <is>
           <t>Іноземна мова
 Сербулова Ю.А.</t>
         </is>
       </c>
-      <c r="L9" s="13" t="inlineStr">
+      <c r="M9" s="13" t="inlineStr">
         <is>
           <t>Інформатика
 Бєльдюгіна С.С.</t>
         </is>
       </c>
-      <c r="M9" s="13" t="inlineStr">
+      <c r="N9" s="13" t="inlineStr">
         <is>
           <t>Історія України
 Левчук Т.Г.</t>
         </is>
       </c>
-      <c r="N9" s="13" t="inlineStr">
+      <c r="O9" s="13" t="inlineStr">
         <is>
           <t>Математика
 Бондаренко О.С.</t>
         </is>
       </c>
-      <c r="O9" s="13" t="inlineStr">
+      <c r="P9" s="13" t="inlineStr">
         <is>
           <t>Українська література
 Антропова Л.І.</t>
         </is>
       </c>
-      <c r="P9" s="13" t="inlineStr">
+      <c r="Q9" s="13" t="inlineStr">
         <is>
           <t>Українська мова
 Антропова Л.І.</t>
         </is>
       </c>
-      <c r="Q9" s="13" t="inlineStr">
+      <c r="R9" s="13" t="inlineStr">
         <is>
           <t>Фізика
 Калюта Н.М.</t>
         </is>
       </c>
-      <c r="R9" s="13" t="inlineStr">
+      <c r="S9" s="13" t="inlineStr">
         <is>
           <t>Фізична культура
 Возіян О.Г.</t>
         </is>
       </c>
-      <c r="S9" s="13" t="inlineStr">
+      <c r="T9" s="13" t="inlineStr">
         <is>
           <t>Хімія
 Сахно Н.О.</t>
         </is>
       </c>
-      <c r="T9" s="92" t="n"/>
-      <c r="U9" s="20" t="n"/>
-      <c r="V9" s="39" t="n"/>
+      <c r="U9" s="92" t="n"/>
+      <c r="V9" s="20" t="n"/>
+      <c r="W9" s="39" t="n"/>
     </row>
     <row r="10" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A10" s="40" t="n"/>
@@ -3630,53 +3730,56 @@
         </is>
       </c>
       <c r="F10" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="G10" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="G10" s="49" t="n">
+      <c r="H10" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="H10" s="49" t="n">
-        <v>6</v>
-      </c>
       <c r="I10" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="J10" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="J10" s="49" t="n">
+      <c r="K10" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="K10" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="L10" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="M10" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="M10" s="49" t="n">
-        <v>6</v>
-      </c>
       <c r="N10" s="49" t="n">
         <v>6</v>
       </c>
       <c r="O10" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="P10" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="P10" s="49" t="n">
+      <c r="Q10" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="Q10" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="R10" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="S10" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="S10" s="49" t="n">
+      <c r="T10" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="T10" s="42">
-        <f>IF(COUNTIF($F10:S10,"=*")&gt;0,IF($C10="К","-"," - "),IF(COUNTIF($F10:S10,"&lt;4")&gt;0,IF(C10="К","-"," - "),(IFERROR(AVERAGE($F10:S10),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U10" s="22" t="n"/>
-      <c r="V10" s="39" t="n"/>
+      <c r="U10" s="42">
+        <f>IF(COUNTIF($F10:T10,"=*")&gt;0,IF($C10="К","-"," - "),IF(COUNTIF($F10:T10,"&lt;4")&gt;0,IF(C10="К","-"," - "),(IFERROR(AVERAGE($F10:T10),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V10" s="22" t="n"/>
+      <c r="W10" s="39" t="n"/>
     </row>
     <row r="11" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A11" s="40" t="n"/>
@@ -3695,53 +3798,56 @@
         </is>
       </c>
       <c r="F11" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="G11" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="H11" s="49" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I11" s="49" t="n">
         <v>6</v>
       </c>
       <c r="J11" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="K11" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="K11" s="49" t="n">
-        <v>6</v>
-      </c>
       <c r="L11" s="49" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M11" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="N11" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="N11" s="49" t="n">
+      <c r="O11" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="O11" s="49" t="n">
+      <c r="P11" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="P11" s="49" t="n">
+      <c r="Q11" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="Q11" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="R11" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="S11" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="S11" s="49" t="n">
+      <c r="T11" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="T11" s="42">
-        <f>IF(COUNTIF($F11:S11,"=*")&gt;0,IF($C11="К","-"," - "),IF(COUNTIF($F11:S11,"&lt;4")&gt;0,IF(C11="К","-"," - "),(IFERROR(AVERAGE($F11:S11),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U11" s="22" t="n"/>
-      <c r="V11" s="39" t="n"/>
+      <c r="U11" s="42">
+        <f>IF(COUNTIF($F11:T11,"=*")&gt;0,IF($C11="К","-"," - "),IF(COUNTIF($F11:T11,"&lt;4")&gt;0,IF(C11="К","-"," - "),(IFERROR(AVERAGE($F11:T11),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V11" s="22" t="n"/>
+      <c r="W11" s="39" t="n"/>
     </row>
     <row r="12" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A12" s="40" t="n"/>
@@ -3760,57 +3866,60 @@
         </is>
       </c>
       <c r="F12" s="49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G12" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="H12" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="H12" s="49" t="n">
-        <v>8</v>
-      </c>
-      <c r="I12" s="49" t="inlineStr">
+      <c r="I12" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="J12" s="49" t="inlineStr">
         <is>
           <t>н/а</t>
         </is>
       </c>
-      <c r="J12" s="49" t="inlineStr">
+      <c r="K12" s="49" t="inlineStr">
         <is>
           <t>н/а</t>
         </is>
       </c>
-      <c r="K12" s="49" t="n">
-        <v>6</v>
-      </c>
       <c r="L12" s="49" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M12" s="49" t="n">
         <v>7</v>
       </c>
       <c r="N12" s="49" t="n">
+        <v>7</v>
+      </c>
+      <c r="O12" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="O12" s="49" t="n">
+      <c r="P12" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="P12" s="49" t="n">
+      <c r="Q12" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="Q12" s="49" t="n">
-        <v>6</v>
-      </c>
       <c r="R12" s="49" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S12" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="T12" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="T12" s="42">
-        <f>IF(COUNTIF($F12:S12,"=*")&gt;0,IF($C12="К","-"," - "),IF(COUNTIF($F12:S12,"&lt;4")&gt;0,IF(C12="К","-"," - "),(IFERROR(AVERAGE($F12:S12),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U12" s="22" t="n"/>
-      <c r="V12" s="39" t="n"/>
+      <c r="U12" s="42">
+        <f>IF(COUNTIF($F12:T12,"=*")&gt;0,IF($C12="К","-"," - "),IF(COUNTIF($F12:T12,"&lt;4")&gt;0,IF(C12="К","-"," - "),(IFERROR(AVERAGE($F12:T12),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V12" s="22" t="n"/>
+      <c r="W12" s="39" t="n"/>
     </row>
     <row r="13" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A13" s="40" t="n"/>
@@ -3829,53 +3938,56 @@
         </is>
       </c>
       <c r="F13" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="G13" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="H13" s="49" t="n">
         <v>8</v>
       </c>
       <c r="I13" s="49" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J13" s="49" t="n">
         <v>4</v>
       </c>
       <c r="K13" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="L13" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="L13" s="49" t="n">
+      <c r="M13" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="M13" s="49" t="n">
+      <c r="N13" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="N13" s="49" t="n">
+      <c r="O13" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="O13" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="P13" s="49" t="n">
         <v>8</v>
       </c>
       <c r="Q13" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="R13" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="R13" s="49" t="n">
+      <c r="S13" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="S13" s="49" t="n">
-        <v>8</v>
-      </c>
-      <c r="T13" s="42">
-        <f>IF(COUNTIF($F13:S13,"=*")&gt;0,IF($C13="К","-"," - "),IF(COUNTIF($F13:S13,"&lt;4")&gt;0,IF(C13="К","-"," - "),(IFERROR(AVERAGE($F13:S13),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U13" s="22" t="n"/>
-      <c r="V13" s="39" t="n"/>
+      <c r="T13" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="U13" s="42">
+        <f>IF(COUNTIF($F13:T13,"=*")&gt;0,IF($C13="К","-"," - "),IF(COUNTIF($F13:T13,"&lt;4")&gt;0,IF(C13="К","-"," - "),(IFERROR(AVERAGE($F13:T13),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V13" s="22" t="n"/>
+      <c r="W13" s="39" t="n"/>
     </row>
     <row r="14" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A14" s="40" t="n"/>
@@ -3894,29 +4006,29 @@
         </is>
       </c>
       <c r="F14" s="49" t="n">
+        <v>7</v>
+      </c>
+      <c r="G14" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="G14" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="H14" s="49" t="n">
         <v>8</v>
       </c>
       <c r="I14" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="J14" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="J14" s="49" t="n">
-        <v>6</v>
-      </c>
       <c r="K14" s="49" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L14" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="M14" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="M14" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="N14" s="49" t="n">
         <v>8</v>
       </c>
@@ -3924,23 +4036,26 @@
         <v>8</v>
       </c>
       <c r="P14" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="Q14" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="R14" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="S14" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="S14" s="49" t="n">
-        <v>8</v>
-      </c>
-      <c r="T14" s="42">
-        <f>IF(COUNTIF($F14:S14,"=*")&gt;0,IF($C14="К","-"," - "),IF(COUNTIF($F14:S14,"&lt;4")&gt;0,IF(C14="К","-"," - "),(IFERROR(AVERAGE($F14:S14),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U14" s="22" t="n"/>
-      <c r="V14" s="39" t="n"/>
+      <c r="T14" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="U14" s="42">
+        <f>IF(COUNTIF($F14:T14,"=*")&gt;0,IF($C14="К","-"," - "),IF(COUNTIF($F14:T14,"&lt;4")&gt;0,IF(C14="К","-"," - "),(IFERROR(AVERAGE($F14:T14),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V14" s="22" t="n"/>
+      <c r="W14" s="39" t="n"/>
     </row>
     <row r="15" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A15" s="40" t="n"/>
@@ -3958,56 +4073,59 @@
           <t>Гончар Марія Сергіївна</t>
         </is>
       </c>
-      <c r="F15" s="49" t="inlineStr">
+      <c r="F15" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="G15" s="49" t="inlineStr">
         <is>
           <t>н/а</t>
         </is>
       </c>
-      <c r="G15" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="H15" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="I15" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="I15" s="49" t="n">
-        <v>6</v>
-      </c>
       <c r="J15" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="K15" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="K15" s="49" t="n">
+      <c r="L15" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="L15" s="49" t="n">
+      <c r="M15" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="M15" s="49" t="n">
+      <c r="N15" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="N15" s="49" t="n">
+      <c r="O15" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="O15" s="49" t="n">
+      <c r="P15" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="P15" s="49" t="n">
+      <c r="Q15" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="Q15" s="49" t="n">
-        <v>6</v>
-      </c>
       <c r="R15" s="49" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S15" s="49" t="n">
         <v>8</v>
       </c>
-      <c r="T15" s="42">
-        <f>IF(COUNTIF($F15:S15,"=*")&gt;0,IF($C15="К","-"," - "),IF(COUNTIF($F15:S15,"&lt;4")&gt;0,IF(C15="К","-"," - "),(IFERROR(AVERAGE($F15:S15),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U15" s="22" t="n"/>
-      <c r="V15" s="39" t="n"/>
+      <c r="T15" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="U15" s="42">
+        <f>IF(COUNTIF($F15:T15,"=*")&gt;0,IF($C15="К","-"," - "),IF(COUNTIF($F15:T15,"&lt;4")&gt;0,IF(C15="К","-"," - "),(IFERROR(AVERAGE($F15:T15),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V15" s="22" t="n"/>
+      <c r="W15" s="39" t="n"/>
     </row>
     <row r="16" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A16" s="40" t="n"/>
@@ -4026,53 +4144,56 @@
         </is>
       </c>
       <c r="F16" s="49" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G16" s="49" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H16" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="I16" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="I16" s="49" t="n">
+      <c r="J16" s="49" t="n">
         <v>11</v>
-      </c>
-      <c r="J16" s="49" t="n">
-        <v>7</v>
       </c>
       <c r="K16" s="49" t="n">
         <v>7</v>
       </c>
       <c r="L16" s="49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M16" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="N16" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="N16" s="49" t="n">
+      <c r="O16" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="O16" s="49" t="n">
-        <v>6</v>
-      </c>
       <c r="P16" s="49" t="n">
         <v>6</v>
       </c>
       <c r="Q16" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="R16" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="R16" s="49" t="n">
-        <v>6</v>
-      </c>
       <c r="S16" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="T16" s="42">
-        <f>IF(COUNTIF($F16:S16,"=*")&gt;0,IF($C16="К","-"," - "),IF(COUNTIF($F16:S16,"&lt;4")&gt;0,IF(C16="К","-"," - "),(IFERROR(AVERAGE($F16:S16),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U16" s="22" t="n"/>
-      <c r="V16" s="39" t="n"/>
+      <c r="T16" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="U16" s="42">
+        <f>IF(COUNTIF($F16:T16,"=*")&gt;0,IF($C16="К","-"," - "),IF(COUNTIF($F16:T16,"&lt;4")&gt;0,IF(C16="К","-"," - "),(IFERROR(AVERAGE($F16:T16),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V16" s="22" t="n"/>
+      <c r="W16" s="39" t="n"/>
     </row>
     <row r="17" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A17" s="40" t="n"/>
@@ -4091,53 +4212,56 @@
         </is>
       </c>
       <c r="F17" s="49" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G17" s="49" t="n">
         <v>9</v>
       </c>
       <c r="H17" s="49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I17" s="49" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J17" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="K17" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="K17" s="49" t="n">
+      <c r="L17" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="L17" s="49" t="n">
-        <v>6</v>
-      </c>
       <c r="M17" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="N17" s="49" t="n">
         <v>11</v>
-      </c>
-      <c r="N17" s="49" t="n">
-        <v>7</v>
       </c>
       <c r="O17" s="49" t="n">
         <v>7</v>
       </c>
       <c r="P17" s="49" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q17" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="Q17" s="49" t="n">
-        <v>6</v>
-      </c>
       <c r="R17" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="S17" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="S17" s="49" t="n">
-        <v>8</v>
-      </c>
-      <c r="T17" s="42">
-        <f>IF(COUNTIF($F17:S17,"=*")&gt;0,IF($C17="К","-"," - "),IF(COUNTIF($F17:S17,"&lt;4")&gt;0,IF(C17="К","-"," - "),(IFERROR(AVERAGE($F17:S17),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U17" s="22" t="n"/>
-      <c r="V17" s="39" t="n"/>
+      <c r="T17" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="U17" s="42">
+        <f>IF(COUNTIF($F17:T17,"=*")&gt;0,IF($C17="К","-"," - "),IF(COUNTIF($F17:T17,"&lt;4")&gt;0,IF(C17="К","-"," - "),(IFERROR(AVERAGE($F17:T17),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V17" s="22" t="n"/>
+      <c r="W17" s="39" t="n"/>
     </row>
     <row r="18" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A18" s="40" t="n"/>
@@ -4156,53 +4280,56 @@
         </is>
       </c>
       <c r="F18" s="49" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G18" s="49" t="n">
         <v>4</v>
       </c>
       <c r="H18" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="I18" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="I18" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="J18" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="K18" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="K18" s="49" t="n">
+      <c r="L18" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="L18" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="M18" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="N18" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="N18" s="49" t="n">
+      <c r="O18" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="O18" s="49" t="n">
-        <v>6</v>
-      </c>
       <c r="P18" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q18" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="Q18" s="49" t="n">
+      <c r="R18" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="R18" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="S18" s="49" t="n">
         <v>8</v>
       </c>
-      <c r="T18" s="42">
-        <f>IF(COUNTIF($F18:S18,"=*")&gt;0,IF($C18="К","-"," - "),IF(COUNTIF($F18:S18,"&lt;4")&gt;0,IF(C18="К","-"," - "),(IFERROR(AVERAGE($F18:S18),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U18" s="22" t="n"/>
-      <c r="V18" s="39" t="n"/>
+      <c r="T18" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="U18" s="42">
+        <f>IF(COUNTIF($F18:T18,"=*")&gt;0,IF($C18="К","-"," - "),IF(COUNTIF($F18:T18,"&lt;4")&gt;0,IF(C18="К","-"," - "),(IFERROR(AVERAGE($F18:T18),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V18" s="22" t="n"/>
+      <c r="W18" s="39" t="n"/>
     </row>
     <row r="19" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A19" s="40" t="n"/>
@@ -4221,53 +4348,56 @@
         </is>
       </c>
       <c r="F19" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="G19" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="G19" s="49" t="n">
+      <c r="H19" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="H19" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="I19" s="49" t="n">
         <v>8</v>
       </c>
       <c r="J19" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="K19" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="K19" s="49" t="n">
-        <v>6</v>
-      </c>
       <c r="L19" s="49" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M19" s="49" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N19" s="49" t="n">
         <v>6</v>
       </c>
       <c r="O19" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="P19" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="P19" s="49" t="n">
-        <v>6</v>
-      </c>
       <c r="Q19" s="49" t="n">
         <v>6</v>
       </c>
       <c r="R19" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="S19" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="S19" s="49" t="n">
+      <c r="T19" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="T19" s="42">
-        <f>IF(COUNTIF($F19:S19,"=*")&gt;0,IF($C19="К","-"," - "),IF(COUNTIF($F19:S19,"&lt;4")&gt;0,IF(C19="К","-"," - "),(IFERROR(AVERAGE($F19:S19),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U19" s="22" t="n"/>
-      <c r="V19" s="39" t="n"/>
+      <c r="U19" s="42">
+        <f>IF(COUNTIF($F19:T19,"=*")&gt;0,IF($C19="К","-"," - "),IF(COUNTIF($F19:T19,"&lt;4")&gt;0,IF(C19="К","-"," - "),(IFERROR(AVERAGE($F19:T19),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V19" s="22" t="n"/>
+      <c r="W19" s="39" t="n"/>
     </row>
     <row r="20" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A20" s="40" t="n"/>
@@ -4286,53 +4416,56 @@
         </is>
       </c>
       <c r="F20" s="49" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G20" s="49" t="n">
         <v>9</v>
       </c>
       <c r="H20" s="49" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I20" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="J20" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="J20" s="49" t="n">
+      <c r="K20" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="K20" s="49" t="n">
-        <v>6</v>
-      </c>
       <c r="L20" s="49" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M20" s="49" t="n">
         <v>7</v>
       </c>
       <c r="N20" s="49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O20" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="P20" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="P20" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="Q20" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="R20" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="R20" s="49" t="n">
-        <v>6</v>
-      </c>
       <c r="S20" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="T20" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="T20" s="42">
-        <f>IF(COUNTIF($F20:S20,"=*")&gt;0,IF($C20="К","-"," - "),IF(COUNTIF($F20:S20,"&lt;4")&gt;0,IF(C20="К","-"," - "),(IFERROR(AVERAGE($F20:S20),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U20" s="22" t="n"/>
-      <c r="V20" s="39" t="n"/>
+      <c r="U20" s="42">
+        <f>IF(COUNTIF($F20:T20,"=*")&gt;0,IF($C20="К","-"," - "),IF(COUNTIF($F20:T20,"&lt;4")&gt;0,IF(C20="К","-"," - "),(IFERROR(AVERAGE($F20:T20),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V20" s="22" t="n"/>
+      <c r="W20" s="39" t="n"/>
     </row>
     <row r="21" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A21" s="40" t="n"/>
@@ -4351,55 +4484,58 @@
         </is>
       </c>
       <c r="F21" s="49" t="n">
+        <v>5</v>
+      </c>
+      <c r="G21" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="G21" s="49" t="n">
-        <v>6</v>
-      </c>
       <c r="H21" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="I21" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="I21" s="49" t="inlineStr">
+      <c r="J21" s="49" t="inlineStr">
         <is>
           <t>н/а</t>
         </is>
       </c>
-      <c r="J21" s="49" t="n">
+      <c r="K21" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="K21" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="L21" s="49" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M21" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="N21" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="N21" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="O21" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="P21" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="P21" s="49" t="n">
+      <c r="Q21" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="Q21" s="49" t="n">
+      <c r="R21" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="R21" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="S21" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="T21" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="T21" s="42">
-        <f>IF(COUNTIF($F21:S21,"=*")&gt;0,IF($C21="К","-"," - "),IF(COUNTIF($F21:S21,"&lt;4")&gt;0,IF(C21="К","-"," - "),(IFERROR(AVERAGE($F21:S21),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U21" s="22" t="n"/>
-      <c r="V21" s="39" t="n"/>
+      <c r="U21" s="42">
+        <f>IF(COUNTIF($F21:T21,"=*")&gt;0,IF($C21="К","-"," - "),IF(COUNTIF($F21:T21,"&lt;4")&gt;0,IF(C21="К","-"," - "),(IFERROR(AVERAGE($F21:T21),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V21" s="22" t="n"/>
+      <c r="W21" s="39" t="n"/>
     </row>
     <row r="22" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A22" s="40" t="n"/>
@@ -4418,53 +4554,56 @@
         </is>
       </c>
       <c r="F22" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="G22" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="G22" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="H22" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="I22" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="I22" s="49" t="n">
+      <c r="J22" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="J22" s="49" t="n">
+      <c r="K22" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="K22" s="49" t="n">
+      <c r="L22" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="L22" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="M22" s="49" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N22" s="49" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O22" s="49" t="n">
         <v>8</v>
       </c>
       <c r="P22" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q22" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="Q22" s="49" t="n">
+      <c r="R22" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="R22" s="49" t="n">
+      <c r="S22" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="S22" s="49" t="n">
-        <v>8</v>
-      </c>
-      <c r="T22" s="42">
-        <f>IF(COUNTIF($F22:S22,"=*")&gt;0,IF($C22="К","-"," - "),IF(COUNTIF($F22:S22,"&lt;4")&gt;0,IF(C22="К","-"," - "),(IFERROR(AVERAGE($F22:S22),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U22" s="22" t="n"/>
-      <c r="V22" s="39" t="n"/>
+      <c r="T22" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="U22" s="42">
+        <f>IF(COUNTIF($F22:T22,"=*")&gt;0,IF($C22="К","-"," - "),IF(COUNTIF($F22:T22,"&lt;4")&gt;0,IF(C22="К","-"," - "),(IFERROR(AVERAGE($F22:T22),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V22" s="22" t="n"/>
+      <c r="W22" s="39" t="n"/>
     </row>
     <row r="23" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A23" s="40" t="n"/>
@@ -4483,55 +4622,58 @@
         </is>
       </c>
       <c r="F23" s="49" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G23" s="49" t="n">
         <v>8</v>
       </c>
       <c r="H23" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="I23" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="I23" s="49" t="n">
-        <v>6</v>
-      </c>
       <c r="J23" s="49" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K23" s="49" t="n">
         <v>10</v>
       </c>
       <c r="L23" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="M23" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="M23" s="49" t="inlineStr">
+      <c r="N23" s="49" t="inlineStr">
         <is>
           <t>н/а</t>
         </is>
-      </c>
-      <c r="N23" s="49" t="n">
-        <v>11</v>
       </c>
       <c r="O23" s="49" t="n">
         <v>11</v>
       </c>
       <c r="P23" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q23" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="Q23" s="49" t="n">
+      <c r="R23" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="R23" s="49" t="n">
+      <c r="S23" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="S23" s="49" t="n">
-        <v>6</v>
-      </c>
-      <c r="T23" s="42">
-        <f>IF(COUNTIF($F23:S23,"=*")&gt;0,IF($C23="К","-"," - "),IF(COUNTIF($F23:S23,"&lt;4")&gt;0,IF(C23="К","-"," - "),(IFERROR(AVERAGE($F23:S23),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U23" s="22" t="n"/>
-      <c r="V23" s="39" t="n"/>
+      <c r="T23" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="U23" s="42">
+        <f>IF(COUNTIF($F23:T23,"=*")&gt;0,IF($C23="К","-"," - "),IF(COUNTIF($F23:T23,"&lt;4")&gt;0,IF(C23="К","-"," - "),(IFERROR(AVERAGE($F23:T23),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V23" s="22" t="n"/>
+      <c r="W23" s="39" t="n"/>
     </row>
     <row r="24" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A24" s="40" t="n"/>
@@ -4553,50 +4695,53 @@
         <v>8</v>
       </c>
       <c r="G24" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="H24" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="H24" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="I24" s="49" t="n">
         <v>8</v>
       </c>
       <c r="J24" s="49" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K24" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="L24" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="L24" s="49" t="n">
-        <v>6</v>
-      </c>
       <c r="M24" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="N24" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="N24" s="49" t="n">
-        <v>6</v>
-      </c>
       <c r="O24" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="P24" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="P24" s="49" t="n">
+      <c r="Q24" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="Q24" s="49" t="n">
+      <c r="R24" s="49" t="n">
         <v>4</v>
-      </c>
-      <c r="R24" s="49" t="n">
-        <v>5</v>
       </c>
       <c r="S24" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="T24" s="42">
-        <f>IF(COUNTIF($F24:S24,"=*")&gt;0,IF($C24="К","-"," - "),IF(COUNTIF($F24:S24,"&lt;4")&gt;0,IF(C24="К","-"," - "),(IFERROR(AVERAGE($F24:S24),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U24" s="22" t="n"/>
-      <c r="V24" s="39" t="n"/>
+      <c r="T24" s="49" t="n">
+        <v>5</v>
+      </c>
+      <c r="U24" s="42">
+        <f>IF(COUNTIF($F24:T24,"=*")&gt;0,IF($C24="К","-"," - "),IF(COUNTIF($F24:T24,"&lt;4")&gt;0,IF(C24="К","-"," - "),(IFERROR(AVERAGE($F24:T24),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V24" s="22" t="n"/>
+      <c r="W24" s="39" t="n"/>
     </row>
     <row r="25" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A25" s="40" t="n"/>
@@ -4615,37 +4760,37 @@
         </is>
       </c>
       <c r="F25" s="49" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G25" s="49" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H25" s="49" t="n">
         <v>9</v>
       </c>
       <c r="I25" s="49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J25" s="49" t="n">
         <v>8</v>
       </c>
       <c r="K25" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="L25" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="L25" s="49" t="n">
+      <c r="M25" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="M25" s="49" t="n">
+      <c r="N25" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="N25" s="49" t="n">
+      <c r="O25" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="O25" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="P25" s="49" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q25" s="49" t="n">
         <v>5</v>
@@ -4654,14 +4799,17 @@
         <v>5</v>
       </c>
       <c r="S25" s="49" t="n">
-        <v>6</v>
-      </c>
-      <c r="T25" s="42">
-        <f>IF(COUNTIF($F25:S25,"=*")&gt;0,IF($C25="К","-"," - "),IF(COUNTIF($F25:S25,"&lt;4")&gt;0,IF(C25="К","-"," - "),(IFERROR(AVERAGE($F25:S25),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U25" s="22" t="n"/>
-      <c r="V25" s="39" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="T25" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="U25" s="42">
+        <f>IF(COUNTIF($F25:T25,"=*")&gt;0,IF($C25="К","-"," - "),IF(COUNTIF($F25:T25,"&lt;4")&gt;0,IF(C25="К","-"," - "),(IFERROR(AVERAGE($F25:T25),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V25" s="22" t="n"/>
+      <c r="W25" s="39" t="n"/>
     </row>
     <row r="26" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A26" s="40" t="n"/>
@@ -4680,53 +4828,56 @@
         </is>
       </c>
       <c r="F26" s="49" t="n">
+        <v>5</v>
+      </c>
+      <c r="G26" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="G26" s="49" t="n">
+      <c r="H26" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="H26" s="49" t="n">
+      <c r="I26" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="I26" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="J26" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="K26" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="K26" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="L26" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="M26" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="M26" s="49" t="n">
-        <v>6</v>
-      </c>
       <c r="N26" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="O26" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="O26" s="49" t="n">
-        <v>6</v>
-      </c>
       <c r="P26" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q26" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="Q26" s="49" t="n">
+      <c r="R26" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="R26" s="49" t="n">
+      <c r="S26" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="S26" s="49" t="n">
+      <c r="T26" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="T26" s="42">
-        <f>IF(COUNTIF($F26:S26,"=*")&gt;0,IF($C26="К","-"," - "),IF(COUNTIF($F26:S26,"&lt;4")&gt;0,IF(C26="К","-"," - "),(IFERROR(AVERAGE($F26:S26),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U26" s="22" t="n"/>
-      <c r="V26" s="39" t="n"/>
+      <c r="U26" s="42">
+        <f>IF(COUNTIF($F26:T26,"=*")&gt;0,IF($C26="К","-"," - "),IF(COUNTIF($F26:T26,"&lt;4")&gt;0,IF(C26="К","-"," - "),(IFERROR(AVERAGE($F26:T26),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V26" s="22" t="n"/>
+      <c r="W26" s="39" t="n"/>
     </row>
     <row r="27" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A27" s="40" t="n"/>
@@ -4745,53 +4896,56 @@
         </is>
       </c>
       <c r="F27" s="49" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G27" s="49" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H27" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="I27" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="I27" s="49" t="n">
+      <c r="J27" s="49" t="n">
         <v>11</v>
-      </c>
-      <c r="J27" s="49" t="n">
-        <v>4</v>
       </c>
       <c r="K27" s="49" t="n">
         <v>4</v>
       </c>
       <c r="L27" s="49" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M27" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="N27" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="N27" s="49" t="n">
+      <c r="O27" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="O27" s="49" t="n">
+      <c r="P27" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="P27" s="49" t="n">
+      <c r="Q27" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="Q27" s="49" t="n">
+      <c r="R27" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="R27" s="49" t="n">
+      <c r="S27" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="S27" s="49" t="n">
+      <c r="T27" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="T27" s="42">
-        <f>IF(COUNTIF($F27:S27,"=*")&gt;0,IF($C27="К","-"," - "),IF(COUNTIF($F27:S27,"&lt;4")&gt;0,IF(C27="К","-"," - "),(IFERROR(AVERAGE($F27:S27),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U27" s="22" t="n"/>
-      <c r="V27" s="39" t="n"/>
+      <c r="U27" s="42">
+        <f>IF(COUNTIF($F27:T27,"=*")&gt;0,IF($C27="К","-"," - "),IF(COUNTIF($F27:T27,"&lt;4")&gt;0,IF(C27="К","-"," - "),(IFERROR(AVERAGE($F27:T27),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V27" s="22" t="n"/>
+      <c r="W27" s="39" t="n"/>
     </row>
     <row r="28" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A28" s="40" t="n"/>
@@ -4810,55 +4964,58 @@
         </is>
       </c>
       <c r="F28" s="49" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G28" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="H28" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="H28" s="49" t="n">
-        <v>6</v>
-      </c>
       <c r="I28" s="49" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J28" s="49" t="n">
         <v>8</v>
       </c>
       <c r="K28" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="L28" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="L28" s="49" t="n">
+      <c r="M28" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="M28" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="N28" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="O28" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="O28" s="49" t="n">
+      <c r="P28" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="P28" s="49" t="n">
+      <c r="Q28" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="Q28" s="49" t="n">
+      <c r="R28" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="R28" s="49" t="n">
+      <c r="S28" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="S28" s="49" t="inlineStr">
+      <c r="T28" s="49" t="inlineStr">
         <is>
           <t>н/а</t>
         </is>
       </c>
-      <c r="T28" s="42">
-        <f>IF(COUNTIF($F28:S28,"=*")&gt;0,IF($C28="К","-"," - "),IF(COUNTIF($F28:S28,"&lt;4")&gt;0,IF(C28="К","-"," - "),(IFERROR(AVERAGE($F28:S28),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U28" s="22" t="n"/>
-      <c r="V28" s="39" t="n"/>
+      <c r="U28" s="42">
+        <f>IF(COUNTIF($F28:T28,"=*")&gt;0,IF($C28="К","-"," - "),IF(COUNTIF($F28:T28,"&lt;4")&gt;0,IF(C28="К","-"," - "),(IFERROR(AVERAGE($F28:T28),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V28" s="22" t="n"/>
+      <c r="W28" s="39" t="n"/>
     </row>
     <row r="29" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A29" s="40" t="n"/>
@@ -4877,53 +5034,56 @@
         </is>
       </c>
       <c r="F29" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="G29" s="49" t="n">
         <v>7</v>
-      </c>
-      <c r="G29" s="49" t="n">
-        <v>10</v>
       </c>
       <c r="H29" s="49" t="n">
         <v>10</v>
       </c>
       <c r="I29" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="J29" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="J29" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="K29" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="L29" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="L29" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="M29" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="N29" s="49" t="n">
         <v>5</v>
-      </c>
-      <c r="N29" s="49" t="n">
-        <v>10</v>
       </c>
       <c r="O29" s="49" t="n">
         <v>10</v>
       </c>
       <c r="P29" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q29" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="Q29" s="49" t="n">
-        <v>6</v>
-      </c>
       <c r="R29" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="S29" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="S29" s="49" t="n">
-        <v>6</v>
-      </c>
-      <c r="T29" s="42">
-        <f>IF(COUNTIF($F29:S29,"=*")&gt;0,IF($C29="К","-"," - "),IF(COUNTIF($F29:S29,"&lt;4")&gt;0,IF(C29="К","-"," - "),(IFERROR(AVERAGE($F29:S29),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U29" s="22" t="n"/>
-      <c r="V29" s="39" t="n"/>
+      <c r="T29" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="U29" s="42">
+        <f>IF(COUNTIF($F29:T29,"=*")&gt;0,IF($C29="К","-"," - "),IF(COUNTIF($F29:T29,"&lt;4")&gt;0,IF(C29="К","-"," - "),(IFERROR(AVERAGE($F29:T29),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V29" s="22" t="n"/>
+      <c r="W29" s="39" t="n"/>
     </row>
     <row r="30" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A30" s="40" t="n"/>
@@ -4945,50 +5105,53 @@
         <v>8</v>
       </c>
       <c r="G30" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="H30" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="H30" s="49" t="n">
+      <c r="I30" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="I30" s="49" t="n">
+      <c r="J30" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="J30" s="49" t="n">
+      <c r="K30" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="K30" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="L30" s="49" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M30" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="N30" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="N30" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="O30" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="P30" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="P30" s="49" t="n">
+      <c r="Q30" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="Q30" s="49" t="n">
+      <c r="R30" s="49" t="n">
         <v>11</v>
-      </c>
-      <c r="R30" s="49" t="n">
-        <v>10</v>
       </c>
       <c r="S30" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="T30" s="42">
-        <f>IF(COUNTIF($F30:S30,"=*")&gt;0,IF($C30="К","-"," - "),IF(COUNTIF($F30:S30,"&lt;4")&gt;0,IF(C30="К","-"," - "),(IFERROR(AVERAGE($F30:S30),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U30" s="22" t="n"/>
-      <c r="V30" s="39" t="n"/>
+      <c r="T30" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="U30" s="42">
+        <f>IF(COUNTIF($F30:T30,"=*")&gt;0,IF($C30="К","-"," - "),IF(COUNTIF($F30:T30,"&lt;4")&gt;0,IF(C30="К","-"," - "),(IFERROR(AVERAGE($F30:T30),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V30" s="22" t="n"/>
+      <c r="W30" s="39" t="n"/>
     </row>
     <row r="31" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A31" s="40" t="n"/>
@@ -5007,59 +5170,62 @@
         </is>
       </c>
       <c r="F31" s="49" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G31" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="H31" s="49" t="inlineStr">
+      <c r="H31" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="I31" s="49" t="inlineStr">
         <is>
           <t>н/а</t>
         </is>
       </c>
-      <c r="I31" s="49" t="n">
+      <c r="J31" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="J31" s="49" t="n">
-        <v>8</v>
-      </c>
-      <c r="K31" s="49" t="inlineStr">
+      <c r="K31" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="L31" s="49" t="inlineStr">
         <is>
           <t>н/а</t>
         </is>
       </c>
-      <c r="L31" s="49" t="n">
-        <v>6</v>
-      </c>
       <c r="M31" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="N31" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="N31" s="49" t="n">
+      <c r="O31" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="O31" s="49" t="n">
-        <v>8</v>
-      </c>
-      <c r="P31" s="49" t="inlineStr">
+      <c r="P31" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q31" s="49" t="inlineStr">
         <is>
           <t>н/а</t>
         </is>
       </c>
-      <c r="Q31" s="49" t="n">
+      <c r="R31" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="R31" s="49" t="n">
+      <c r="S31" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="S31" s="49" t="n">
+      <c r="T31" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="T31" s="42">
-        <f>IF(COUNTIF($F31:S31,"=*")&gt;0,IF($C31="К","-"," - "),IF(COUNTIF($F31:S31,"&lt;4")&gt;0,IF(C31="К","-"," - "),(IFERROR(AVERAGE($F31:S31),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U31" s="22" t="n"/>
-      <c r="V31" s="39" t="n"/>
+      <c r="U31" s="42">
+        <f>IF(COUNTIF($F31:T31,"=*")&gt;0,IF($C31="К","-"," - "),IF(COUNTIF($F31:T31,"&lt;4")&gt;0,IF(C31="К","-"," - "),(IFERROR(AVERAGE($F31:T31),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V31" s="22" t="n"/>
+      <c r="W31" s="39" t="n"/>
     </row>
     <row r="32" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A32" s="40" t="n"/>
@@ -5078,53 +5244,56 @@
         </is>
       </c>
       <c r="F32" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="G32" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="G32" s="49" t="n">
+      <c r="H32" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="H32" s="49" t="n">
+      <c r="I32" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="I32" s="49" t="n">
+      <c r="J32" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="J32" s="49" t="n">
+      <c r="K32" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="K32" s="49" t="n">
+      <c r="L32" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="L32" s="49" t="n">
-        <v>6</v>
-      </c>
       <c r="M32" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="N32" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="N32" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="O32" s="49" t="n">
         <v>8</v>
       </c>
       <c r="P32" s="49" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q32" s="49" t="n">
         <v>7</v>
       </c>
       <c r="R32" s="49" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S32" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="T32" s="42">
-        <f>IF(COUNTIF($F32:S32,"=*")&gt;0,IF($C32="К","-"," - "),IF(COUNTIF($F32:S32,"&lt;4")&gt;0,IF(C32="К","-"," - "),(IFERROR(AVERAGE($F32:S32),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U32" s="22" t="n"/>
-      <c r="V32" s="39" t="n"/>
+      <c r="T32" s="49" t="n">
+        <v>9</v>
+      </c>
+      <c r="U32" s="42">
+        <f>IF(COUNTIF($F32:T32,"=*")&gt;0,IF($C32="К","-"," - "),IF(COUNTIF($F32:T32,"&lt;4")&gt;0,IF(C32="К","-"," - "),(IFERROR(AVERAGE($F32:T32),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V32" s="22" t="n"/>
+      <c r="W32" s="39" t="n"/>
     </row>
     <row r="33" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A33" s="40" t="n"/>
@@ -5143,53 +5312,56 @@
         </is>
       </c>
       <c r="F33" s="49" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G33" s="49" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H33" s="49" t="n">
         <v>9</v>
       </c>
       <c r="I33" s="49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J33" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="K33" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="K33" s="49" t="n">
+      <c r="L33" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="L33" s="49" t="n">
+      <c r="M33" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="M33" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="N33" s="49" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O33" s="49" t="n">
         <v>10</v>
       </c>
       <c r="P33" s="49" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q33" s="49" t="n">
         <v>8</v>
       </c>
       <c r="R33" s="49" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="S33" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="T33" s="42">
-        <f>IF(COUNTIF($F33:S33,"=*")&gt;0,IF($C33="К","-"," - "),IF(COUNTIF($F33:S33,"&lt;4")&gt;0,IF(C33="К","-"," - "),(IFERROR(AVERAGE($F33:S33),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U33" s="22" t="n"/>
-      <c r="V33" s="39" t="n"/>
+      <c r="T33" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="U33" s="42">
+        <f>IF(COUNTIF($F33:T33,"=*")&gt;0,IF($C33="К","-"," - "),IF(COUNTIF($F33:T33,"&lt;4")&gt;0,IF(C33="К","-"," - "),(IFERROR(AVERAGE($F33:T33),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V33" s="22" t="n"/>
+      <c r="W33" s="39" t="n"/>
     </row>
     <row r="34" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A34" s="40" t="n"/>
@@ -5207,60 +5379,63 @@
           <t>Тимченко Олексій Вікторович</t>
         </is>
       </c>
-      <c r="F34" s="49" t="inlineStr">
+      <c r="F34" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="G34" s="49" t="inlineStr">
         <is>
           <t>н/а</t>
         </is>
       </c>
-      <c r="G34" s="49" t="n">
+      <c r="H34" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="H34" s="49" t="n">
+      <c r="I34" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="I34" s="49" t="inlineStr">
+      <c r="J34" s="49" t="inlineStr">
         <is>
           <t>н/а</t>
         </is>
       </c>
-      <c r="J34" s="49" t="n">
+      <c r="K34" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="K34" s="49" t="n">
-        <v>6</v>
-      </c>
       <c r="L34" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="M34" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="M34" s="49" t="n">
+      <c r="N34" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="N34" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="O34" s="49" t="n">
         <v>8</v>
       </c>
       <c r="P34" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q34" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="Q34" s="49" t="n">
+      <c r="R34" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="R34" s="49" t="inlineStr">
+      <c r="S34" s="49" t="inlineStr">
         <is>
           <t>н/а</t>
         </is>
       </c>
-      <c r="S34" s="49" t="n">
+      <c r="T34" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="T34" s="42">
-        <f>IF(COUNTIF($F34:S34,"=*")&gt;0,IF($C34="К","-"," - "),IF(COUNTIF($F34:S34,"&lt;4")&gt;0,IF(C34="К","-"," - "),(IFERROR(AVERAGE($F34:S34),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U34" s="22" t="n"/>
-      <c r="V34" s="39" t="n"/>
+      <c r="U34" s="42">
+        <f>IF(COUNTIF($F34:T34,"=*")&gt;0,IF($C34="К","-"," - "),IF(COUNTIF($F34:T34,"&lt;4")&gt;0,IF(C34="К","-"," - "),(IFERROR(AVERAGE($F34:T34),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V34" s="22" t="n"/>
+      <c r="W34" s="39" t="n"/>
     </row>
     <row r="35" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A35" s="40" t="n"/>
@@ -5282,54 +5457,57 @@
         <v>8</v>
       </c>
       <c r="G35" s="49" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H35" s="49" t="n">
         <v>4</v>
       </c>
       <c r="I35" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="J35" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="J35" s="49" t="n">
-        <v>6</v>
-      </c>
       <c r="K35" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="L35" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="L35" s="49" t="inlineStr">
+      <c r="M35" s="49" t="inlineStr">
         <is>
           <t>н/а</t>
         </is>
       </c>
-      <c r="M35" s="49" t="n">
+      <c r="N35" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="N35" s="49" t="n">
-        <v>6</v>
-      </c>
       <c r="O35" s="49" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="P35" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="Q35" s="49" t="inlineStr">
+      <c r="Q35" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="R35" s="49" t="inlineStr">
         <is>
           <t>н/а</t>
         </is>
       </c>
-      <c r="R35" s="49" t="n">
+      <c r="S35" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="S35" s="49" t="n">
-        <v>8</v>
-      </c>
-      <c r="T35" s="42">
-        <f>IF(COUNTIF($F35:S35,"=*")&gt;0,IF($C35="К","-"," - "),IF(COUNTIF($F35:S35,"&lt;4")&gt;0,IF(C35="К","-"," - "),(IFERROR(AVERAGE($F35:S35),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U35" s="22" t="n"/>
-      <c r="V35" s="39" t="n"/>
+      <c r="T35" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="U35" s="42">
+        <f>IF(COUNTIF($F35:T35,"=*")&gt;0,IF($C35="К","-"," - "),IF(COUNTIF($F35:T35,"&lt;4")&gt;0,IF(C35="К","-"," - "),(IFERROR(AVERAGE($F35:T35),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V35" s="22" t="n"/>
+      <c r="W35" s="39" t="n"/>
     </row>
     <row r="36" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A36" s="40" t="n"/>
@@ -5351,50 +5529,53 @@
         <v>8</v>
       </c>
       <c r="G36" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="H36" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="H36" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="I36" s="49" t="n">
         <v>8</v>
       </c>
       <c r="J36" s="49" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K36" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="L36" s="49" t="n">
         <v>4</v>
-      </c>
-      <c r="L36" s="49" t="n">
-        <v>5</v>
       </c>
       <c r="M36" s="49" t="n">
         <v>5</v>
       </c>
       <c r="N36" s="49" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O36" s="49" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P36" s="49" t="n">
         <v>6</v>
       </c>
       <c r="Q36" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="R36" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="R36" s="49" t="n">
+      <c r="S36" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="S36" s="49" t="n">
+      <c r="T36" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="T36" s="42">
-        <f>IF(COUNTIF($F36:S36,"=*")&gt;0,IF($C36="К","-"," - "),IF(COUNTIF($F36:S36,"&lt;4")&gt;0,IF(C36="К","-"," - "),(IFERROR(AVERAGE($F36:S36),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U36" s="22" t="n"/>
-      <c r="V36" s="39" t="n"/>
+      <c r="U36" s="42">
+        <f>IF(COUNTIF($F36:T36,"=*")&gt;0,IF($C36="К","-"," - "),IF(COUNTIF($F36:T36,"&lt;4")&gt;0,IF(C36="К","-"," - "),(IFERROR(AVERAGE($F36:T36),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V36" s="22" t="n"/>
+      <c r="W36" s="39" t="n"/>
     </row>
     <row r="37" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A37" s="40" t="n"/>
@@ -5416,50 +5597,53 @@
         <v>9</v>
       </c>
       <c r="G37" s="49" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H37" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="I37" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="I37" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="J37" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="K37" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="K37" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="L37" s="49" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M37" s="49" t="n">
         <v>5</v>
       </c>
       <c r="N37" s="49" t="n">
+        <v>5</v>
+      </c>
+      <c r="O37" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="O37" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="P37" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q37" s="49" t="n">
         <v>10</v>
-      </c>
-      <c r="Q37" s="49" t="n">
-        <v>7</v>
       </c>
       <c r="R37" s="49" t="n">
         <v>7</v>
       </c>
       <c r="S37" s="49" t="n">
+        <v>7</v>
+      </c>
+      <c r="T37" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="T37" s="42">
-        <f>IF(COUNTIF($F37:S37,"=*")&gt;0,IF($C37="К","-"," - "),IF(COUNTIF($F37:S37,"&lt;4")&gt;0,IF(C37="К","-"," - "),(IFERROR(AVERAGE($F37:S37),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U37" s="22" t="n"/>
-      <c r="V37" s="39" t="n"/>
+      <c r="U37" s="42">
+        <f>IF(COUNTIF($F37:T37,"=*")&gt;0,IF($C37="К","-"," - "),IF(COUNTIF($F37:T37,"&lt;4")&gt;0,IF(C37="К","-"," - "),(IFERROR(AVERAGE($F37:T37),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V37" s="22" t="n"/>
+      <c r="W37" s="39" t="n"/>
     </row>
     <row r="38" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A38" s="40" t="n"/>
@@ -5478,53 +5662,56 @@
         </is>
       </c>
       <c r="F38" s="49" t="n">
+        <v>5</v>
+      </c>
+      <c r="G38" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="G38" s="49" t="n">
-        <v>6</v>
-      </c>
       <c r="H38" s="49" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I38" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="J38" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="J38" s="49" t="n">
-        <v>6</v>
-      </c>
       <c r="K38" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="L38" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="L38" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="M38" s="49" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N38" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="O38" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="O38" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="P38" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q38" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="Q38" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="R38" s="49" t="n">
         <v>8</v>
       </c>
       <c r="S38" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="T38" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="T38" s="42">
-        <f>IF(COUNTIF($F38:S38,"=*")&gt;0,IF($C38="К","-"," - "),IF(COUNTIF($F38:S38,"&lt;4")&gt;0,IF(C38="К","-"," - "),(IFERROR(AVERAGE($F38:S38),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U38" s="22" t="n"/>
-      <c r="V38" s="39" t="n"/>
+      <c r="U38" s="42">
+        <f>IF(COUNTIF($F38:T38,"=*")&gt;0,IF($C38="К","-"," - "),IF(COUNTIF($F38:T38,"&lt;4")&gt;0,IF(C38="К","-"," - "),(IFERROR(AVERAGE($F38:T38),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V38" s="22" t="n"/>
+      <c r="W38" s="39" t="n"/>
     </row>
     <row r="39" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A39" s="40" t="n"/>
@@ -5542,56 +5729,59 @@
           <t>Яремчук Євген Степанович</t>
         </is>
       </c>
-      <c r="F39" s="49" t="inlineStr">
+      <c r="F39" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="G39" s="49" t="inlineStr">
         <is>
           <t>н/а</t>
         </is>
       </c>
-      <c r="G39" s="49" t="n">
+      <c r="H39" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="H39" s="49" t="n">
+      <c r="I39" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="I39" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="J39" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="K39" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="K39" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="L39" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="M39" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="M39" s="49" t="n">
+      <c r="N39" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="N39" s="49" t="n">
+      <c r="O39" s="49" t="n">
         <v>7</v>
-      </c>
-      <c r="O39" s="49" t="n">
-        <v>11</v>
       </c>
       <c r="P39" s="49" t="n">
         <v>11</v>
       </c>
       <c r="Q39" s="49" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="R39" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="S39" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="S39" s="49" t="n">
-        <v>8</v>
-      </c>
-      <c r="T39" s="42">
-        <f>IF(COUNTIF($F39:S39,"=*")&gt;0,IF($C39="К","-"," - "),IF(COUNTIF($F39:S39,"&lt;4")&gt;0,IF(C39="К","-"," - "),(IFERROR(AVERAGE($F39:S39),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U39" s="22" t="n"/>
-      <c r="V39" s="39" t="n"/>
+      <c r="T39" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="U39" s="42">
+        <f>IF(COUNTIF($F39:T39,"=*")&gt;0,IF($C39="К","-"," - "),IF(COUNTIF($F39:T39,"&lt;4")&gt;0,IF(C39="К","-"," - "),(IFERROR(AVERAGE($F39:T39),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V39" s="22" t="n"/>
+      <c r="W39" s="39" t="n"/>
     </row>
     <row r="40" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A40" s="40" t="n"/>
@@ -5659,12 +5849,16 @@
         <f>IF(SUM(S$10:S39)=0,IF(COUNTA(S$10:S39)=0,"Очікую",0),SUM(S$10:S39)/$D39)</f>
         <v/>
       </c>
-      <c r="T40" s="9">
-        <f>IFERROR(AVERAGE($F40:S40),"Очікую")</f>
-        <v/>
-      </c>
-      <c r="U40" s="20" t="n"/>
-      <c r="V40" s="39" t="n"/>
+      <c r="T40" s="8">
+        <f>IF(SUM(T$10:T39)=0,IF(COUNTA(T$10:T39)=0,"Очікую",0),SUM(T$10:T39)/$D39)</f>
+        <v/>
+      </c>
+      <c r="U40" s="9">
+        <f>IFERROR(AVERAGE($F40:T40),"Очікую")</f>
+        <v/>
+      </c>
+      <c r="V40" s="20" t="n"/>
+      <c r="W40" s="39" t="n"/>
     </row>
     <row r="41" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A41" s="40" t="n"/>
@@ -5732,9 +5926,13 @@
         <f>IF(SUM(S$10:S39)=0,IF(COUNTA(S$10:S39)=0,"Очікую",0),IF(COUNTIF(S$10:S39,"&gt;=4")=0,0,COUNTIF(S$10:S39,"&gt;=4")/$D39*100))</f>
         <v/>
       </c>
-      <c r="T41" s="6" t="n"/>
-      <c r="U41" s="20" t="n"/>
-      <c r="V41" s="39" t="n"/>
+      <c r="T41" s="43">
+        <f>IF(SUM(T$10:T39)=0,IF(COUNTA(T$10:T39)=0,"Очікую",0),IF(COUNTIF(T$10:T39,"&gt;=4")=0,0,COUNTIF(T$10:T39,"&gt;=4")/$D39*100))</f>
+        <v/>
+      </c>
+      <c r="U41" s="6" t="n"/>
+      <c r="V41" s="20" t="n"/>
+      <c r="W41" s="39" t="n"/>
     </row>
     <row r="42" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A42" s="40" t="n"/>
@@ -5802,9 +6000,13 @@
         <f>IF(SUM(S$10:S39)=0,IF(COUNTA(S$10:S39)=0,"Очікую",0),IF(COUNTIF(S$10:S39,"&gt;=7")=0,0,COUNTIF(S$10:S39,"&gt;=7")/$D39*100))</f>
         <v/>
       </c>
-      <c r="T42" s="6" t="n"/>
-      <c r="U42" s="20" t="n"/>
-      <c r="V42" s="39" t="n"/>
+      <c r="T42" s="43">
+        <f>IF(SUM(T$10:T39)=0,IF(COUNTA(T$10:T39)=0,"Очікую",0),IF(COUNTIF(T$10:T39,"&gt;=7")=0,0,COUNTIF(T$10:T39,"&gt;=7")/$D39*100))</f>
+        <v/>
+      </c>
+      <c r="U42" s="6" t="n"/>
+      <c r="V42" s="20" t="n"/>
+      <c r="W42" s="39" t="n"/>
     </row>
     <row r="43" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A43" s="40" t="n"/>
@@ -5817,7 +6019,7 @@
         </is>
       </c>
       <c r="F43" s="8">
-        <f>IFERROR(AVERAGE(F41:S41),"Очікую")</f>
+        <f>IFERROR(AVERAGE(F41:T41),"Очікую")</f>
         <v/>
       </c>
       <c r="G43" s="6" t="n"/>
@@ -5834,8 +6036,9 @@
       <c r="R43" s="6" t="n"/>
       <c r="S43" s="6" t="n"/>
       <c r="T43" s="6" t="n"/>
-      <c r="U43" s="20" t="n"/>
-      <c r="V43" s="39" t="n"/>
+      <c r="U43" s="6" t="n"/>
+      <c r="V43" s="20" t="n"/>
+      <c r="W43" s="39" t="n"/>
     </row>
     <row r="44" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A44" s="40" t="n"/>
@@ -5848,7 +6051,7 @@
         </is>
       </c>
       <c r="F44" s="8">
-        <f>IFERROR(AVERAGE($F42:S42),"Очікую")</f>
+        <f>IFERROR(AVERAGE($F42:T42),"Очікую")</f>
         <v/>
       </c>
       <c r="G44" s="6" t="n"/>
@@ -5865,8 +6068,9 @@
       <c r="R44" s="6" t="n"/>
       <c r="S44" s="6" t="n"/>
       <c r="T44" s="6" t="n"/>
-      <c r="U44" s="20" t="n"/>
-      <c r="V44" s="39" t="n"/>
+      <c r="U44" s="6" t="n"/>
+      <c r="V44" s="20" t="n"/>
+      <c r="W44" s="39" t="n"/>
     </row>
     <row r="45" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A45" s="40" t="n"/>
@@ -5892,12 +6096,13 @@
       <c r="N45" s="6" t="n"/>
       <c r="O45" s="6" t="n"/>
       <c r="P45" s="6" t="n"/>
-      <c r="Q45" s="52" t="n"/>
+      <c r="Q45" s="6" t="n"/>
       <c r="R45" s="52" t="n"/>
       <c r="S45" s="52" t="n"/>
       <c r="T45" s="52" t="n"/>
-      <c r="U45" s="20" t="n"/>
-      <c r="V45" s="39" t="n"/>
+      <c r="U45" s="52" t="n"/>
+      <c r="V45" s="20" t="n"/>
+      <c r="W45" s="39" t="n"/>
     </row>
     <row r="46" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A46" s="40" t="n"/>
@@ -5922,11 +6127,11 @@
       <c r="I46" s="55" t="n"/>
       <c r="J46" s="55" t="n"/>
       <c r="K46" s="55" t="n"/>
-      <c r="L46" s="6" t="n"/>
+      <c r="L46" s="55" t="n"/>
       <c r="M46" s="6" t="n"/>
       <c r="N46" s="6" t="n"/>
-      <c r="O46" s="56" t="n"/>
-      <c r="P46" s="54" t="inlineStr">
+      <c r="O46" s="6" t="n"/>
+      <c r="P46" s="56" t="inlineStr">
         <is>
           <t>Ірина ДОПІРА</t>
         </is>
@@ -5935,8 +6140,9 @@
       <c r="R46" s="54" t="n"/>
       <c r="S46" s="54" t="n"/>
       <c r="T46" s="54" t="n"/>
-      <c r="U46" s="20" t="n"/>
-      <c r="V46" s="39" t="n"/>
+      <c r="U46" s="54" t="n"/>
+      <c r="V46" s="20" t="n"/>
+      <c r="W46" s="39" t="n"/>
     </row>
     <row r="47" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A47" s="40" t="n"/>
@@ -5956,17 +6162,18 @@
       <c r="I47" s="55" t="n"/>
       <c r="J47" s="55" t="n"/>
       <c r="K47" s="55" t="n"/>
-      <c r="L47" s="6" t="n"/>
+      <c r="L47" s="55" t="n"/>
       <c r="M47" s="6" t="n"/>
       <c r="N47" s="6" t="n"/>
-      <c r="O47" s="56" t="n"/>
-      <c r="P47" s="52" t="n"/>
+      <c r="O47" s="6" t="n"/>
+      <c r="P47" s="56" t="n"/>
       <c r="Q47" s="52" t="n"/>
       <c r="R47" s="52" t="n"/>
       <c r="S47" s="52" t="n"/>
       <c r="T47" s="52" t="n"/>
-      <c r="U47" s="20" t="n"/>
-      <c r="V47" s="39" t="n"/>
+      <c r="U47" s="52" t="n"/>
+      <c r="V47" s="20" t="n"/>
+      <c r="W47" s="39" t="n"/>
     </row>
     <row r="48" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A48" s="40" t="n"/>
@@ -5979,7 +6186,7 @@
         </is>
       </c>
       <c r="F48" s="63">
-        <f>IF(F45="Очікую","Очікую",IF(F45-COUNTIF($T$10:$T39," - ")&lt;ROUNDDOWN(F45*0.4,0),F45-COUNTIF($T$10:$T39," - "),ROUNDDOWN(F45*0.4,0)))</f>
+        <f>IF(F45="Очікую","Очікую",IF(F45-COUNTIF($U$10:$U39," - ")&lt;ROUNDDOWN(F45*0.4,0),F45-COUNTIF($U$10:$U39," - "),ROUNDDOWN(F45*0.4,0)))</f>
         <v/>
       </c>
       <c r="G48" s="6" t="n"/>
@@ -5991,11 +6198,11 @@
       <c r="I48" s="56" t="n"/>
       <c r="J48" s="56" t="n"/>
       <c r="K48" s="56" t="n"/>
-      <c r="L48" s="6" t="n"/>
+      <c r="L48" s="56" t="n"/>
       <c r="M48" s="6" t="n"/>
       <c r="N48" s="6" t="n"/>
-      <c r="O48" s="56" t="n"/>
-      <c r="P48" s="54" t="inlineStr">
+      <c r="O48" s="6" t="n"/>
+      <c r="P48" s="56" t="inlineStr">
         <is>
           <t>Маргарита БРІТІКОВА</t>
         </is>
@@ -6004,8 +6211,9 @@
       <c r="R48" s="54" t="n"/>
       <c r="S48" s="54" t="n"/>
       <c r="T48" s="54" t="n"/>
-      <c r="U48" s="20" t="n"/>
-      <c r="V48" s="39" t="n"/>
+      <c r="U48" s="54" t="n"/>
+      <c r="V48" s="20" t="n"/>
+      <c r="W48" s="39" t="n"/>
     </row>
     <row r="49" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A49" s="40" t="n"/>
@@ -6028,8 +6236,9 @@
       <c r="R49" s="14" t="n"/>
       <c r="S49" s="14" t="n"/>
       <c r="T49" s="14" t="n"/>
-      <c r="U49" s="15" t="n"/>
-      <c r="V49" s="39" t="n"/>
+      <c r="U49" s="14" t="n"/>
+      <c r="V49" s="15" t="n"/>
+      <c r="W49" s="39" t="n"/>
     </row>
     <row r="50" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A50" s="38" t="n"/>
@@ -6053,7 +6262,8 @@
       <c r="S50" s="38" t="n"/>
       <c r="T50" s="38" t="n"/>
       <c r="U50" s="38" t="n"/>
-      <c r="V50" s="39" t="n"/>
+      <c r="V50" s="38" t="n"/>
+      <c r="W50" s="39" t="n"/>
     </row>
     <row r="51" hidden="1" ht="15" customFormat="1" customHeight="1" s="11"/>
     <row r="52" hidden="1" ht="15" customFormat="1" customHeight="1" s="11"/>
@@ -6127,16 +6337,16 @@
     <row r="120" hidden="1" ht="12" customHeight="1"/>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="C3:T3"/>
-    <mergeCell ref="F8:S8"/>
-    <mergeCell ref="C6:T6"/>
-    <mergeCell ref="C7:T7"/>
     <mergeCell ref="E8:E9"/>
     <mergeCell ref="C8:C9"/>
+    <mergeCell ref="C5:U5"/>
+    <mergeCell ref="U8:U9"/>
     <mergeCell ref="D8:D9"/>
-    <mergeCell ref="C5:T5"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="C4:T4"/>
+    <mergeCell ref="C3:U3"/>
+    <mergeCell ref="C7:U7"/>
+    <mergeCell ref="C4:U4"/>
+    <mergeCell ref="F8:T8"/>
+    <mergeCell ref="C6:U6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.1968503937007874" right="0.1968503937007874" top="0.1968503937007874" bottom="0.1968503937007874" header="0" footer="0"/>
@@ -6151,7 +6361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V27"/>
+  <dimension ref="A1:W27"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1"/>
   <cols>
     <col width="2.7109375" customWidth="1" style="1" min="1" max="2"/>
@@ -6159,10 +6369,9 @@
     <col width="6.5703125" customWidth="1" style="1" min="4" max="4"/>
     <col width="40.42578125" customWidth="1" style="1" min="5" max="5"/>
     <col width="6.7109375" customWidth="1" style="1" min="6" max="25"/>
-    <col width="11.3" customWidth="1" min="20" max="20"/>
-    <col width="2.7" customWidth="1" min="21" max="21"/>
+    <col width="11.3" customWidth="1" min="21" max="21"/>
     <col width="2.7" customWidth="1" min="22" max="22"/>
-    <col hidden="1" width="13" customWidth="1" min="23" max="23"/>
+    <col width="2.7" customWidth="1" min="23" max="23"/>
     <col hidden="1" width="13" customWidth="1" min="24" max="24"/>
     <col hidden="1" width="13" customWidth="1" min="25" max="25"/>
     <col hidden="1" width="11.28515625" customWidth="1" style="1" min="26" max="26"/>
@@ -6202,6 +6411,7 @@
       <c r="T1" s="38" t="n"/>
       <c r="U1" s="38" t="n"/>
       <c r="V1" s="38" t="n"/>
+      <c r="W1" s="38" t="n"/>
     </row>
     <row r="2" ht="12" customHeight="1">
       <c r="A2" s="40" t="n"/>
@@ -6224,8 +6434,9 @@
       <c r="R2" s="18" t="n"/>
       <c r="S2" s="18" t="n"/>
       <c r="T2" s="18" t="n"/>
-      <c r="U2" s="19" t="n"/>
-      <c r="V2" s="39" t="n"/>
+      <c r="U2" s="18" t="n"/>
+      <c r="V2" s="19" t="n"/>
+      <c r="W2" s="39" t="n"/>
     </row>
     <row r="3" ht="54.95" customFormat="1" customHeight="1" s="2">
       <c r="A3" s="40" t="n"/>
@@ -6254,8 +6465,9 @@
       <c r="R3" s="86" t="n"/>
       <c r="S3" s="86" t="n"/>
       <c r="T3" s="86" t="n"/>
-      <c r="U3" s="20" t="n"/>
-      <c r="V3" s="39" t="n"/>
+      <c r="U3" s="86" t="n"/>
+      <c r="V3" s="20" t="n"/>
+      <c r="W3" s="39" t="n"/>
     </row>
     <row r="4" ht="15" customFormat="1" customHeight="1" s="3">
       <c r="A4" s="40" t="n"/>
@@ -6282,8 +6494,9 @@
       <c r="R4" s="86" t="n"/>
       <c r="S4" s="86" t="n"/>
       <c r="T4" s="86" t="n"/>
-      <c r="U4" s="20" t="n"/>
-      <c r="V4" s="39" t="n"/>
+      <c r="U4" s="86" t="n"/>
+      <c r="V4" s="20" t="n"/>
+      <c r="W4" s="39" t="n"/>
     </row>
     <row r="5" ht="15" customFormat="1" customHeight="1" s="2">
       <c r="A5" s="40" t="n"/>
@@ -6310,15 +6523,16 @@
       <c r="R5" s="87" t="n"/>
       <c r="S5" s="87" t="n"/>
       <c r="T5" s="87" t="n"/>
-      <c r="U5" s="20" t="n"/>
-      <c r="V5" s="39" t="n"/>
+      <c r="U5" s="87" t="n"/>
+      <c r="V5" s="20" t="n"/>
+      <c r="W5" s="39" t="n"/>
     </row>
     <row r="6" ht="15" customFormat="1" customHeight="1" s="2">
       <c r="A6" s="40" t="n"/>
       <c r="B6" s="12" t="n"/>
       <c r="C6" s="73" t="inlineStr">
         <is>
-          <t>За І семестр 2025-2026 н.р.</t>
+          <t>За ІІ семестр 2025-2026 н.р.</t>
         </is>
       </c>
       <c r="D6" s="87" t="n"/>
@@ -6338,8 +6552,9 @@
       <c r="R6" s="87" t="n"/>
       <c r="S6" s="87" t="n"/>
       <c r="T6" s="87" t="n"/>
-      <c r="U6" s="20" t="n"/>
-      <c r="V6" s="39" t="n"/>
+      <c r="U6" s="87" t="n"/>
+      <c r="V6" s="20" t="n"/>
+      <c r="W6" s="39" t="n"/>
     </row>
     <row r="7" ht="15" customFormat="1" customHeight="1" s="2">
       <c r="A7" s="40" t="n"/>
@@ -6366,8 +6581,9 @@
       <c r="R7" s="88" t="n"/>
       <c r="S7" s="88" t="n"/>
       <c r="T7" s="88" t="n"/>
-      <c r="U7" s="20" t="n"/>
-      <c r="V7" s="39" t="n"/>
+      <c r="U7" s="88" t="n"/>
+      <c r="V7" s="20" t="n"/>
+      <c r="W7" s="39" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="40" t="n"/>
@@ -6405,14 +6621,15 @@
       <c r="P8" s="89" t="n"/>
       <c r="Q8" s="89" t="n"/>
       <c r="R8" s="89" t="n"/>
-      <c r="S8" s="90" t="n"/>
-      <c r="T8" s="91" t="inlineStr">
+      <c r="S8" s="89" t="n"/>
+      <c r="T8" s="90" t="n"/>
+      <c r="U8" s="91" t="inlineStr">
         <is>
           <t>Середній бал</t>
         </is>
       </c>
-      <c r="U8" s="20" t="n"/>
-      <c r="V8" s="39" t="n"/>
+      <c r="V8" s="20" t="n"/>
+      <c r="W8" s="39" t="n"/>
     </row>
     <row r="9" ht="125.1" customHeight="1">
       <c r="A9" s="40" t="n"/>
@@ -6422,91 +6639,97 @@
       <c r="E9" s="92" t="n"/>
       <c r="F9" s="13" t="inlineStr">
         <is>
+          <t>Астрономія
+Наговська Т.С.</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
           <t>Біологія
 Богданенко О.В.</t>
         </is>
       </c>
-      <c r="G9" s="13" t="inlineStr">
+      <c r="H9" s="13" t="inlineStr">
         <is>
           <t>Всесвітня історія
 Мельничук С.А.</t>
         </is>
       </c>
-      <c r="H9" s="13" t="inlineStr">
+      <c r="I9" s="13" t="inlineStr">
         <is>
           <t>Географія
 Наговська Т.С.</t>
         </is>
       </c>
-      <c r="I9" s="13" t="inlineStr">
+      <c r="J9" s="13" t="inlineStr">
         <is>
           <t>Зарубіжна література
 Сербулова Ю.А.</t>
         </is>
       </c>
-      <c r="J9" s="13" t="inlineStr">
+      <c r="K9" s="13" t="inlineStr">
         <is>
           <t>Захист України
 Лазар В.І.</t>
         </is>
       </c>
-      <c r="K9" s="13" t="inlineStr">
+      <c r="L9" s="13" t="inlineStr">
         <is>
           <t>Іноземна мова
 Сербулова Ю.А.</t>
         </is>
       </c>
-      <c r="L9" s="13" t="inlineStr">
+      <c r="M9" s="13" t="inlineStr">
         <is>
           <t>Інформатика
 Бєльдюгіна С.С.</t>
         </is>
       </c>
-      <c r="M9" s="13" t="inlineStr">
+      <c r="N9" s="13" t="inlineStr">
         <is>
           <t>Історія України
 Левчук Т.Г.</t>
         </is>
       </c>
-      <c r="N9" s="13" t="inlineStr">
+      <c r="O9" s="13" t="inlineStr">
         <is>
           <t>Математика
 Бондаренко О.С.</t>
         </is>
       </c>
-      <c r="O9" s="13" t="inlineStr">
+      <c r="P9" s="13" t="inlineStr">
         <is>
           <t>Українська література
 Антропова Л.І.</t>
         </is>
       </c>
-      <c r="P9" s="13" t="inlineStr">
+      <c r="Q9" s="13" t="inlineStr">
         <is>
           <t>Українська мова
 Антропова Л.І.</t>
         </is>
       </c>
-      <c r="Q9" s="13" t="inlineStr">
+      <c r="R9" s="13" t="inlineStr">
         <is>
           <t>Фізика
 Калюта Н.М.</t>
         </is>
       </c>
-      <c r="R9" s="13" t="inlineStr">
+      <c r="S9" s="13" t="inlineStr">
         <is>
           <t>Фізична культура
 Возіян О.Г.</t>
         </is>
       </c>
-      <c r="S9" s="13" t="inlineStr">
+      <c r="T9" s="13" t="inlineStr">
         <is>
           <t>Хімія
 Сахно Н.О.</t>
         </is>
       </c>
-      <c r="T9" s="92" t="n"/>
-      <c r="U9" s="20" t="n"/>
-      <c r="V9" s="39" t="n"/>
+      <c r="U9" s="92" t="n"/>
+      <c r="V9" s="20" t="n"/>
+      <c r="W9" s="39" t="n"/>
     </row>
     <row r="10" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A10" s="40" t="n"/>
@@ -6528,50 +6751,53 @@
         <v>8</v>
       </c>
       <c r="G10" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="H10" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="H10" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="I10" s="49" t="n">
         <v>8</v>
       </c>
       <c r="J10" s="49" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K10" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="L10" s="49" t="n">
         <v>4</v>
-      </c>
-      <c r="L10" s="49" t="n">
-        <v>5</v>
       </c>
       <c r="M10" s="49" t="n">
         <v>5</v>
       </c>
       <c r="N10" s="49" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O10" s="49" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P10" s="49" t="n">
         <v>6</v>
       </c>
       <c r="Q10" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="R10" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="R10" s="49" t="n">
+      <c r="S10" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="S10" s="49" t="n">
+      <c r="T10" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="T10" s="42">
-        <f>IF(COUNTIF($F10:S10,"=*")&gt;0,IF($C10="К","-"," - "),IF(COUNTIF($F10:S10,"&lt;4")&gt;0,IF(C10="К","-"," - "),(IFERROR(AVERAGE($F10:S10),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U10" s="22" t="n"/>
-      <c r="V10" s="39" t="n"/>
+      <c r="U10" s="42">
+        <f>IF(COUNTIF($F10:T10,"=*")&gt;0,IF($C10="К","-"," - "),IF(COUNTIF($F10:T10,"&lt;4")&gt;0,IF(C10="К","-"," - "),(IFERROR(AVERAGE($F10:T10),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V10" s="22" t="n"/>
+      <c r="W10" s="39" t="n"/>
     </row>
     <row r="11" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A11" s="40" t="n"/>
@@ -6590,53 +6816,56 @@
         </is>
       </c>
       <c r="F11" s="49" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G11" s="49" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H11" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="I11" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="I11" s="49" t="n">
+      <c r="J11" s="49" t="n">
         <v>11</v>
-      </c>
-      <c r="J11" s="49" t="n">
-        <v>4</v>
       </c>
       <c r="K11" s="49" t="n">
         <v>4</v>
       </c>
       <c r="L11" s="49" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M11" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="N11" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="N11" s="49" t="n">
+      <c r="O11" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="O11" s="49" t="n">
+      <c r="P11" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="P11" s="49" t="n">
+      <c r="Q11" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="Q11" s="49" t="n">
+      <c r="R11" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="R11" s="49" t="n">
+      <c r="S11" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="S11" s="49" t="n">
+      <c r="T11" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="T11" s="42">
-        <f>IF(COUNTIF($F11:S11,"=*")&gt;0,IF($C11="К","-"," - "),IF(COUNTIF($F11:S11,"&lt;4")&gt;0,IF(C11="К","-"," - "),(IFERROR(AVERAGE($F11:S11),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U11" s="22" t="n"/>
-      <c r="V11" s="39" t="n"/>
+      <c r="U11" s="42">
+        <f>IF(COUNTIF($F11:T11,"=*")&gt;0,IF($C11="К","-"," - "),IF(COUNTIF($F11:T11,"&lt;4")&gt;0,IF(C11="К","-"," - "),(IFERROR(AVERAGE($F11:T11),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V11" s="22" t="n"/>
+      <c r="W11" s="39" t="n"/>
     </row>
     <row r="12" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A12" s="40" t="n"/>
@@ -6655,53 +6884,56 @@
         </is>
       </c>
       <c r="F12" s="49" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G12" s="49" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H12" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="I12" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="I12" s="49" t="n">
+      <c r="J12" s="49" t="n">
         <v>11</v>
-      </c>
-      <c r="J12" s="49" t="n">
-        <v>7</v>
       </c>
       <c r="K12" s="49" t="n">
         <v>7</v>
       </c>
       <c r="L12" s="49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M12" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="N12" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="N12" s="49" t="n">
+      <c r="O12" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="O12" s="49" t="n">
-        <v>6</v>
-      </c>
       <c r="P12" s="49" t="n">
         <v>6</v>
       </c>
       <c r="Q12" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="R12" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="R12" s="49" t="n">
-        <v>6</v>
-      </c>
       <c r="S12" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="T12" s="42">
-        <f>IF(COUNTIF($F12:S12,"=*")&gt;0,IF($C12="К","-"," - "),IF(COUNTIF($F12:S12,"&lt;4")&gt;0,IF(C12="К","-"," - "),(IFERROR(AVERAGE($F12:S12),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U12" s="22" t="n"/>
-      <c r="V12" s="39" t="n"/>
+      <c r="T12" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="U12" s="42">
+        <f>IF(COUNTIF($F12:T12,"=*")&gt;0,IF($C12="К","-"," - "),IF(COUNTIF($F12:T12,"&lt;4")&gt;0,IF(C12="К","-"," - "),(IFERROR(AVERAGE($F12:T12),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V12" s="22" t="n"/>
+      <c r="W12" s="39" t="n"/>
     </row>
     <row r="13" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A13" s="40" t="n"/>
@@ -6720,53 +6952,56 @@
         </is>
       </c>
       <c r="F13" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="G13" s="49" t="n">
         <v>7</v>
-      </c>
-      <c r="G13" s="49" t="n">
-        <v>10</v>
       </c>
       <c r="H13" s="49" t="n">
         <v>10</v>
       </c>
       <c r="I13" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="J13" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="J13" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="K13" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="L13" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="L13" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="M13" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="N13" s="49" t="n">
         <v>5</v>
-      </c>
-      <c r="N13" s="49" t="n">
-        <v>10</v>
       </c>
       <c r="O13" s="49" t="n">
         <v>10</v>
       </c>
       <c r="P13" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q13" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="Q13" s="49" t="n">
-        <v>6</v>
-      </c>
       <c r="R13" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="S13" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="S13" s="49" t="n">
-        <v>6</v>
-      </c>
-      <c r="T13" s="42">
-        <f>IF(COUNTIF($F13:S13,"=*")&gt;0,IF($C13="К","-"," - "),IF(COUNTIF($F13:S13,"&lt;4")&gt;0,IF(C13="К","-"," - "),(IFERROR(AVERAGE($F13:S13),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U13" s="22" t="n"/>
-      <c r="V13" s="39" t="n"/>
+      <c r="T13" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="U13" s="42">
+        <f>IF(COUNTIF($F13:T13,"=*")&gt;0,IF($C13="К","-"," - "),IF(COUNTIF($F13:T13,"&lt;4")&gt;0,IF(C13="К","-"," - "),(IFERROR(AVERAGE($F13:T13),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V13" s="22" t="n"/>
+      <c r="W13" s="39" t="n"/>
     </row>
     <row r="14" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A14" s="40" t="n"/>
@@ -6785,53 +7020,56 @@
         </is>
       </c>
       <c r="F14" s="49" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G14" s="49" t="n">
         <v>9</v>
       </c>
       <c r="H14" s="49" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I14" s="49" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J14" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="K14" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="K14" s="49" t="n">
+      <c r="L14" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="L14" s="49" t="n">
-        <v>6</v>
-      </c>
       <c r="M14" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="N14" s="49" t="n">
         <v>11</v>
-      </c>
-      <c r="N14" s="49" t="n">
-        <v>7</v>
       </c>
       <c r="O14" s="49" t="n">
         <v>7</v>
       </c>
       <c r="P14" s="49" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q14" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="Q14" s="49" t="n">
-        <v>6</v>
-      </c>
       <c r="R14" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="S14" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="S14" s="49" t="n">
-        <v>8</v>
-      </c>
-      <c r="T14" s="42">
-        <f>IF(COUNTIF($F14:S14,"=*")&gt;0,IF($C14="К","-"," - "),IF(COUNTIF($F14:S14,"&lt;4")&gt;0,IF(C14="К","-"," - "),(IFERROR(AVERAGE($F14:S14),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U14" s="22" t="n"/>
-      <c r="V14" s="39" t="n"/>
+      <c r="T14" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="U14" s="42">
+        <f>IF(COUNTIF($F14:T14,"=*")&gt;0,IF($C14="К","-"," - "),IF(COUNTIF($F14:T14,"&lt;4")&gt;0,IF(C14="К","-"," - "),(IFERROR(AVERAGE($F14:T14),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V14" s="22" t="n"/>
+      <c r="W14" s="39" t="n"/>
     </row>
     <row r="15" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A15" s="40" t="n"/>
@@ -6850,53 +7088,56 @@
         </is>
       </c>
       <c r="F15" s="49" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G15" s="49" t="n">
         <v>4</v>
       </c>
       <c r="H15" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="I15" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="I15" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="J15" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="K15" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="K15" s="49" t="n">
+      <c r="L15" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="L15" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="M15" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="N15" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="N15" s="49" t="n">
+      <c r="O15" s="49" t="n">
         <v>9</v>
       </c>
-      <c r="O15" s="49" t="n">
-        <v>6</v>
-      </c>
       <c r="P15" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q15" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="Q15" s="49" t="n">
+      <c r="R15" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="R15" s="49" t="n">
-        <v>8</v>
-      </c>
       <c r="S15" s="49" t="n">
         <v>8</v>
       </c>
-      <c r="T15" s="42">
-        <f>IF(COUNTIF($F15:S15,"=*")&gt;0,IF($C15="К","-"," - "),IF(COUNTIF($F15:S15,"&lt;4")&gt;0,IF(C15="К","-"," - "),(IFERROR(AVERAGE($F15:S15),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U15" s="22" t="n"/>
-      <c r="V15" s="39" t="n"/>
+      <c r="T15" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="U15" s="42">
+        <f>IF(COUNTIF($F15:T15,"=*")&gt;0,IF($C15="К","-"," - "),IF(COUNTIF($F15:T15,"&lt;4")&gt;0,IF(C15="К","-"," - "),(IFERROR(AVERAGE($F15:T15),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V15" s="22" t="n"/>
+      <c r="W15" s="39" t="n"/>
     </row>
     <row r="16" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A16" s="40" t="n"/>
@@ -6915,59 +7156,62 @@
         </is>
       </c>
       <c r="F16" s="49" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G16" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="H16" s="49" t="inlineStr">
+      <c r="H16" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" s="49" t="inlineStr">
         <is>
           <t>н/а</t>
         </is>
       </c>
-      <c r="I16" s="49" t="n">
+      <c r="J16" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="J16" s="49" t="n">
-        <v>8</v>
-      </c>
-      <c r="K16" s="49" t="inlineStr">
+      <c r="K16" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="L16" s="49" t="inlineStr">
         <is>
           <t>н/а</t>
         </is>
       </c>
-      <c r="L16" s="49" t="n">
-        <v>6</v>
-      </c>
       <c r="M16" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="N16" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="N16" s="49" t="n">
+      <c r="O16" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="O16" s="49" t="n">
-        <v>8</v>
-      </c>
-      <c r="P16" s="49" t="inlineStr">
+      <c r="P16" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q16" s="49" t="inlineStr">
         <is>
           <t>н/а</t>
         </is>
       </c>
-      <c r="Q16" s="49" t="n">
+      <c r="R16" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="R16" s="49" t="n">
+      <c r="S16" s="49" t="n">
         <v>10</v>
       </c>
-      <c r="S16" s="49" t="n">
+      <c r="T16" s="49" t="n">
         <v>11</v>
       </c>
-      <c r="T16" s="42">
-        <f>IF(COUNTIF($F16:S16,"=*")&gt;0,IF($C16="К","-"," - "),IF(COUNTIF($F16:S16,"&lt;4")&gt;0,IF(C16="К","-"," - "),(IFERROR(AVERAGE($F16:S16),"Очікую"))))</f>
-        <v/>
-      </c>
-      <c r="U16" s="22" t="n"/>
-      <c r="V16" s="39" t="n"/>
+      <c r="U16" s="42">
+        <f>IF(COUNTIF($F16:T16,"=*")&gt;0,IF($C16="К","-"," - "),IF(COUNTIF($F16:T16,"&lt;4")&gt;0,IF(C16="К","-"," - "),(IFERROR(AVERAGE($F16:T16),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V16" s="22" t="n"/>
+      <c r="W16" s="39" t="n"/>
     </row>
     <row r="17" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A17" s="40" t="n"/>
@@ -7035,12 +7279,16 @@
         <f>IF(SUM(S$10:S16)=0,IF(COUNTA(S$10:S16)=0,"Очікую",0),SUM(S$10:S16)/$D16)</f>
         <v/>
       </c>
-      <c r="T17" s="9">
-        <f>IFERROR(AVERAGE($F17:S17),"Очікую")</f>
-        <v/>
-      </c>
-      <c r="U17" s="20" t="n"/>
-      <c r="V17" s="39" t="n"/>
+      <c r="T17" s="8">
+        <f>IF(SUM(T$10:T16)=0,IF(COUNTA(T$10:T16)=0,"Очікую",0),SUM(T$10:T16)/$D16)</f>
+        <v/>
+      </c>
+      <c r="U17" s="9">
+        <f>IFERROR(AVERAGE($F17:T17),"Очікую")</f>
+        <v/>
+      </c>
+      <c r="V17" s="20" t="n"/>
+      <c r="W17" s="39" t="n"/>
     </row>
     <row r="18" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A18" s="40" t="n"/>
@@ -7108,9 +7356,13 @@
         <f>IF(SUM(S$10:S16)=0,IF(COUNTA(S$10:S16)=0,"Очікую",0),IF(COUNTIF(S$10:S16,"&gt;=4")=0,0,COUNTIF(S$10:S16,"&gt;=4")/$D16*100))</f>
         <v/>
       </c>
-      <c r="T18" s="6" t="n"/>
-      <c r="U18" s="20" t="n"/>
-      <c r="V18" s="39" t="n"/>
+      <c r="T18" s="43">
+        <f>IF(SUM(T$10:T16)=0,IF(COUNTA(T$10:T16)=0,"Очікую",0),IF(COUNTIF(T$10:T16,"&gt;=4")=0,0,COUNTIF(T$10:T16,"&gt;=4")/$D16*100))</f>
+        <v/>
+      </c>
+      <c r="U18" s="6" t="n"/>
+      <c r="V18" s="20" t="n"/>
+      <c r="W18" s="39" t="n"/>
     </row>
     <row r="19" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A19" s="40" t="n"/>
@@ -7178,9 +7430,13 @@
         <f>IF(SUM(S$10:S16)=0,IF(COUNTA(S$10:S16)=0,"Очікую",0),IF(COUNTIF(S$10:S16,"&gt;=7")=0,0,COUNTIF(S$10:S16,"&gt;=7")/$D16*100))</f>
         <v/>
       </c>
-      <c r="T19" s="6" t="n"/>
-      <c r="U19" s="20" t="n"/>
-      <c r="V19" s="39" t="n"/>
+      <c r="T19" s="43">
+        <f>IF(SUM(T$10:T16)=0,IF(COUNTA(T$10:T16)=0,"Очікую",0),IF(COUNTIF(T$10:T16,"&gt;=7")=0,0,COUNTIF(T$10:T16,"&gt;=7")/$D16*100))</f>
+        <v/>
+      </c>
+      <c r="U19" s="6" t="n"/>
+      <c r="V19" s="20" t="n"/>
+      <c r="W19" s="39" t="n"/>
     </row>
     <row r="20" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A20" s="40" t="n"/>
@@ -7193,7 +7449,7 @@
         </is>
       </c>
       <c r="F20" s="8">
-        <f>IFERROR(AVERAGE(F18:S18),"Очікую")</f>
+        <f>IFERROR(AVERAGE(F18:T18),"Очікую")</f>
         <v/>
       </c>
       <c r="G20" s="6" t="n"/>
@@ -7210,8 +7466,9 @@
       <c r="R20" s="6" t="n"/>
       <c r="S20" s="6" t="n"/>
       <c r="T20" s="6" t="n"/>
-      <c r="U20" s="20" t="n"/>
-      <c r="V20" s="39" t="n"/>
+      <c r="U20" s="6" t="n"/>
+      <c r="V20" s="20" t="n"/>
+      <c r="W20" s="39" t="n"/>
     </row>
     <row r="21" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A21" s="40" t="n"/>
@@ -7224,7 +7481,7 @@
         </is>
       </c>
       <c r="F21" s="8">
-        <f>IFERROR(AVERAGE($F19:S19),"Очікую")</f>
+        <f>IFERROR(AVERAGE($F19:T19),"Очікую")</f>
         <v/>
       </c>
       <c r="G21" s="6" t="n"/>
@@ -7241,8 +7498,9 @@
       <c r="R21" s="6" t="n"/>
       <c r="S21" s="6" t="n"/>
       <c r="T21" s="6" t="n"/>
-      <c r="U21" s="20" t="n"/>
-      <c r="V21" s="39" t="n"/>
+      <c r="U21" s="6" t="n"/>
+      <c r="V21" s="20" t="n"/>
+      <c r="W21" s="39" t="n"/>
     </row>
     <row r="22" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A22" s="40" t="n"/>
@@ -7268,12 +7526,13 @@
       <c r="N22" s="6" t="n"/>
       <c r="O22" s="6" t="n"/>
       <c r="P22" s="6" t="n"/>
-      <c r="Q22" s="52" t="n"/>
+      <c r="Q22" s="6" t="n"/>
       <c r="R22" s="52" t="n"/>
       <c r="S22" s="52" t="n"/>
       <c r="T22" s="52" t="n"/>
-      <c r="U22" s="20" t="n"/>
-      <c r="V22" s="39" t="n"/>
+      <c r="U22" s="52" t="n"/>
+      <c r="V22" s="20" t="n"/>
+      <c r="W22" s="39" t="n"/>
     </row>
     <row r="23" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A23" s="40" t="n"/>
@@ -7298,11 +7557,11 @@
       <c r="I23" s="55" t="n"/>
       <c r="J23" s="55" t="n"/>
       <c r="K23" s="55" t="n"/>
-      <c r="L23" s="6" t="n"/>
+      <c r="L23" s="55" t="n"/>
       <c r="M23" s="6" t="n"/>
       <c r="N23" s="6" t="n"/>
-      <c r="O23" s="56" t="n"/>
-      <c r="P23" s="54" t="inlineStr">
+      <c r="O23" s="6" t="n"/>
+      <c r="P23" s="56" t="inlineStr">
         <is>
           <t>Ірина ДОПІРА</t>
         </is>
@@ -7311,8 +7570,9 @@
       <c r="R23" s="54" t="n"/>
       <c r="S23" s="54" t="n"/>
       <c r="T23" s="54" t="n"/>
-      <c r="U23" s="20" t="n"/>
-      <c r="V23" s="39" t="n"/>
+      <c r="U23" s="54" t="n"/>
+      <c r="V23" s="20" t="n"/>
+      <c r="W23" s="39" t="n"/>
     </row>
     <row r="24" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A24" s="40" t="n"/>
@@ -7332,17 +7592,18 @@
       <c r="I24" s="55" t="n"/>
       <c r="J24" s="55" t="n"/>
       <c r="K24" s="55" t="n"/>
-      <c r="L24" s="6" t="n"/>
+      <c r="L24" s="55" t="n"/>
       <c r="M24" s="6" t="n"/>
       <c r="N24" s="6" t="n"/>
-      <c r="O24" s="56" t="n"/>
-      <c r="P24" s="52" t="n"/>
+      <c r="O24" s="6" t="n"/>
+      <c r="P24" s="56" t="n"/>
       <c r="Q24" s="52" t="n"/>
       <c r="R24" s="52" t="n"/>
       <c r="S24" s="52" t="n"/>
       <c r="T24" s="52" t="n"/>
-      <c r="U24" s="20" t="n"/>
-      <c r="V24" s="39" t="n"/>
+      <c r="U24" s="52" t="n"/>
+      <c r="V24" s="20" t="n"/>
+      <c r="W24" s="39" t="n"/>
     </row>
     <row r="25" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A25" s="40" t="n"/>
@@ -7355,7 +7616,7 @@
         </is>
       </c>
       <c r="F25" s="63">
-        <f>IF(F22="Очікую","Очікую",IF(F22-COUNTIF($T$10:$T16," - ")&lt;ROUNDDOWN(F22*0.4,0),F22-COUNTIF($T$10:$T16," - "),ROUNDDOWN(F22*0.4,0)))</f>
+        <f>IF(F22="Очікую","Очікую",IF(F22-COUNTIF($U$10:$U16," - ")&lt;ROUNDDOWN(F22*0.4,0),F22-COUNTIF($U$10:$U16," - "),ROUNDDOWN(F22*0.4,0)))</f>
         <v/>
       </c>
       <c r="G25" s="6" t="n"/>
@@ -7367,11 +7628,11 @@
       <c r="I25" s="56" t="n"/>
       <c r="J25" s="56" t="n"/>
       <c r="K25" s="56" t="n"/>
-      <c r="L25" s="6" t="n"/>
+      <c r="L25" s="56" t="n"/>
       <c r="M25" s="6" t="n"/>
       <c r="N25" s="6" t="n"/>
-      <c r="O25" s="56" t="n"/>
-      <c r="P25" s="54" t="inlineStr">
+      <c r="O25" s="6" t="n"/>
+      <c r="P25" s="56" t="inlineStr">
         <is>
           <t>Маргарита БРІТІКОВА</t>
         </is>
@@ -7380,8 +7641,9 @@
       <c r="R25" s="54" t="n"/>
       <c r="S25" s="54" t="n"/>
       <c r="T25" s="54" t="n"/>
-      <c r="U25" s="20" t="n"/>
-      <c r="V25" s="39" t="n"/>
+      <c r="U25" s="54" t="n"/>
+      <c r="V25" s="20" t="n"/>
+      <c r="W25" s="39" t="n"/>
     </row>
     <row r="26" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A26" s="40" t="n"/>
@@ -7404,8 +7666,9 @@
       <c r="R26" s="14" t="n"/>
       <c r="S26" s="14" t="n"/>
       <c r="T26" s="14" t="n"/>
-      <c r="U26" s="15" t="n"/>
-      <c r="V26" s="39" t="n"/>
+      <c r="U26" s="14" t="n"/>
+      <c r="V26" s="15" t="n"/>
+      <c r="W26" s="39" t="n"/>
     </row>
     <row r="27" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A27" s="38" t="n"/>
@@ -7429,7 +7692,8 @@
       <c r="S27" s="38" t="n"/>
       <c r="T27" s="38" t="n"/>
       <c r="U27" s="38" t="n"/>
-      <c r="V27" s="39" t="n"/>
+      <c r="V27" s="38" t="n"/>
+      <c r="W27" s="39" t="n"/>
     </row>
     <row r="28" hidden="1" ht="15" customFormat="1" customHeight="1" s="11"/>
     <row r="29" hidden="1" ht="15" customFormat="1" customHeight="1" s="11"/>
@@ -7526,16 +7790,16 @@
     <row r="120" hidden="1" ht="12" customHeight="1"/>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="C3:T3"/>
-    <mergeCell ref="F8:S8"/>
-    <mergeCell ref="C6:T6"/>
-    <mergeCell ref="C7:T7"/>
     <mergeCell ref="E8:E9"/>
     <mergeCell ref="C8:C9"/>
+    <mergeCell ref="C5:U5"/>
+    <mergeCell ref="U8:U9"/>
     <mergeCell ref="D8:D9"/>
-    <mergeCell ref="C5:T5"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="C4:T4"/>
+    <mergeCell ref="C3:U3"/>
+    <mergeCell ref="C7:U7"/>
+    <mergeCell ref="C4:U4"/>
+    <mergeCell ref="F8:T8"/>
+    <mergeCell ref="C6:U6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.1968503937007874" right="0.1968503937007874" top="0.1968503937007874" bottom="0.1968503937007874" header="0" footer="0"/>
@@ -7550,7 +7814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:W18"/>
+  <dimension ref="A1:X18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1"/>
   <cols>
     <col width="2.7109375" customWidth="1" style="1" min="1" max="2"/>
@@ -7558,11 +7822,10 @@
     <col width="6.5703125" customWidth="1" style="1" min="4" max="4"/>
     <col width="40.42578125" customWidth="1" style="1" min="5" max="5"/>
     <col width="6.7109375" customWidth="1" style="1" min="6" max="25"/>
-    <col width="11.3" customWidth="1" min="20" max="20"/>
     <col width="11.3" customWidth="1" min="21" max="21"/>
-    <col width="2.7" customWidth="1" min="22" max="22"/>
+    <col width="11.3" customWidth="1" min="22" max="22"/>
     <col width="2.7" customWidth="1" min="23" max="23"/>
-    <col hidden="1" width="13" customWidth="1" min="24" max="24"/>
+    <col width="2.7" customWidth="1" min="24" max="24"/>
     <col hidden="1" width="13" customWidth="1" min="25" max="25"/>
     <col hidden="1" width="11.28515625" customWidth="1" style="1" min="26" max="27"/>
     <col hidden="1" width="13" customWidth="1" min="27" max="27"/>
@@ -7603,6 +7866,7 @@
       <c r="U1" s="38" t="n"/>
       <c r="V1" s="38" t="n"/>
       <c r="W1" s="38" t="n"/>
+      <c r="X1" s="38" t="n"/>
     </row>
     <row r="2" ht="12" customHeight="1">
       <c r="A2" s="40" t="n"/>
@@ -7626,8 +7890,9 @@
       <c r="S2" s="18" t="n"/>
       <c r="T2" s="18" t="n"/>
       <c r="U2" s="18" t="n"/>
-      <c r="V2" s="19" t="n"/>
-      <c r="W2" s="39" t="n"/>
+      <c r="V2" s="18" t="n"/>
+      <c r="W2" s="19" t="n"/>
+      <c r="X2" s="39" t="n"/>
     </row>
     <row r="3" ht="54.95" customFormat="1" customHeight="1" s="2">
       <c r="A3" s="40" t="n"/>
@@ -7657,8 +7922,9 @@
       <c r="S3" s="86" t="n"/>
       <c r="T3" s="86" t="n"/>
       <c r="U3" s="86" t="n"/>
-      <c r="V3" s="20" t="n"/>
-      <c r="W3" s="39" t="n"/>
+      <c r="V3" s="86" t="n"/>
+      <c r="W3" s="20" t="n"/>
+      <c r="X3" s="39" t="n"/>
     </row>
     <row r="4" ht="15" customFormat="1" customHeight="1" s="3">
       <c r="A4" s="40" t="n"/>
@@ -7686,8 +7952,9 @@
       <c r="S4" s="86" t="n"/>
       <c r="T4" s="86" t="n"/>
       <c r="U4" s="86" t="n"/>
-      <c r="V4" s="20" t="n"/>
-      <c r="W4" s="39" t="n"/>
+      <c r="V4" s="86" t="n"/>
+      <c r="W4" s="20" t="n"/>
+      <c r="X4" s="39" t="n"/>
     </row>
     <row r="5" ht="15" customFormat="1" customHeight="1" s="2">
       <c r="A5" s="40" t="n"/>
@@ -7714,8 +7981,9 @@
       <c r="S5" s="87" t="n"/>
       <c r="T5" s="87" t="n"/>
       <c r="U5" s="87" t="n"/>
-      <c r="V5" s="20" t="n"/>
-      <c r="W5" s="39" t="n"/>
+      <c r="V5" s="87" t="n"/>
+      <c r="W5" s="20" t="n"/>
+      <c r="X5" s="39" t="n"/>
     </row>
     <row r="6" ht="15" customFormat="1" customHeight="1" s="2">
       <c r="A6" s="40" t="n"/>
@@ -7742,8 +8010,9 @@
       <c r="S6" s="87" t="n"/>
       <c r="T6" s="87" t="n"/>
       <c r="U6" s="87" t="n"/>
-      <c r="V6" s="20" t="n"/>
-      <c r="W6" s="39" t="n"/>
+      <c r="V6" s="87" t="n"/>
+      <c r="W6" s="20" t="n"/>
+      <c r="X6" s="39" t="n"/>
     </row>
     <row r="7" ht="15" customFormat="1" customHeight="1" s="2">
       <c r="A7" s="40" t="n"/>
@@ -7770,8 +8039,9 @@
       <c r="S7" s="88" t="n"/>
       <c r="T7" s="88" t="n"/>
       <c r="U7" s="88" t="n"/>
-      <c r="V7" s="20" t="n"/>
-      <c r="W7" s="39" t="n"/>
+      <c r="V7" s="88" t="n"/>
+      <c r="W7" s="20" t="n"/>
+      <c r="X7" s="39" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="40" t="n"/>
@@ -7809,19 +8079,20 @@
       <c r="P8" s="89" t="n"/>
       <c r="Q8" s="89" t="n"/>
       <c r="R8" s="89" t="n"/>
-      <c r="S8" s="90" t="n"/>
-      <c r="T8" s="91" t="inlineStr">
+      <c r="S8" s="89" t="n"/>
+      <c r="T8" s="90" t="n"/>
+      <c r="U8" s="91" t="inlineStr">
         <is>
           <t>Середній бал</t>
         </is>
       </c>
-      <c r="U8" s="91" t="inlineStr">
+      <c r="V8" s="91" t="inlineStr">
         <is>
           <t>Рейтинговий бал</t>
         </is>
       </c>
-      <c r="V8" s="20" t="n"/>
-      <c r="W8" s="39" t="n"/>
+      <c r="W8" s="20" t="n"/>
+      <c r="X8" s="39" t="n"/>
     </row>
     <row r="9" ht="125.1" customHeight="1">
       <c r="A9" s="40" t="n"/>
@@ -7885,172 +8156,184 @@
         <f>'Зведена D5'!S9</f>
         <v/>
       </c>
-      <c r="T9" s="92" t="n"/>
+      <c r="T9" s="13">
+        <f>'Зведена D5'!T9</f>
+        <v/>
+      </c>
       <c r="U9" s="92" t="n"/>
-      <c r="V9" s="20" t="n"/>
-      <c r="W9" s="39" t="n"/>
+      <c r="V9" s="92" t="n"/>
+      <c r="W9" s="20" t="n"/>
+      <c r="X9" s="39" t="n"/>
     </row>
     <row r="10" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A10" s="40" t="n"/>
       <c r="B10" s="12" t="n"/>
       <c r="C10" s="93">
-        <f>'Зведена D5'!C19</f>
+        <f>'Зведена D5'!C20</f>
         <v/>
       </c>
       <c r="D10" s="93" t="n">
         <v>1</v>
       </c>
       <c r="E10" s="94">
-        <f>'Зведена D5'!E19</f>
+        <f>'Зведена D5'!E20</f>
         <v/>
       </c>
       <c r="F10" s="95">
-        <f>'Зведена D5'!F19</f>
+        <f>'Зведена D5'!F20</f>
         <v/>
       </c>
       <c r="G10" s="95">
-        <f>'Зведена D5'!G19</f>
+        <f>'Зведена D5'!G20</f>
         <v/>
       </c>
       <c r="H10" s="95">
-        <f>'Зведена D5'!H19</f>
+        <f>'Зведена D5'!H20</f>
         <v/>
       </c>
       <c r="I10" s="95">
-        <f>'Зведена D5'!I19</f>
+        <f>'Зведена D5'!I20</f>
         <v/>
       </c>
       <c r="J10" s="95">
-        <f>'Зведена D5'!J19</f>
+        <f>'Зведена D5'!J20</f>
         <v/>
       </c>
       <c r="K10" s="95">
-        <f>'Зведена D5'!K19</f>
+        <f>'Зведена D5'!K20</f>
         <v/>
       </c>
       <c r="L10" s="95">
-        <f>'Зведена D5'!L19</f>
+        <f>'Зведена D5'!L20</f>
         <v/>
       </c>
       <c r="M10" s="95">
-        <f>'Зведена D5'!M19</f>
+        <f>'Зведена D5'!M20</f>
         <v/>
       </c>
       <c r="N10" s="95">
-        <f>'Зведена D5'!N19</f>
+        <f>'Зведена D5'!N20</f>
         <v/>
       </c>
       <c r="O10" s="95">
-        <f>'Зведена D5'!O19</f>
+        <f>'Зведена D5'!O20</f>
         <v/>
       </c>
       <c r="P10" s="95">
-        <f>'Зведена D5'!P19</f>
+        <f>'Зведена D5'!P20</f>
         <v/>
       </c>
       <c r="Q10" s="95">
-        <f>'Зведена D5'!Q19</f>
+        <f>'Зведена D5'!Q20</f>
         <v/>
       </c>
       <c r="R10" s="95">
-        <f>'Зведена D5'!R19</f>
+        <f>'Зведена D5'!R20</f>
         <v/>
       </c>
       <c r="S10" s="95">
-        <f>'Зведена D5'!S19</f>
-        <v/>
-      </c>
-      <c r="T10" s="96">
-        <f>IF(COUNTIF($F10:S10,"=*")&gt;0,IF($C10="К","-"," - "),IF(COUNTIF($F10:S10,"&lt;4")&gt;0,IF(C10="К","-"," - "),(IFERROR(AVERAGE($F10:S10),"Очікую"))))</f>
+        <f>'Зведена D5'!S20</f>
+        <v/>
+      </c>
+      <c r="T10" s="95">
+        <f>'Зведена D5'!T20</f>
         <v/>
       </c>
       <c r="U10" s="96">
-        <f>IFERROR(T10/12*90,"Очікую")</f>
-        <v/>
-      </c>
-      <c r="V10" s="22" t="n"/>
-      <c r="W10" s="39" t="n"/>
+        <f>IF(COUNTIF($F10:T10,"=*")&gt;0,IF($C10="К","-"," - "),IF(COUNTIF($F10:T10,"&lt;4")&gt;0,IF(C10="К","-"," - "),(IFERROR(AVERAGE($F10:T10),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V10" s="96">
+        <f>IFERROR(U10/12*90,"Очікую")</f>
+        <v/>
+      </c>
+      <c r="W10" s="22" t="n"/>
+      <c r="X10" s="39" t="n"/>
     </row>
     <row r="11" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A11" s="40" t="n"/>
       <c r="B11" s="12" t="n"/>
       <c r="C11" s="93">
-        <f>'Зведена D5'!C20</f>
+        <f>'Зведена D5'!C19</f>
         <v/>
       </c>
       <c r="D11" s="93" t="n">
         <v>2</v>
       </c>
       <c r="E11" s="94">
-        <f>'Зведена D5'!E20</f>
+        <f>'Зведена D5'!E19</f>
         <v/>
       </c>
       <c r="F11" s="95">
-        <f>'Зведена D5'!F20</f>
+        <f>'Зведена D5'!F19</f>
         <v/>
       </c>
       <c r="G11" s="95">
-        <f>'Зведена D5'!G20</f>
+        <f>'Зведена D5'!G19</f>
         <v/>
       </c>
       <c r="H11" s="95">
-        <f>'Зведена D5'!H20</f>
+        <f>'Зведена D5'!H19</f>
         <v/>
       </c>
       <c r="I11" s="95">
-        <f>'Зведена D5'!I20</f>
+        <f>'Зведена D5'!I19</f>
         <v/>
       </c>
       <c r="J11" s="95">
-        <f>'Зведена D5'!J20</f>
+        <f>'Зведена D5'!J19</f>
         <v/>
       </c>
       <c r="K11" s="95">
-        <f>'Зведена D5'!K20</f>
+        <f>'Зведена D5'!K19</f>
         <v/>
       </c>
       <c r="L11" s="95">
-        <f>'Зведена D5'!L20</f>
+        <f>'Зведена D5'!L19</f>
         <v/>
       </c>
       <c r="M11" s="95">
-        <f>'Зведена D5'!M20</f>
+        <f>'Зведена D5'!M19</f>
         <v/>
       </c>
       <c r="N11" s="95">
-        <f>'Зведена D5'!N20</f>
+        <f>'Зведена D5'!N19</f>
         <v/>
       </c>
       <c r="O11" s="95">
-        <f>'Зведена D5'!O20</f>
+        <f>'Зведена D5'!O19</f>
         <v/>
       </c>
       <c r="P11" s="95">
-        <f>'Зведена D5'!P20</f>
+        <f>'Зведена D5'!P19</f>
         <v/>
       </c>
       <c r="Q11" s="95">
-        <f>'Зведена D5'!Q20</f>
+        <f>'Зведена D5'!Q19</f>
         <v/>
       </c>
       <c r="R11" s="95">
-        <f>'Зведена D5'!R20</f>
+        <f>'Зведена D5'!R19</f>
         <v/>
       </c>
       <c r="S11" s="95">
-        <f>'Зведена D5'!S20</f>
-        <v/>
-      </c>
-      <c r="T11" s="96">
-        <f>IF(COUNTIF($F11:S11,"=*")&gt;0,IF($C11="К","-"," - "),IF(COUNTIF($F11:S11,"&lt;4")&gt;0,IF(C11="К","-"," - "),(IFERROR(AVERAGE($F11:S11),"Очікую"))))</f>
+        <f>'Зведена D5'!S19</f>
+        <v/>
+      </c>
+      <c r="T11" s="95">
+        <f>'Зведена D5'!T19</f>
         <v/>
       </c>
       <c r="U11" s="96">
-        <f>IFERROR(T11/12*90,"Очікую")</f>
-        <v/>
-      </c>
-      <c r="V11" s="22" t="n"/>
-      <c r="W11" s="39" t="n"/>
+        <f>IF(COUNTIF($F11:T11,"=*")&gt;0,IF($C11="К","-"," - "),IF(COUNTIF($F11:T11,"&lt;4")&gt;0,IF(C11="К","-"," - "),(IFERROR(AVERAGE($F11:T11),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V11" s="96">
+        <f>IFERROR(U11/12*90,"Очікую")</f>
+        <v/>
+      </c>
+      <c r="W11" s="22" t="n"/>
+      <c r="X11" s="39" t="n"/>
     </row>
     <row r="12" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A12" s="40" t="n"/>
@@ -8122,16 +8405,20 @@
         <f>'Зведена D5'!S23</f>
         <v/>
       </c>
-      <c r="T12" s="96">
-        <f>IF(COUNTIF($F12:S12,"=*")&gt;0,IF($C12="К","-"," - "),IF(COUNTIF($F12:S12,"&lt;4")&gt;0,IF(C12="К","-"," - "),(IFERROR(AVERAGE($F12:S12),"Очікую"))))</f>
+      <c r="T12" s="95">
+        <f>'Зведена D5'!T23</f>
         <v/>
       </c>
       <c r="U12" s="96">
-        <f>IFERROR(T12/12*90,"Очікую")</f>
-        <v/>
-      </c>
-      <c r="V12" s="22" t="n"/>
-      <c r="W12" s="39" t="n"/>
+        <f>IF(COUNTIF($F12:T12,"=*")&gt;0,IF($C12="К","-"," - "),IF(COUNTIF($F12:T12,"&lt;4")&gt;0,IF(C12="К","-"," - "),(IFERROR(AVERAGE($F12:T12),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V12" s="96">
+        <f>IFERROR(U12/12*90,"Очікую")</f>
+        <v/>
+      </c>
+      <c r="W12" s="22" t="n"/>
+      <c r="X12" s="39" t="n"/>
     </row>
     <row r="13" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A13" s="40" t="n"/>
@@ -8157,13 +8444,14 @@
       <c r="N13" s="6" t="n"/>
       <c r="O13" s="6" t="n"/>
       <c r="P13" s="6" t="n"/>
-      <c r="Q13" s="52" t="n"/>
+      <c r="Q13" s="6" t="n"/>
       <c r="R13" s="52" t="n"/>
       <c r="S13" s="52" t="n"/>
       <c r="T13" s="52" t="n"/>
       <c r="U13" s="52" t="n"/>
-      <c r="V13" s="20" t="n"/>
-      <c r="W13" s="39" t="n"/>
+      <c r="V13" s="52" t="n"/>
+      <c r="W13" s="20" t="n"/>
+      <c r="X13" s="39" t="n"/>
     </row>
     <row r="14" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A14" s="40" t="n"/>
@@ -8188,11 +8476,11 @@
       <c r="I14" s="55" t="n"/>
       <c r="J14" s="55" t="n"/>
       <c r="K14" s="55" t="n"/>
-      <c r="L14" s="6" t="n"/>
+      <c r="L14" s="55" t="n"/>
       <c r="M14" s="6" t="n"/>
       <c r="N14" s="6" t="n"/>
-      <c r="O14" s="56" t="n"/>
-      <c r="P14" s="54">
+      <c r="O14" s="6" t="n"/>
+      <c r="P14" s="56">
         <f>'Зведена D5'!P34</f>
         <v/>
       </c>
@@ -8201,8 +8489,9 @@
       <c r="S14" s="54" t="n"/>
       <c r="T14" s="54" t="n"/>
       <c r="U14" s="54" t="n"/>
-      <c r="V14" s="20" t="n"/>
-      <c r="W14" s="39" t="n"/>
+      <c r="V14" s="54" t="n"/>
+      <c r="W14" s="20" t="n"/>
+      <c r="X14" s="39" t="n"/>
     </row>
     <row r="15" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A15" s="40" t="n"/>
@@ -8223,18 +8512,19 @@
       <c r="I15" s="55" t="n"/>
       <c r="J15" s="55" t="n"/>
       <c r="K15" s="55" t="n"/>
-      <c r="L15" s="6" t="n"/>
+      <c r="L15" s="55" t="n"/>
       <c r="M15" s="6" t="n"/>
       <c r="N15" s="6" t="n"/>
-      <c r="O15" s="56" t="n"/>
-      <c r="P15" s="52" t="n"/>
+      <c r="O15" s="6" t="n"/>
+      <c r="P15" s="56" t="n"/>
       <c r="Q15" s="52" t="n"/>
       <c r="R15" s="52" t="n"/>
       <c r="S15" s="52" t="n"/>
       <c r="T15" s="52" t="n"/>
       <c r="U15" s="52" t="n"/>
-      <c r="V15" s="20" t="n"/>
-      <c r="W15" s="39" t="n"/>
+      <c r="V15" s="52" t="n"/>
+      <c r="W15" s="20" t="n"/>
+      <c r="X15" s="39" t="n"/>
     </row>
     <row r="16" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A16" s="40" t="n"/>
@@ -8259,11 +8549,11 @@
       <c r="I16" s="56" t="n"/>
       <c r="J16" s="56" t="n"/>
       <c r="K16" s="56" t="n"/>
-      <c r="L16" s="6" t="n"/>
+      <c r="L16" s="56" t="n"/>
       <c r="M16" s="6" t="n"/>
       <c r="N16" s="6" t="n"/>
-      <c r="O16" s="56" t="n"/>
-      <c r="P16" s="54" t="inlineStr">
+      <c r="O16" s="6" t="n"/>
+      <c r="P16" s="56" t="inlineStr">
         <is>
           <t>Маргарита БРІТІКОВА</t>
         </is>
@@ -8273,8 +8563,9 @@
       <c r="S16" s="54" t="n"/>
       <c r="T16" s="54" t="n"/>
       <c r="U16" s="54" t="n"/>
-      <c r="V16" s="20" t="n"/>
-      <c r="W16" s="39" t="n"/>
+      <c r="V16" s="54" t="n"/>
+      <c r="W16" s="20" t="n"/>
+      <c r="X16" s="39" t="n"/>
     </row>
     <row r="17" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A17" s="40" t="n"/>
@@ -8298,8 +8589,9 @@
       <c r="S17" s="14" t="n"/>
       <c r="T17" s="14" t="n"/>
       <c r="U17" s="14" t="n"/>
-      <c r="V17" s="15" t="n"/>
-      <c r="W17" s="39" t="n"/>
+      <c r="V17" s="14" t="n"/>
+      <c r="W17" s="15" t="n"/>
+      <c r="X17" s="39" t="n"/>
     </row>
     <row r="18" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A18" s="38" t="n"/>
@@ -8324,7 +8616,8 @@
       <c r="T18" s="38" t="n"/>
       <c r="U18" s="38" t="n"/>
       <c r="V18" s="38" t="n"/>
-      <c r="W18" s="39" t="n"/>
+      <c r="W18" s="38" t="n"/>
+      <c r="X18" s="39" t="n"/>
     </row>
     <row r="19" hidden="1" ht="15" customFormat="1" customHeight="1" s="11"/>
     <row r="20" hidden="1" ht="15" customFormat="1" customHeight="1" s="11"/>
@@ -8425,17 +8718,17 @@
     <row r="115" hidden="1" ht="12" customHeight="1"/>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="F8:S8"/>
     <mergeCell ref="E8:E9"/>
     <mergeCell ref="C8:C9"/>
-    <mergeCell ref="C5:U5"/>
+    <mergeCell ref="C4:V4"/>
     <mergeCell ref="U8:U9"/>
+    <mergeCell ref="C3:V3"/>
+    <mergeCell ref="V8:V9"/>
+    <mergeCell ref="C7:V7"/>
     <mergeCell ref="D8:D9"/>
-    <mergeCell ref="C7:U7"/>
-    <mergeCell ref="C4:U4"/>
-    <mergeCell ref="C3:U3"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="C6:U6"/>
+    <mergeCell ref="C6:V6"/>
+    <mergeCell ref="F8:T8"/>
+    <mergeCell ref="C5:V5"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.1968503937007874" right="0.1968503937007874" top="0.1968503937007874" bottom="0.1968503937007874" header="0" footer="0"/>
@@ -8450,7 +8743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:W32"/>
+  <dimension ref="A1:X32"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1"/>
   <cols>
     <col width="2.7109375" customWidth="1" style="1" min="1" max="2"/>
@@ -8458,11 +8751,10 @@
     <col width="6.5703125" customWidth="1" style="1" min="4" max="4"/>
     <col width="40.42578125" customWidth="1" style="1" min="5" max="5"/>
     <col width="6.7109375" customWidth="1" style="1" min="6" max="25"/>
-    <col width="11.3" customWidth="1" min="20" max="20"/>
     <col width="11.3" customWidth="1" min="21" max="21"/>
-    <col width="2.7" customWidth="1" min="22" max="22"/>
+    <col width="11.3" customWidth="1" min="22" max="22"/>
     <col width="2.7" customWidth="1" min="23" max="23"/>
-    <col hidden="1" width="13" customWidth="1" min="24" max="24"/>
+    <col width="2.7" customWidth="1" min="24" max="24"/>
     <col hidden="1" width="13" customWidth="1" min="25" max="25"/>
     <col hidden="1" width="11.28515625" customWidth="1" style="1" min="26" max="27"/>
     <col hidden="1" width="13" customWidth="1" min="27" max="27"/>
@@ -8503,6 +8795,7 @@
       <c r="U1" s="38" t="n"/>
       <c r="V1" s="38" t="n"/>
       <c r="W1" s="38" t="n"/>
+      <c r="X1" s="38" t="n"/>
     </row>
     <row r="2" ht="12" customHeight="1">
       <c r="A2" s="40" t="n"/>
@@ -8526,8 +8819,9 @@
       <c r="S2" s="29" t="n"/>
       <c r="T2" s="29" t="n"/>
       <c r="U2" s="29" t="n"/>
-      <c r="V2" s="30" t="n"/>
-      <c r="W2" s="39" t="n"/>
+      <c r="V2" s="29" t="n"/>
+      <c r="W2" s="30" t="n"/>
+      <c r="X2" s="39" t="n"/>
     </row>
     <row r="3" ht="54.95" customFormat="1" customHeight="1" s="2">
       <c r="A3" s="40" t="n"/>
@@ -8557,8 +8851,9 @@
       <c r="S3" s="86" t="n"/>
       <c r="T3" s="86" t="n"/>
       <c r="U3" s="86" t="n"/>
-      <c r="V3" s="32" t="n"/>
-      <c r="W3" s="39" t="n"/>
+      <c r="V3" s="86" t="n"/>
+      <c r="W3" s="32" t="n"/>
+      <c r="X3" s="39" t="n"/>
     </row>
     <row r="4" ht="15" customFormat="1" customHeight="1" s="3">
       <c r="A4" s="40" t="n"/>
@@ -8586,8 +8881,9 @@
       <c r="S4" s="86" t="n"/>
       <c r="T4" s="86" t="n"/>
       <c r="U4" s="86" t="n"/>
-      <c r="V4" s="32" t="n"/>
-      <c r="W4" s="39" t="n"/>
+      <c r="V4" s="86" t="n"/>
+      <c r="W4" s="32" t="n"/>
+      <c r="X4" s="39" t="n"/>
     </row>
     <row r="5" ht="15" customFormat="1" customHeight="1" s="2">
       <c r="A5" s="40" t="n"/>
@@ -8614,8 +8910,9 @@
       <c r="S5" s="87" t="n"/>
       <c r="T5" s="87" t="n"/>
       <c r="U5" s="87" t="n"/>
-      <c r="V5" s="32" t="n"/>
-      <c r="W5" s="39" t="n"/>
+      <c r="V5" s="87" t="n"/>
+      <c r="W5" s="32" t="n"/>
+      <c r="X5" s="39" t="n"/>
     </row>
     <row r="6" ht="15" customFormat="1" customHeight="1" s="2">
       <c r="A6" s="40" t="n"/>
@@ -8642,8 +8939,9 @@
       <c r="S6" s="87" t="n"/>
       <c r="T6" s="87" t="n"/>
       <c r="U6" s="87" t="n"/>
-      <c r="V6" s="32" t="n"/>
-      <c r="W6" s="39" t="n"/>
+      <c r="V6" s="87" t="n"/>
+      <c r="W6" s="32" t="n"/>
+      <c r="X6" s="39" t="n"/>
     </row>
     <row r="7" ht="15" customFormat="1" customHeight="1" s="2">
       <c r="A7" s="40" t="n"/>
@@ -8670,8 +8968,9 @@
       <c r="S7" s="88" t="n"/>
       <c r="T7" s="88" t="n"/>
       <c r="U7" s="88" t="n"/>
-      <c r="V7" s="32" t="n"/>
-      <c r="W7" s="39" t="n"/>
+      <c r="V7" s="88" t="n"/>
+      <c r="W7" s="32" t="n"/>
+      <c r="X7" s="39" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="40" t="n"/>
@@ -8709,19 +9008,20 @@
       <c r="P8" s="89" t="n"/>
       <c r="Q8" s="89" t="n"/>
       <c r="R8" s="89" t="n"/>
-      <c r="S8" s="90" t="n"/>
-      <c r="T8" s="91" t="inlineStr">
+      <c r="S8" s="89" t="n"/>
+      <c r="T8" s="90" t="n"/>
+      <c r="U8" s="91" t="inlineStr">
         <is>
           <t>Середній бал</t>
         </is>
       </c>
-      <c r="U8" s="91" t="inlineStr">
+      <c r="V8" s="91" t="inlineStr">
         <is>
           <t>Рейтинговий бал</t>
         </is>
       </c>
-      <c r="V8" s="32" t="n"/>
-      <c r="W8" s="39" t="n"/>
+      <c r="W8" s="32" t="n"/>
+      <c r="X8" s="39" t="n"/>
     </row>
     <row r="9" ht="125.1" customHeight="1">
       <c r="A9" s="40" t="n"/>
@@ -8785,10 +9085,14 @@
         <f>'Зведена D7'!S9</f>
         <v/>
       </c>
-      <c r="T9" s="92" t="n"/>
+      <c r="T9" s="50">
+        <f>'Зведена D7'!T9</f>
+        <v/>
+      </c>
       <c r="U9" s="92" t="n"/>
-      <c r="V9" s="32" t="n"/>
-      <c r="W9" s="39" t="n"/>
+      <c r="V9" s="92" t="n"/>
+      <c r="W9" s="32" t="n"/>
+      <c r="X9" s="39" t="n"/>
     </row>
     <row r="10" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A10" s="40" t="n"/>
@@ -8860,583 +9164,615 @@
         <f>'Зведена D7'!S33</f>
         <v/>
       </c>
-      <c r="T10" s="97">
-        <f>IF(COUNTIF($F10:S10,"=*")&gt;0,IF($C10="К","-"," - "),IF(COUNTIF($F10:S10,"&lt;4")&gt;0,IF(C10="К","-"," - "),(IFERROR(AVERAGE($F10:S10),"Очікую"))))</f>
+      <c r="T10" s="93">
+        <f>'Зведена D7'!T33</f>
         <v/>
       </c>
       <c r="U10" s="97">
-        <f>IFERROR(T10/12*90,"Очікую")</f>
-        <v/>
-      </c>
-      <c r="V10" s="33" t="n"/>
-      <c r="W10" s="39" t="n"/>
+        <f>IF(COUNTIF($F10:T10,"=*")&gt;0,IF($C10="К","-"," - "),IF(COUNTIF($F10:T10,"&lt;4")&gt;0,IF(C10="К","-"," - "),(IFERROR(AVERAGE($F10:T10),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V10" s="97">
+        <f>IFERROR(U10/12*90,"Очікую")</f>
+        <v/>
+      </c>
+      <c r="W10" s="33" t="n"/>
+      <c r="X10" s="39" t="n"/>
     </row>
     <row r="11" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A11" s="40" t="n"/>
       <c r="B11" s="31" t="n"/>
       <c r="C11" s="93">
-        <f>'Зведена D7'!C17</f>
+        <f>'Зведена D7'!C27</f>
         <v/>
       </c>
       <c r="D11" s="93" t="n">
         <v>2</v>
       </c>
       <c r="E11" s="94">
-        <f>'Зведена D7'!E17</f>
+        <f>'Зведена D7'!E27</f>
         <v/>
       </c>
       <c r="F11" s="93">
-        <f>'Зведена D7'!F17</f>
+        <f>'Зведена D7'!F27</f>
         <v/>
       </c>
       <c r="G11" s="93">
-        <f>'Зведена D7'!G17</f>
+        <f>'Зведена D7'!G27</f>
         <v/>
       </c>
       <c r="H11" s="93">
-        <f>'Зведена D7'!H17</f>
+        <f>'Зведена D7'!H27</f>
         <v/>
       </c>
       <c r="I11" s="93">
-        <f>'Зведена D7'!I17</f>
+        <f>'Зведена D7'!I27</f>
         <v/>
       </c>
       <c r="J11" s="93">
-        <f>'Зведена D7'!J17</f>
+        <f>'Зведена D7'!J27</f>
         <v/>
       </c>
       <c r="K11" s="93">
-        <f>'Зведена D7'!K17</f>
+        <f>'Зведена D7'!K27</f>
         <v/>
       </c>
       <c r="L11" s="93">
-        <f>'Зведена D7'!L17</f>
+        <f>'Зведена D7'!L27</f>
         <v/>
       </c>
       <c r="M11" s="93">
-        <f>'Зведена D7'!M17</f>
+        <f>'Зведена D7'!M27</f>
         <v/>
       </c>
       <c r="N11" s="93">
-        <f>'Зведена D7'!N17</f>
+        <f>'Зведена D7'!N27</f>
         <v/>
       </c>
       <c r="O11" s="93">
-        <f>'Зведена D7'!O17</f>
+        <f>'Зведена D7'!O27</f>
         <v/>
       </c>
       <c r="P11" s="93">
-        <f>'Зведена D7'!P17</f>
+        <f>'Зведена D7'!P27</f>
         <v/>
       </c>
       <c r="Q11" s="93">
-        <f>'Зведена D7'!Q17</f>
+        <f>'Зведена D7'!Q27</f>
         <v/>
       </c>
       <c r="R11" s="93">
-        <f>'Зведена D7'!R17</f>
+        <f>'Зведена D7'!R27</f>
         <v/>
       </c>
       <c r="S11" s="93">
-        <f>'Зведена D7'!S17</f>
-        <v/>
-      </c>
-      <c r="T11" s="97">
-        <f>IF(COUNTIF($F11:S11,"=*")&gt;0,IF($C11="К","-"," - "),IF(COUNTIF($F11:S11,"&lt;4")&gt;0,IF(C11="К","-"," - "),(IFERROR(AVERAGE($F11:S11),"Очікую"))))</f>
+        <f>'Зведена D7'!S27</f>
+        <v/>
+      </c>
+      <c r="T11" s="93">
+        <f>'Зведена D7'!T27</f>
         <v/>
       </c>
       <c r="U11" s="97">
-        <f>IFERROR(T11/12*90,"Очікую")</f>
-        <v/>
-      </c>
-      <c r="V11" s="33" t="n"/>
-      <c r="W11" s="39" t="n"/>
+        <f>IF(COUNTIF($F11:T11,"=*")&gt;0,IF($C11="К","-"," - "),IF(COUNTIF($F11:T11,"&lt;4")&gt;0,IF(C11="К","-"," - "),(IFERROR(AVERAGE($F11:T11),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V11" s="97">
+        <f>IFERROR(U11/12*90,"Очікую")</f>
+        <v/>
+      </c>
+      <c r="W11" s="33" t="n"/>
+      <c r="X11" s="39" t="n"/>
     </row>
     <row r="12" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A12" s="40" t="n"/>
       <c r="B12" s="31" t="n"/>
       <c r="C12" s="93">
-        <f>'Зведена D7'!C27</f>
+        <f>'Зведена D7'!C17</f>
         <v/>
       </c>
       <c r="D12" s="93" t="n">
         <v>3</v>
       </c>
       <c r="E12" s="94">
-        <f>'Зведена D7'!E27</f>
+        <f>'Зведена D7'!E17</f>
         <v/>
       </c>
       <c r="F12" s="93">
-        <f>'Зведена D7'!F27</f>
+        <f>'Зведена D7'!F17</f>
         <v/>
       </c>
       <c r="G12" s="93">
-        <f>'Зведена D7'!G27</f>
+        <f>'Зведена D7'!G17</f>
         <v/>
       </c>
       <c r="H12" s="93">
-        <f>'Зведена D7'!H27</f>
+        <f>'Зведена D7'!H17</f>
         <v/>
       </c>
       <c r="I12" s="93">
-        <f>'Зведена D7'!I27</f>
+        <f>'Зведена D7'!I17</f>
         <v/>
       </c>
       <c r="J12" s="93">
-        <f>'Зведена D7'!J27</f>
+        <f>'Зведена D7'!J17</f>
         <v/>
       </c>
       <c r="K12" s="93">
-        <f>'Зведена D7'!K27</f>
+        <f>'Зведена D7'!K17</f>
         <v/>
       </c>
       <c r="L12" s="93">
-        <f>'Зведена D7'!L27</f>
+        <f>'Зведена D7'!L17</f>
         <v/>
       </c>
       <c r="M12" s="93">
-        <f>'Зведена D7'!M27</f>
+        <f>'Зведена D7'!M17</f>
         <v/>
       </c>
       <c r="N12" s="93">
-        <f>'Зведена D7'!N27</f>
+        <f>'Зведена D7'!N17</f>
         <v/>
       </c>
       <c r="O12" s="93">
-        <f>'Зведена D7'!O27</f>
+        <f>'Зведена D7'!O17</f>
         <v/>
       </c>
       <c r="P12" s="93">
-        <f>'Зведена D7'!P27</f>
+        <f>'Зведена D7'!P17</f>
         <v/>
       </c>
       <c r="Q12" s="93">
-        <f>'Зведена D7'!Q27</f>
+        <f>'Зведена D7'!Q17</f>
         <v/>
       </c>
       <c r="R12" s="93">
-        <f>'Зведена D7'!R27</f>
+        <f>'Зведена D7'!R17</f>
         <v/>
       </c>
       <c r="S12" s="93">
-        <f>'Зведена D7'!S27</f>
-        <v/>
-      </c>
-      <c r="T12" s="97">
-        <f>IF(COUNTIF($F12:S12,"=*")&gt;0,IF($C12="К","-"," - "),IF(COUNTIF($F12:S12,"&lt;4")&gt;0,IF(C12="К","-"," - "),(IFERROR(AVERAGE($F12:S12),"Очікую"))))</f>
+        <f>'Зведена D7'!S17</f>
+        <v/>
+      </c>
+      <c r="T12" s="93">
+        <f>'Зведена D7'!T17</f>
         <v/>
       </c>
       <c r="U12" s="97">
-        <f>IFERROR(T12/12*90,"Очікую")</f>
-        <v/>
-      </c>
-      <c r="V12" s="33" t="n"/>
-      <c r="W12" s="39" t="n"/>
+        <f>IF(COUNTIF($F12:T12,"=*")&gt;0,IF($C12="К","-"," - "),IF(COUNTIF($F12:T12,"&lt;4")&gt;0,IF(C12="К","-"," - "),(IFERROR(AVERAGE($F12:T12),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V12" s="97">
+        <f>IFERROR(U12/12*90,"Очікую")</f>
+        <v/>
+      </c>
+      <c r="W12" s="33" t="n"/>
+      <c r="X12" s="39" t="n"/>
     </row>
     <row r="13" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A13" s="40" t="n"/>
       <c r="B13" s="31" t="n"/>
       <c r="C13" s="93">
-        <f>'Зведена D7'!C22</f>
+        <f>'Зведена D7'!C14</f>
         <v/>
       </c>
       <c r="D13" s="93" t="n">
         <v>4</v>
       </c>
       <c r="E13" s="94">
-        <f>'Зведена D7'!E22</f>
+        <f>'Зведена D7'!E14</f>
         <v/>
       </c>
       <c r="F13" s="93">
-        <f>'Зведена D7'!F22</f>
+        <f>'Зведена D7'!F14</f>
         <v/>
       </c>
       <c r="G13" s="93">
-        <f>'Зведена D7'!G22</f>
+        <f>'Зведена D7'!G14</f>
         <v/>
       </c>
       <c r="H13" s="93">
-        <f>'Зведена D7'!H22</f>
+        <f>'Зведена D7'!H14</f>
         <v/>
       </c>
       <c r="I13" s="93">
-        <f>'Зведена D7'!I22</f>
+        <f>'Зведена D7'!I14</f>
         <v/>
       </c>
       <c r="J13" s="93">
-        <f>'Зведена D7'!J22</f>
+        <f>'Зведена D7'!J14</f>
         <v/>
       </c>
       <c r="K13" s="93">
-        <f>'Зведена D7'!K22</f>
+        <f>'Зведена D7'!K14</f>
         <v/>
       </c>
       <c r="L13" s="93">
-        <f>'Зведена D7'!L22</f>
+        <f>'Зведена D7'!L14</f>
         <v/>
       </c>
       <c r="M13" s="93">
-        <f>'Зведена D7'!M22</f>
+        <f>'Зведена D7'!M14</f>
         <v/>
       </c>
       <c r="N13" s="93">
-        <f>'Зведена D7'!N22</f>
+        <f>'Зведена D7'!N14</f>
         <v/>
       </c>
       <c r="O13" s="93">
-        <f>'Зведена D7'!O22</f>
+        <f>'Зведена D7'!O14</f>
         <v/>
       </c>
       <c r="P13" s="93">
-        <f>'Зведена D7'!P22</f>
+        <f>'Зведена D7'!P14</f>
         <v/>
       </c>
       <c r="Q13" s="93">
-        <f>'Зведена D7'!Q22</f>
+        <f>'Зведена D7'!Q14</f>
         <v/>
       </c>
       <c r="R13" s="93">
-        <f>'Зведена D7'!R22</f>
+        <f>'Зведена D7'!R14</f>
         <v/>
       </c>
       <c r="S13" s="93">
-        <f>'Зведена D7'!S22</f>
-        <v/>
-      </c>
-      <c r="T13" s="97">
-        <f>IF(COUNTIF($F13:S13,"=*")&gt;0,IF($C13="К","-"," - "),IF(COUNTIF($F13:S13,"&lt;4")&gt;0,IF(C13="К","-"," - "),(IFERROR(AVERAGE($F13:S13),"Очікую"))))</f>
+        <f>'Зведена D7'!S14</f>
+        <v/>
+      </c>
+      <c r="T13" s="93">
+        <f>'Зведена D7'!T14</f>
         <v/>
       </c>
       <c r="U13" s="97">
-        <f>IFERROR(T13/12*90,"Очікую")</f>
-        <v/>
-      </c>
-      <c r="V13" s="33" t="n"/>
-      <c r="W13" s="39" t="n"/>
+        <f>IF(COUNTIF($F13:T13,"=*")&gt;0,IF($C13="К","-"," - "),IF(COUNTIF($F13:T13,"&lt;4")&gt;0,IF(C13="К","-"," - "),(IFERROR(AVERAGE($F13:T13),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V13" s="97">
+        <f>IFERROR(U13/12*90,"Очікую")</f>
+        <v/>
+      </c>
+      <c r="W13" s="33" t="n"/>
+      <c r="X13" s="39" t="n"/>
     </row>
     <row r="14" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A14" s="40" t="n"/>
       <c r="B14" s="31" t="n"/>
       <c r="C14" s="93">
-        <f>'Зведена D7'!C14</f>
+        <f>'Зведена D7'!C22</f>
         <v/>
       </c>
       <c r="D14" s="93" t="n">
         <v>5</v>
       </c>
       <c r="E14" s="94">
-        <f>'Зведена D7'!E14</f>
+        <f>'Зведена D7'!E22</f>
         <v/>
       </c>
       <c r="F14" s="93">
-        <f>'Зведена D7'!F14</f>
+        <f>'Зведена D7'!F22</f>
         <v/>
       </c>
       <c r="G14" s="93">
-        <f>'Зведена D7'!G14</f>
+        <f>'Зведена D7'!G22</f>
         <v/>
       </c>
       <c r="H14" s="93">
-        <f>'Зведена D7'!H14</f>
+        <f>'Зведена D7'!H22</f>
         <v/>
       </c>
       <c r="I14" s="93">
-        <f>'Зведена D7'!I14</f>
+        <f>'Зведена D7'!I22</f>
         <v/>
       </c>
       <c r="J14" s="93">
-        <f>'Зведена D7'!J14</f>
+        <f>'Зведена D7'!J22</f>
         <v/>
       </c>
       <c r="K14" s="93">
-        <f>'Зведена D7'!K14</f>
+        <f>'Зведена D7'!K22</f>
         <v/>
       </c>
       <c r="L14" s="93">
-        <f>'Зведена D7'!L14</f>
+        <f>'Зведена D7'!L22</f>
         <v/>
       </c>
       <c r="M14" s="93">
-        <f>'Зведена D7'!M14</f>
+        <f>'Зведена D7'!M22</f>
         <v/>
       </c>
       <c r="N14" s="93">
-        <f>'Зведена D7'!N14</f>
+        <f>'Зведена D7'!N22</f>
         <v/>
       </c>
       <c r="O14" s="93">
-        <f>'Зведена D7'!O14</f>
+        <f>'Зведена D7'!O22</f>
         <v/>
       </c>
       <c r="P14" s="93">
-        <f>'Зведена D7'!P14</f>
+        <f>'Зведена D7'!P22</f>
         <v/>
       </c>
       <c r="Q14" s="93">
-        <f>'Зведена D7'!Q14</f>
+        <f>'Зведена D7'!Q22</f>
         <v/>
       </c>
       <c r="R14" s="93">
-        <f>'Зведена D7'!R14</f>
+        <f>'Зведена D7'!R22</f>
         <v/>
       </c>
       <c r="S14" s="93">
-        <f>'Зведена D7'!S14</f>
-        <v/>
-      </c>
-      <c r="T14" s="97">
-        <f>IF(COUNTIF($F14:S14,"=*")&gt;0,IF($C14="К","-"," - "),IF(COUNTIF($F14:S14,"&lt;4")&gt;0,IF(C14="К","-"," - "),(IFERROR(AVERAGE($F14:S14),"Очікую"))))</f>
+        <f>'Зведена D7'!S22</f>
+        <v/>
+      </c>
+      <c r="T14" s="93">
+        <f>'Зведена D7'!T22</f>
         <v/>
       </c>
       <c r="U14" s="97">
-        <f>IFERROR(T14/12*90,"Очікую")</f>
-        <v/>
-      </c>
-      <c r="V14" s="33" t="n"/>
-      <c r="W14" s="39" t="n"/>
+        <f>IF(COUNTIF($F14:T14,"=*")&gt;0,IF($C14="К","-"," - "),IF(COUNTIF($F14:T14,"&lt;4")&gt;0,IF(C14="К","-"," - "),(IFERROR(AVERAGE($F14:T14),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V14" s="97">
+        <f>IFERROR(U14/12*90,"Очікую")</f>
+        <v/>
+      </c>
+      <c r="W14" s="33" t="n"/>
+      <c r="X14" s="39" t="n"/>
     </row>
     <row r="15" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A15" s="40" t="n"/>
       <c r="B15" s="31" t="n"/>
       <c r="C15" s="47">
-        <f>'Зведена D7'!C32</f>
+        <f>'Зведена D7'!C18</f>
         <v/>
       </c>
       <c r="D15" s="47" t="n">
         <v>6</v>
       </c>
       <c r="E15" s="48">
-        <f>'Зведена D7'!E32</f>
+        <f>'Зведена D7'!E18</f>
         <v/>
       </c>
       <c r="F15" s="47">
-        <f>'Зведена D7'!F32</f>
+        <f>'Зведена D7'!F18</f>
         <v/>
       </c>
       <c r="G15" s="47">
-        <f>'Зведена D7'!G32</f>
+        <f>'Зведена D7'!G18</f>
         <v/>
       </c>
       <c r="H15" s="47">
-        <f>'Зведена D7'!H32</f>
+        <f>'Зведена D7'!H18</f>
         <v/>
       </c>
       <c r="I15" s="47">
-        <f>'Зведена D7'!I32</f>
+        <f>'Зведена D7'!I18</f>
         <v/>
       </c>
       <c r="J15" s="47">
-        <f>'Зведена D7'!J32</f>
+        <f>'Зведена D7'!J18</f>
         <v/>
       </c>
       <c r="K15" s="47">
-        <f>'Зведена D7'!K32</f>
+        <f>'Зведена D7'!K18</f>
         <v/>
       </c>
       <c r="L15" s="47">
-        <f>'Зведена D7'!L32</f>
+        <f>'Зведена D7'!L18</f>
         <v/>
       </c>
       <c r="M15" s="47">
-        <f>'Зведена D7'!M32</f>
+        <f>'Зведена D7'!M18</f>
         <v/>
       </c>
       <c r="N15" s="47">
-        <f>'Зведена D7'!N32</f>
+        <f>'Зведена D7'!N18</f>
         <v/>
       </c>
       <c r="O15" s="47">
-        <f>'Зведена D7'!O32</f>
+        <f>'Зведена D7'!O18</f>
         <v/>
       </c>
       <c r="P15" s="47">
-        <f>'Зведена D7'!P32</f>
+        <f>'Зведена D7'!P18</f>
         <v/>
       </c>
       <c r="Q15" s="47">
-        <f>'Зведена D7'!Q32</f>
+        <f>'Зведена D7'!Q18</f>
         <v/>
       </c>
       <c r="R15" s="47">
-        <f>'Зведена D7'!R32</f>
+        <f>'Зведена D7'!R18</f>
         <v/>
       </c>
       <c r="S15" s="47">
-        <f>'Зведена D7'!S32</f>
-        <v/>
-      </c>
-      <c r="T15" s="51">
-        <f>IF(COUNTIF($F15:S15,"=*")&gt;0,IF($C15="К","-"," - "),IF(COUNTIF($F15:S15,"&lt;4")&gt;0,IF(C15="К","-"," - "),(IFERROR(AVERAGE($F15:S15),"Очікую"))))</f>
+        <f>'Зведена D7'!S18</f>
+        <v/>
+      </c>
+      <c r="T15" s="47">
+        <f>'Зведена D7'!T18</f>
         <v/>
       </c>
       <c r="U15" s="51">
-        <f>IFERROR(T15/12*90,"Очікую")</f>
-        <v/>
-      </c>
-      <c r="V15" s="33" t="n"/>
-      <c r="W15" s="39" t="n"/>
+        <f>IF(COUNTIF($F15:T15,"=*")&gt;0,IF($C15="К","-"," - "),IF(COUNTIF($F15:T15,"&lt;4")&gt;0,IF(C15="К","-"," - "),(IFERROR(AVERAGE($F15:T15),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V15" s="51">
+        <f>IFERROR(U15/12*90,"Очікую")</f>
+        <v/>
+      </c>
+      <c r="W15" s="33" t="n"/>
+      <c r="X15" s="39" t="n"/>
     </row>
     <row r="16" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A16" s="40" t="n"/>
       <c r="B16" s="31" t="n"/>
       <c r="C16" s="47">
-        <f>'Зведена D7'!C20</f>
+        <f>'Зведена D7'!C32</f>
         <v/>
       </c>
       <c r="D16" s="47" t="n">
         <v>7</v>
       </c>
       <c r="E16" s="48">
-        <f>'Зведена D7'!E20</f>
+        <f>'Зведена D7'!E32</f>
         <v/>
       </c>
       <c r="F16" s="47">
-        <f>'Зведена D7'!F20</f>
+        <f>'Зведена D7'!F32</f>
         <v/>
       </c>
       <c r="G16" s="47">
-        <f>'Зведена D7'!G20</f>
+        <f>'Зведена D7'!G32</f>
         <v/>
       </c>
       <c r="H16" s="47">
-        <f>'Зведена D7'!H20</f>
+        <f>'Зведена D7'!H32</f>
         <v/>
       </c>
       <c r="I16" s="47">
-        <f>'Зведена D7'!I20</f>
+        <f>'Зведена D7'!I32</f>
         <v/>
       </c>
       <c r="J16" s="47">
-        <f>'Зведена D7'!J20</f>
+        <f>'Зведена D7'!J32</f>
         <v/>
       </c>
       <c r="K16" s="47">
-        <f>'Зведена D7'!K20</f>
+        <f>'Зведена D7'!K32</f>
         <v/>
       </c>
       <c r="L16" s="47">
-        <f>'Зведена D7'!L20</f>
+        <f>'Зведена D7'!L32</f>
         <v/>
       </c>
       <c r="M16" s="47">
-        <f>'Зведена D7'!M20</f>
+        <f>'Зведена D7'!M32</f>
         <v/>
       </c>
       <c r="N16" s="47">
-        <f>'Зведена D7'!N20</f>
+        <f>'Зведена D7'!N32</f>
         <v/>
       </c>
       <c r="O16" s="47">
-        <f>'Зведена D7'!O20</f>
+        <f>'Зведена D7'!O32</f>
         <v/>
       </c>
       <c r="P16" s="47">
-        <f>'Зведена D7'!P20</f>
+        <f>'Зведена D7'!P32</f>
         <v/>
       </c>
       <c r="Q16" s="47">
-        <f>'Зведена D7'!Q20</f>
+        <f>'Зведена D7'!Q32</f>
         <v/>
       </c>
       <c r="R16" s="47">
-        <f>'Зведена D7'!R20</f>
+        <f>'Зведена D7'!R32</f>
         <v/>
       </c>
       <c r="S16" s="47">
-        <f>'Зведена D7'!S20</f>
-        <v/>
-      </c>
-      <c r="T16" s="51">
-        <f>IF(COUNTIF($F16:S16,"=*")&gt;0,IF($C16="К","-"," - "),IF(COUNTIF($F16:S16,"&lt;4")&gt;0,IF(C16="К","-"," - "),(IFERROR(AVERAGE($F16:S16),"Очікую"))))</f>
+        <f>'Зведена D7'!S32</f>
+        <v/>
+      </c>
+      <c r="T16" s="47">
+        <f>'Зведена D7'!T32</f>
         <v/>
       </c>
       <c r="U16" s="51">
-        <f>IFERROR(T16/12*90,"Очікую")</f>
-        <v/>
-      </c>
-      <c r="V16" s="33" t="n"/>
-      <c r="W16" s="39" t="n"/>
+        <f>IF(COUNTIF($F16:T16,"=*")&gt;0,IF($C16="К","-"," - "),IF(COUNTIF($F16:T16,"&lt;4")&gt;0,IF(C16="К","-"," - "),(IFERROR(AVERAGE($F16:T16),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V16" s="51">
+        <f>IFERROR(U16/12*90,"Очікую")</f>
+        <v/>
+      </c>
+      <c r="W16" s="33" t="n"/>
+      <c r="X16" s="39" t="n"/>
     </row>
     <row r="17" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A17" s="40" t="n"/>
       <c r="B17" s="31" t="n"/>
       <c r="C17" s="47">
-        <f>'Зведена D7'!C18</f>
+        <f>'Зведена D7'!C20</f>
         <v/>
       </c>
       <c r="D17" s="47" t="n">
         <v>8</v>
       </c>
       <c r="E17" s="48">
-        <f>'Зведена D7'!E18</f>
+        <f>'Зведена D7'!E20</f>
         <v/>
       </c>
       <c r="F17" s="47">
-        <f>'Зведена D7'!F18</f>
+        <f>'Зведена D7'!F20</f>
         <v/>
       </c>
       <c r="G17" s="47">
-        <f>'Зведена D7'!G18</f>
+        <f>'Зведена D7'!G20</f>
         <v/>
       </c>
       <c r="H17" s="47">
-        <f>'Зведена D7'!H18</f>
+        <f>'Зведена D7'!H20</f>
         <v/>
       </c>
       <c r="I17" s="47">
-        <f>'Зведена D7'!I18</f>
+        <f>'Зведена D7'!I20</f>
         <v/>
       </c>
       <c r="J17" s="47">
-        <f>'Зведена D7'!J18</f>
+        <f>'Зведена D7'!J20</f>
         <v/>
       </c>
       <c r="K17" s="47">
-        <f>'Зведена D7'!K18</f>
+        <f>'Зведена D7'!K20</f>
         <v/>
       </c>
       <c r="L17" s="47">
-        <f>'Зведена D7'!L18</f>
+        <f>'Зведена D7'!L20</f>
         <v/>
       </c>
       <c r="M17" s="47">
-        <f>'Зведена D7'!M18</f>
+        <f>'Зведена D7'!M20</f>
         <v/>
       </c>
       <c r="N17" s="47">
-        <f>'Зведена D7'!N18</f>
+        <f>'Зведена D7'!N20</f>
         <v/>
       </c>
       <c r="O17" s="47">
-        <f>'Зведена D7'!O18</f>
+        <f>'Зведена D7'!O20</f>
         <v/>
       </c>
       <c r="P17" s="47">
-        <f>'Зведена D7'!P18</f>
+        <f>'Зведена D7'!P20</f>
         <v/>
       </c>
       <c r="Q17" s="47">
-        <f>'Зведена D7'!Q18</f>
+        <f>'Зведена D7'!Q20</f>
         <v/>
       </c>
       <c r="R17" s="47">
-        <f>'Зведена D7'!R18</f>
+        <f>'Зведена D7'!R20</f>
         <v/>
       </c>
       <c r="S17" s="47">
-        <f>'Зведена D7'!S18</f>
-        <v/>
-      </c>
-      <c r="T17" s="51">
-        <f>IF(COUNTIF($F17:S17,"=*")&gt;0,IF($C17="К","-"," - "),IF(COUNTIF($F17:S17,"&lt;4")&gt;0,IF(C17="К","-"," - "),(IFERROR(AVERAGE($F17:S17),"Очікую"))))</f>
+        <f>'Зведена D7'!S20</f>
+        <v/>
+      </c>
+      <c r="T17" s="47">
+        <f>'Зведена D7'!T20</f>
         <v/>
       </c>
       <c r="U17" s="51">
-        <f>IFERROR(T17/12*90,"Очікую")</f>
-        <v/>
-      </c>
-      <c r="V17" s="33" t="n"/>
-      <c r="W17" s="39" t="n"/>
+        <f>IF(COUNTIF($F17:T17,"=*")&gt;0,IF($C17="К","-"," - "),IF(COUNTIF($F17:T17,"&lt;4")&gt;0,IF(C17="К","-"," - "),(IFERROR(AVERAGE($F17:T17),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V17" s="51">
+        <f>IFERROR(U17/12*90,"Очікую")</f>
+        <v/>
+      </c>
+      <c r="W17" s="33" t="n"/>
+      <c r="X17" s="39" t="n"/>
     </row>
     <row r="18" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A18" s="40" t="n"/>
@@ -9508,16 +9844,20 @@
         <f>'Зведена D7'!S10</f>
         <v/>
       </c>
-      <c r="T18" s="51">
-        <f>IF(COUNTIF($F18:S18,"=*")&gt;0,IF($C18="К","-"," - "),IF(COUNTIF($F18:S18,"&lt;4")&gt;0,IF(C18="К","-"," - "),(IFERROR(AVERAGE($F18:S18),"Очікую"))))</f>
+      <c r="T18" s="47">
+        <f>'Зведена D7'!T10</f>
         <v/>
       </c>
       <c r="U18" s="51">
-        <f>IFERROR(T18/12*90,"Очікую")</f>
-        <v/>
-      </c>
-      <c r="V18" s="33" t="n"/>
-      <c r="W18" s="39" t="n"/>
+        <f>IF(COUNTIF($F18:T18,"=*")&gt;0,IF($C18="К","-"," - "),IF(COUNTIF($F18:T18,"&lt;4")&gt;0,IF(C18="К","-"," - "),(IFERROR(AVERAGE($F18:T18),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V18" s="51">
+        <f>IFERROR(U18/12*90,"Очікую")</f>
+        <v/>
+      </c>
+      <c r="W18" s="33" t="n"/>
+      <c r="X18" s="39" t="n"/>
     </row>
     <row r="19" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A19" s="40" t="n"/>
@@ -9589,16 +9929,20 @@
         <f>'Зведена D7'!S11</f>
         <v/>
       </c>
-      <c r="T19" s="51">
-        <f>IF(COUNTIF($F19:S19,"=*")&gt;0,IF($C19="К","-"," - "),IF(COUNTIF($F19:S19,"&lt;4")&gt;0,IF(C19="К","-"," - "),(IFERROR(AVERAGE($F19:S19),"Очікую"))))</f>
+      <c r="T19" s="47">
+        <f>'Зведена D7'!T11</f>
         <v/>
       </c>
       <c r="U19" s="51">
-        <f>IFERROR(T19/12*90,"Очікую")</f>
-        <v/>
-      </c>
-      <c r="V19" s="33" t="n"/>
-      <c r="W19" s="39" t="n"/>
+        <f>IF(COUNTIF($F19:T19,"=*")&gt;0,IF($C19="К","-"," - "),IF(COUNTIF($F19:T19,"&lt;4")&gt;0,IF(C19="К","-"," - "),(IFERROR(AVERAGE($F19:T19),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V19" s="51">
+        <f>IFERROR(U19/12*90,"Очікую")</f>
+        <v/>
+      </c>
+      <c r="W19" s="33" t="n"/>
+      <c r="X19" s="39" t="n"/>
     </row>
     <row r="20" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A20" s="40" t="n"/>
@@ -9670,16 +10014,20 @@
         <f>'Зведена D7'!S16</f>
         <v/>
       </c>
-      <c r="T20" s="51">
-        <f>IF(COUNTIF($F20:S20,"=*")&gt;0,IF($C20="К","-"," - "),IF(COUNTIF($F20:S20,"&lt;4")&gt;0,IF(C20="К","-"," - "),(IFERROR(AVERAGE($F20:S20),"Очікую"))))</f>
+      <c r="T20" s="47">
+        <f>'Зведена D7'!T16</f>
         <v/>
       </c>
       <c r="U20" s="51">
-        <f>IFERROR(T20/12*90,"Очікую")</f>
-        <v/>
-      </c>
-      <c r="V20" s="33" t="n"/>
-      <c r="W20" s="39" t="n"/>
+        <f>IF(COUNTIF($F20:T20,"=*")&gt;0,IF($C20="К","-"," - "),IF(COUNTIF($F20:T20,"&lt;4")&gt;0,IF(C20="К","-"," - "),(IFERROR(AVERAGE($F20:T20),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V20" s="51">
+        <f>IFERROR(U20/12*90,"Очікую")</f>
+        <v/>
+      </c>
+      <c r="W20" s="33" t="n"/>
+      <c r="X20" s="39" t="n"/>
     </row>
     <row r="21" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A21" s="40" t="n"/>
@@ -9751,16 +10099,20 @@
         <f>'Зведена D7'!S24</f>
         <v/>
       </c>
-      <c r="T21" s="51">
-        <f>IF(COUNTIF($F21:S21,"=*")&gt;0,IF($C21="К","-"," - "),IF(COUNTIF($F21:S21,"&lt;4")&gt;0,IF(C21="К","-"," - "),(IFERROR(AVERAGE($F21:S21),"Очікую"))))</f>
+      <c r="T21" s="47">
+        <f>'Зведена D7'!T24</f>
         <v/>
       </c>
       <c r="U21" s="51">
-        <f>IFERROR(T21/12*90,"Очікую")</f>
-        <v/>
-      </c>
-      <c r="V21" s="33" t="n"/>
-      <c r="W21" s="39" t="n"/>
+        <f>IF(COUNTIF($F21:T21,"=*")&gt;0,IF($C21="К","-"," - "),IF(COUNTIF($F21:T21,"&lt;4")&gt;0,IF(C21="К","-"," - "),(IFERROR(AVERAGE($F21:T21),"Очікую"))))</f>
+        <v/>
+      </c>
+      <c r="V21" s="51">
+        <f>IFERROR(U21/12*90,"Очікую")</f>
+        <v/>
+      </c>
+      <c r="W21" s="33" t="n"/>
+      <c r="X21" s="39" t="n"/>
     </row>
     <row r="22" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A22" s="40" t="n"/>
@@ -9784,15 +10136,16 @@
       <c r="L22" s="24" t="n"/>
       <c r="M22" s="24" t="n"/>
       <c r="N22" s="24" t="n"/>
-      <c r="O22" s="27" t="n"/>
-      <c r="P22" s="26" t="n"/>
-      <c r="Q22" s="24" t="n"/>
+      <c r="O22" s="24" t="n"/>
+      <c r="P22" s="27" t="n"/>
+      <c r="Q22" s="26" t="n"/>
       <c r="R22" s="24" t="n"/>
       <c r="S22" s="24" t="n"/>
       <c r="T22" s="24" t="n"/>
       <c r="U22" s="24" t="n"/>
-      <c r="V22" s="32" t="n"/>
-      <c r="W22" s="39" t="n"/>
+      <c r="V22" s="24" t="n"/>
+      <c r="W22" s="32" t="n"/>
+      <c r="X22" s="39" t="n"/>
     </row>
     <row r="23" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A23" s="40" t="n"/>
@@ -9817,10 +10170,10 @@
       <c r="I23" s="55" t="n"/>
       <c r="J23" s="55" t="n"/>
       <c r="K23" s="55" t="n"/>
-      <c r="L23" s="6" t="n"/>
+      <c r="L23" s="55" t="n"/>
       <c r="M23" s="6" t="n"/>
       <c r="N23" s="6" t="n"/>
-      <c r="O23" s="56" t="n"/>
+      <c r="O23" s="6" t="n"/>
       <c r="P23" s="56">
         <f>'Зведена D7'!P46</f>
         <v/>
@@ -9829,9 +10182,10 @@
       <c r="R23" s="56" t="n"/>
       <c r="S23" s="56" t="n"/>
       <c r="T23" s="56" t="n"/>
-      <c r="U23" s="24" t="n"/>
-      <c r="V23" s="32" t="n"/>
-      <c r="W23" s="39" t="n"/>
+      <c r="U23" s="56" t="n"/>
+      <c r="V23" s="24" t="n"/>
+      <c r="W23" s="32" t="n"/>
+      <c r="X23" s="39" t="n"/>
     </row>
     <row r="24" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A24" s="40" t="n"/>
@@ -9855,15 +10209,16 @@
       <c r="L24" s="6" t="n"/>
       <c r="M24" s="6" t="n"/>
       <c r="N24" s="6" t="n"/>
-      <c r="O24" s="10" t="n"/>
+      <c r="O24" s="6" t="n"/>
       <c r="P24" s="10" t="n"/>
-      <c r="Q24" s="6" t="n"/>
+      <c r="Q24" s="10" t="n"/>
       <c r="R24" s="6" t="n"/>
       <c r="S24" s="6" t="n"/>
       <c r="T24" s="6" t="n"/>
-      <c r="U24" s="24" t="n"/>
-      <c r="V24" s="32" t="n"/>
-      <c r="W24" s="39" t="n"/>
+      <c r="U24" s="6" t="n"/>
+      <c r="V24" s="24" t="n"/>
+      <c r="W24" s="32" t="n"/>
+      <c r="X24" s="39" t="n"/>
     </row>
     <row r="25" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A25" s="40" t="n"/>
@@ -9888,10 +10243,10 @@
       <c r="I25" s="56" t="n"/>
       <c r="J25" s="56" t="n"/>
       <c r="K25" s="56" t="n"/>
-      <c r="L25" s="6" t="n"/>
+      <c r="L25" s="56" t="n"/>
       <c r="M25" s="6" t="n"/>
       <c r="N25" s="6" t="n"/>
-      <c r="O25" s="56" t="n"/>
+      <c r="O25" s="6" t="n"/>
       <c r="P25" s="56" t="inlineStr">
         <is>
           <t>Маргарита БРІТІКОВА</t>
@@ -9901,9 +10256,10 @@
       <c r="R25" s="56" t="n"/>
       <c r="S25" s="56" t="n"/>
       <c r="T25" s="56" t="n"/>
-      <c r="U25" s="24" t="n"/>
-      <c r="V25" s="32" t="n"/>
-      <c r="W25" s="39" t="n"/>
+      <c r="U25" s="56" t="n"/>
+      <c r="V25" s="24" t="n"/>
+      <c r="W25" s="32" t="n"/>
+      <c r="X25" s="39" t="n"/>
     </row>
     <row r="26" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A26" s="40" t="n"/>
@@ -9927,8 +10283,9 @@
       <c r="S26" s="35" t="n"/>
       <c r="T26" s="35" t="n"/>
       <c r="U26" s="35" t="n"/>
-      <c r="V26" s="36" t="n"/>
-      <c r="W26" s="39" t="n"/>
+      <c r="V26" s="35" t="n"/>
+      <c r="W26" s="36" t="n"/>
+      <c r="X26" s="39" t="n"/>
     </row>
     <row r="27" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A27" s="38" t="n"/>
@@ -9953,23 +10310,24 @@
       <c r="T27" s="16" t="n"/>
       <c r="U27" s="16" t="n"/>
       <c r="V27" s="16" t="n"/>
-      <c r="W27" s="39" t="n"/>
+      <c r="W27" s="16" t="n"/>
+      <c r="X27" s="39" t="n"/>
     </row>
     <row r="28" hidden="1" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A28" s="41" t="n"/>
-      <c r="W28" s="41" t="n"/>
+      <c r="X28" s="41" t="n"/>
     </row>
     <row r="29" hidden="1" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A29" s="41" t="n"/>
-      <c r="W29" s="41" t="n"/>
+      <c r="X29" s="41" t="n"/>
     </row>
     <row r="30" hidden="1" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A30" s="41" t="n"/>
-      <c r="W30" s="41" t="n"/>
+      <c r="X30" s="41" t="n"/>
     </row>
     <row r="31" hidden="1" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A31" s="41" t="n"/>
-      <c r="W31" s="41" t="n"/>
+      <c r="X31" s="41" t="n"/>
     </row>
     <row r="32" hidden="1" ht="15" customFormat="1" customHeight="1" s="11">
       <c r="A32" s="41" t="n"/>
@@ -9995,6 +10353,7 @@
       <c r="U32" s="41" t="n"/>
       <c r="V32" s="41" t="n"/>
       <c r="W32" s="41" t="n"/>
+      <c r="X32" s="41" t="n"/>
     </row>
     <row r="33" hidden="1" ht="15" customFormat="1" customHeight="1" s="11"/>
     <row r="34" hidden="1" ht="15" customFormat="1" customHeight="1" s="11"/>
@@ -10086,17 +10445,17 @@
     <row r="120" hidden="1" customHeight="1"/>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="F8:S8"/>
     <mergeCell ref="E8:E9"/>
     <mergeCell ref="C8:C9"/>
-    <mergeCell ref="C5:U5"/>
+    <mergeCell ref="C4:V4"/>
     <mergeCell ref="U8:U9"/>
+    <mergeCell ref="C3:V3"/>
+    <mergeCell ref="V8:V9"/>
+    <mergeCell ref="C7:V7"/>
     <mergeCell ref="D8:D9"/>
-    <mergeCell ref="C7:U7"/>
-    <mergeCell ref="C4:U4"/>
-    <mergeCell ref="C3:U3"/>
-    <mergeCell ref="T8:T9"/>
-    <mergeCell ref="C6:U6"/>
+    <mergeCell ref="C6:V6"/>
+    <mergeCell ref="F8:T8"/>
+    <mergeCell ref="C5:V5"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.1968503937007874" right="0.1968503937007874" top="0.1968503937007874" bottom="0.1968503937007874" header="0" footer="0"/>
